--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,568 +31,562 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
-  </si>
-  <si>
-    <t>04.09.202648</t>
-  </si>
-  <si>
-    <t>04.09.202649</t>
-  </si>
-  <si>
-    <t>04.09.202650</t>
-  </si>
-  <si>
-    <t>04.09.202651</t>
-  </si>
-  <si>
-    <t>04.09.202652</t>
-  </si>
-  <si>
-    <t>04.09.202653</t>
-  </si>
-  <si>
-    <t>04.09.202654</t>
-  </si>
-  <si>
-    <t>04.09.202655</t>
-  </si>
-  <si>
-    <t>04.09.202656</t>
-  </si>
-  <si>
-    <t>04.09.202657</t>
-  </si>
-  <si>
-    <t>04.09.202658</t>
-  </si>
-  <si>
-    <t>04.09.202659</t>
-  </si>
-  <si>
-    <t>04.09.202660</t>
-  </si>
-  <si>
-    <t>04.09.202661</t>
-  </si>
-  <si>
-    <t>04.09.202662</t>
-  </si>
-  <si>
-    <t>04.09.202663</t>
-  </si>
-  <si>
-    <t>04.09.202664</t>
-  </si>
-  <si>
-    <t>04.09.202665</t>
-  </si>
-  <si>
-    <t>04.09.202666</t>
-  </si>
-  <si>
-    <t>04.09.202667</t>
-  </si>
-  <si>
-    <t>04.09.202668</t>
-  </si>
-  <si>
-    <t>04.09.202669</t>
-  </si>
-  <si>
-    <t>04.09.202670</t>
-  </si>
-  <si>
-    <t>04.09.202671</t>
-  </si>
-  <si>
-    <t>04.09.202672</t>
-  </si>
-  <si>
-    <t>04.09.202673</t>
-  </si>
-  <si>
-    <t>04.09.202674</t>
-  </si>
-  <si>
-    <t>04.09.202675</t>
-  </si>
-  <si>
-    <t>04.09.202676</t>
-  </si>
-  <si>
-    <t>04.09.202677</t>
-  </si>
-  <si>
-    <t>04.09.202678</t>
-  </si>
-  <si>
-    <t>04.09.202679</t>
-  </si>
-  <si>
-    <t>04.09.202680</t>
-  </si>
-  <si>
-    <t>04.09.202681</t>
-  </si>
-  <si>
-    <t>04.09.202682</t>
-  </si>
-  <si>
-    <t>04.09.202683</t>
-  </si>
-  <si>
-    <t>04.09.202684</t>
-  </si>
-  <si>
-    <t>04.09.202685</t>
-  </si>
-  <si>
-    <t>04.09.202686</t>
-  </si>
-  <si>
-    <t>04.09.202687</t>
-  </si>
-  <si>
-    <t>04.09.202688</t>
-  </si>
-  <si>
-    <t>04.09.202689</t>
-  </si>
-  <si>
-    <t>04.09.202690</t>
-  </si>
-  <si>
-    <t>04.09.202691</t>
-  </si>
-  <si>
-    <t>04.09.202692</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
   </si>
 </sst>
 </file>
@@ -954,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -976,10 +970,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>0.96</v>
+        <v>11.66</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -993,10 +987,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.96</v>
+        <v>11.66</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1010,10 +1004,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.96</v>
+        <v>11.66</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1027,10 +1021,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1044,10 +1038,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.96</v>
+        <v>8.66</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1061,10 +1055,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.96</v>
+        <v>8.66</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1078,10 +1072,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>0.96</v>
+        <v>8.66</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1095,10 +1089,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.96</v>
+        <v>8.66</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1112,10 +1106,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1129,10 +1123,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1146,10 +1140,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1163,10 +1157,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1180,10 +1174,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1197,10 +1191,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1214,10 +1208,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1231,10 +1225,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1248,10 +1242,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1265,10 +1259,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1282,10 +1276,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>0.968</v>
+        <v>1.162</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1299,10 +1293,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.98</v>
+        <v>1.162</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1316,10 +1310,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.441</v>
+        <v>1.203</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1333,10 +1327,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>3.589</v>
+        <v>1.247</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1350,10 +1344,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>8.898999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1367,10 +1361,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.976</v>
+        <v>1.456</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1384,13 +1378,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>94.809</v>
+        <v>33.073</v>
       </c>
       <c r="C26">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1395,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>161.339</v>
+        <v>61.61</v>
       </c>
       <c r="C27">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1412,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>262.455</v>
+        <v>107.866</v>
       </c>
       <c r="C28">
-        <v>235</v>
+        <v>92</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1429,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>383.569</v>
+        <v>166.034</v>
       </c>
       <c r="C29">
-        <v>400</v>
+        <v>172</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1446,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>689.285</v>
+        <v>342.085</v>
       </c>
       <c r="C30">
-        <v>617</v>
+        <v>275</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1463,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>866.9349999999999</v>
+        <v>437.177</v>
       </c>
       <c r="C31">
-        <v>848</v>
+        <v>369</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1480,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>1062.46</v>
+        <v>536.602</v>
       </c>
       <c r="C32">
-        <v>1093</v>
+        <v>485</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1497,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>1266.751</v>
+        <v>648.662</v>
       </c>
       <c r="C33">
-        <v>1352</v>
+        <v>564</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1514,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>1611.856</v>
+        <v>881.574</v>
       </c>
       <c r="C34">
-        <v>1652</v>
+        <v>642</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1531,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>1804.986</v>
+        <v>1015.746</v>
       </c>
       <c r="C35">
-        <v>1896</v>
+        <v>755</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1548,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>2020.134</v>
+        <v>1125.906</v>
       </c>
       <c r="C36">
-        <v>2018</v>
+        <v>779</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1565,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>2180.97</v>
+        <v>1227.044</v>
       </c>
       <c r="C37">
-        <v>2154</v>
+        <v>774</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1582,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>2432.036</v>
+        <v>1404.62</v>
       </c>
       <c r="C38">
-        <v>2404</v>
+        <v>863</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1599,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>2589.469</v>
+        <v>1483.459</v>
       </c>
       <c r="C39">
-        <v>2608</v>
+        <v>923</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1616,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>2707.005</v>
+        <v>1576.81</v>
       </c>
       <c r="C40">
-        <v>2721</v>
+        <v>944</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1633,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>2810.176</v>
+        <v>1665.579</v>
       </c>
       <c r="C41">
-        <v>2752</v>
+        <v>973</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1650,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>2964.735</v>
+        <v>1748.097</v>
       </c>
       <c r="C42">
-        <v>2855</v>
+        <v>1094</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1667,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>3048.048</v>
+        <v>1823.675</v>
       </c>
       <c r="C43">
-        <v>2884</v>
+        <v>1083</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1684,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>3119.408</v>
+        <v>1877.783</v>
       </c>
       <c r="C44">
-        <v>2952</v>
+        <v>1055</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1701,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>3172.508</v>
+        <v>1933.593</v>
       </c>
       <c r="C45">
-        <v>2932</v>
+        <v>1145</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1718,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>3225.136</v>
+        <v>1961.348</v>
       </c>
       <c r="C46">
-        <v>2926</v>
+        <v>1160</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1735,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>3269.397</v>
+        <v>1982.53</v>
       </c>
       <c r="C47">
-        <v>2909</v>
+        <v>1218</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1752,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>3291.315</v>
+        <v>1988.804</v>
       </c>
       <c r="C48">
-        <v>2887</v>
+        <v>1192</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1769,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>3309.134</v>
+        <v>1996.582</v>
       </c>
       <c r="C49">
-        <v>2976</v>
+        <v>1160</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1786,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>3308.801</v>
+        <v>1993.003</v>
       </c>
       <c r="C50">
-        <v>3042</v>
+        <v>1201</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1803,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>3299.722</v>
+        <v>1970.484</v>
       </c>
       <c r="C51">
-        <v>3041</v>
+        <v>1153</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1820,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>3286.425</v>
+        <v>1948.515</v>
       </c>
       <c r="C52">
-        <v>3005</v>
+        <v>1186</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1837,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>3272.65</v>
+        <v>1912.122</v>
       </c>
       <c r="C53">
-        <v>3018</v>
+        <v>1121</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1854,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>3194.828</v>
+        <v>1875.257</v>
       </c>
       <c r="C54">
-        <v>2935</v>
+        <v>1217</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1871,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>3151.711</v>
+        <v>1839.955</v>
       </c>
       <c r="C55">
-        <v>2868</v>
+        <v>1142</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1888,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>3100.092</v>
+        <v>1795.62</v>
       </c>
       <c r="C56">
-        <v>2937</v>
+        <v>1118</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1905,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>3058.231</v>
+        <v>1740.829</v>
       </c>
       <c r="C57">
-        <v>2869</v>
+        <v>1069</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1922,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>2985.137</v>
+        <v>1676.412</v>
       </c>
       <c r="C58">
-        <v>2826</v>
+        <v>1011</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1939,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>2889.937</v>
+        <v>1618.906</v>
       </c>
       <c r="C59">
-        <v>2675</v>
+        <v>961</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1956,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>2799.786</v>
+        <v>1558.713</v>
       </c>
       <c r="C60">
-        <v>2615</v>
+        <v>877</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1973,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>2704.817</v>
+        <v>1483.662</v>
       </c>
       <c r="C61">
-        <v>2630</v>
+        <v>860</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1990,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>2459.856</v>
+        <v>1332.113</v>
       </c>
       <c r="C62">
-        <v>2479</v>
+        <v>828</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2007,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>2306.982</v>
+        <v>1245.598</v>
       </c>
       <c r="C63">
-        <v>2367</v>
+        <v>743</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2024,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>2151.474</v>
+        <v>1151.896</v>
       </c>
       <c r="C64">
-        <v>2195</v>
+        <v>729</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2041,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>2006.755</v>
+        <v>1070.038</v>
       </c>
       <c r="C65">
-        <v>2027</v>
+        <v>593</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2058,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>1740.004</v>
+        <v>886.614</v>
       </c>
       <c r="C66">
-        <v>1905</v>
+        <v>496</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2075,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>1523.052</v>
+        <v>775.933</v>
       </c>
       <c r="C67">
-        <v>1681</v>
+        <v>413</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2092,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>1333.799</v>
+        <v>668.537</v>
       </c>
       <c r="C68">
-        <v>1443</v>
+        <v>391</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2109,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>1122.689</v>
+        <v>544.193</v>
       </c>
       <c r="C69">
-        <v>1257</v>
+        <v>320</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2126,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>823.049</v>
+        <v>368.534</v>
       </c>
       <c r="C70">
-        <v>987</v>
+        <v>248</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2143,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>663.1950000000001</v>
+        <v>291.184</v>
       </c>
       <c r="C71">
-        <v>737</v>
+        <v>187</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2160,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>506.128</v>
+        <v>202.469</v>
       </c>
       <c r="C72">
-        <v>536</v>
+        <v>136</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2177,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>364.944</v>
+        <v>137.646</v>
       </c>
       <c r="C73">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2194,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>163.39</v>
+        <v>63.799</v>
       </c>
       <c r="C74">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2211,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>96.36</v>
+        <v>33.664</v>
       </c>
       <c r="C75">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2228,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>49.463</v>
+        <v>18.907</v>
       </c>
       <c r="C76">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,10 +2245,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>31.992</v>
+        <v>15.856</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2268,10 +2262,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>49.095</v>
+        <v>46.575</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2285,10 +2279,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>48.068</v>
+        <v>46.678</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2302,10 +2296,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>52.398</v>
+        <v>46.178</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2319,10 +2313,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>52.358</v>
+        <v>46.278</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2336,10 +2330,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>51.79</v>
+        <v>43.36</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2353,10 +2347,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>51.574</v>
+        <v>42.76</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2370,10 +2364,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>49.57</v>
+        <v>40.56</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2387,10 +2381,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>46.67</v>
+        <v>38.06</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2404,10 +2398,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>39.36</v>
+        <v>35.162</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2421,10 +2415,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>40.16</v>
+        <v>35.162</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2438,10 +2432,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>38.56</v>
+        <v>33.162</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2455,10 +2449,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>36.26</v>
+        <v>31.362</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2472,10 +2466,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>30.56</v>
+        <v>30.76</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2489,10 +2483,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2506,10 +2500,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>9.960000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2523,10 +2517,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>13.46</v>
+        <v>1.16</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2540,10 +2534,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2557,10 +2551,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2574,10 +2568,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2591,10 +2585,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2608,10 +2602,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2625,10 +2619,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2642,10 +2636,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2659,10 +2653,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2676,10 +2670,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2693,10 +2687,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2710,10 +2704,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2727,10 +2721,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2744,10 +2738,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2761,10 +2755,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2778,10 +2772,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2795,10 +2789,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2812,10 +2806,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2829,10 +2823,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2846,10 +2840,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2863,10 +2857,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2880,10 +2874,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2897,10 +2891,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2914,10 +2908,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>0.964</v>
+        <v>1.162</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2931,10 +2925,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.984</v>
+        <v>1.162</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2948,10 +2942,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>7.867</v>
+        <v>1.225</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2965,10 +2959,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>7.947</v>
+        <v>1.313</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2982,10 +2976,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>8.1</v>
+        <v>1.396</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2999,13 +2993,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>13.333</v>
+        <v>1.559</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3010,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>78.624</v>
+        <v>17.99</v>
       </c>
       <c r="C122">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3027,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>137.374</v>
+        <v>34.896</v>
       </c>
       <c r="C123">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3044,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>226.764</v>
+        <v>69.55</v>
       </c>
       <c r="C124">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3061,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>338.594</v>
+        <v>116.631</v>
       </c>
       <c r="C125">
-        <v>335</v>
+        <v>100</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3078,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>623.2670000000001</v>
+        <v>273.304</v>
       </c>
       <c r="C126">
-        <v>532</v>
+        <v>179</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3095,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>783.881</v>
+        <v>365.571</v>
       </c>
       <c r="C127">
-        <v>752</v>
+        <v>270</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3112,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>985.016</v>
+        <v>477.805</v>
       </c>
       <c r="C128">
-        <v>1021</v>
+        <v>356</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3129,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>1194.456</v>
+        <v>582.08</v>
       </c>
       <c r="C129">
-        <v>1359</v>
+        <v>420</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3146,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>1519.277</v>
+        <v>812.4450000000001</v>
       </c>
       <c r="C130">
-        <v>1687</v>
+        <v>547</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3163,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>1722.747</v>
+        <v>932.312</v>
       </c>
       <c r="C131">
-        <v>1827</v>
+        <v>674</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3180,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B132">
-        <v>1956.876</v>
-      </c>
-      <c r="C132">
-        <v>1966</v>
+        <v>1041.12</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3194,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B133">
-        <v>2149.137</v>
-      </c>
-      <c r="C133">
-        <v>2130</v>
+        <v>1155.093</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,13 +3208,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B134">
-        <v>2405.773</v>
-      </c>
-      <c r="C134">
-        <v>2292</v>
+        <v>1364.381</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3237,13 +3222,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B135">
-        <v>2581.082</v>
-      </c>
-      <c r="C135">
-        <v>2397</v>
+        <v>1469.349</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3254,13 +3236,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B136">
-        <v>2723.984</v>
-      </c>
-      <c r="C136">
-        <v>2601</v>
+        <v>1554.535</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,13 +3250,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B137">
-        <v>2824.998</v>
-      </c>
-      <c r="C137">
-        <v>2764</v>
+        <v>1635.145</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3288,13 +3264,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B138">
-        <v>2978.614</v>
-      </c>
-      <c r="C138">
-        <v>2885</v>
+        <v>1760.41</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3305,13 +3278,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B139">
-        <v>3058.722</v>
-      </c>
-      <c r="C139">
-        <v>3022</v>
+        <v>1825.05</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3322,13 +3292,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B140">
-        <v>3127.65</v>
-      </c>
-      <c r="C140">
-        <v>3076</v>
+        <v>1871.979</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3339,13 +3306,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B141">
-        <v>3177.935</v>
-      </c>
-      <c r="C141">
-        <v>3076</v>
+        <v>1937.056</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3356,13 +3320,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B142">
-        <v>3230.302</v>
-      </c>
-      <c r="C142">
-        <v>3148</v>
+        <v>1990.404</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3373,13 +3334,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B143">
-        <v>3251.786</v>
-      </c>
-      <c r="C143">
-        <v>3038</v>
+        <v>2014.873</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3390,10 +3348,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B144">
-        <v>3249.906</v>
+        <v>2032.412</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3404,10 +3362,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B145">
-        <v>3247.066</v>
+        <v>2037.188</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3418,10 +3376,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B146">
-        <v>3237.43</v>
+        <v>2033.264</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3432,10 +3390,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B147">
-        <v>3203.665</v>
+        <v>2022.174</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3446,10 +3404,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B148">
-        <v>3176.111</v>
+        <v>2007.055</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3460,10 +3418,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B149">
-        <v>3136.263</v>
+        <v>1983.457</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3474,10 +3432,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B150">
-        <v>3133.775</v>
+        <v>1929.889</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3488,10 +3446,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B151">
-        <v>3091.335</v>
+        <v>1904.428</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3502,10 +3460,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B152">
-        <v>3014.359</v>
+        <v>1866.915</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3516,10 +3474,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B153">
-        <v>2965.181</v>
+        <v>1826.348</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3530,10 +3488,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B154">
-        <v>2869.885</v>
+        <v>1743.549</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3544,10 +3502,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B155">
-        <v>2804.189</v>
+        <v>1693.287</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3558,10 +3516,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B156">
-        <v>2721.527</v>
+        <v>1631.824</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3572,10 +3530,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B157">
-        <v>2621.95</v>
+        <v>1566.041</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3586,10 +3544,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B158">
-        <v>2424.243</v>
+        <v>1439.453</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3600,10 +3558,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B159">
-        <v>2289.566</v>
+        <v>1357.551</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3614,10 +3572,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B160">
-        <v>2168.407</v>
+        <v>1275.93</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3628,10 +3586,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B161">
-        <v>2031.409</v>
+        <v>1176.989</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3642,10 +3600,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B162">
-        <v>1772.637</v>
+        <v>1001.109</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3656,10 +3614,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B163">
-        <v>1571.049</v>
+        <v>884.253</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3670,10 +3628,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B164">
-        <v>1366.472</v>
+        <v>763.891</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3684,10 +3642,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B165">
-        <v>1169.687</v>
+        <v>633.197</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3698,10 +3656,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B166">
-        <v>876.314</v>
+        <v>453.52</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3712,10 +3670,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B167">
-        <v>679.837</v>
+        <v>355.202</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3726,10 +3684,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B168">
-        <v>515.554</v>
+        <v>243.305</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3740,10 +3698,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B169">
-        <v>361.048</v>
+        <v>149.217</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3754,10 +3712,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B170">
-        <v>183.025</v>
+        <v>62.391</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3768,10 +3726,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B171">
-        <v>106.734</v>
+        <v>29.939</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3782,10 +3740,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B172">
-        <v>48.326</v>
+        <v>14.857</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3796,10 +3754,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B173">
-        <v>27.438</v>
+        <v>12.117</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3810,10 +3768,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B174">
-        <v>41.587</v>
+        <v>43.436</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3824,10 +3782,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B175">
-        <v>48.233</v>
+        <v>43.53</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3838,10 +3796,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B176">
-        <v>47.544</v>
+        <v>42.69</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3852,10 +3810,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B177">
-        <v>47.5</v>
+        <v>42.882</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3866,10 +3824,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B178">
-        <v>60.286</v>
+        <v>41.062</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3880,10 +3838,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B179">
-        <v>53.874</v>
+        <v>40.062</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3894,10 +3852,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B180">
-        <v>55.77</v>
+        <v>38.062</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3908,10 +3866,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B181">
-        <v>59.47</v>
+        <v>35.562</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3922,10 +3880,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B182">
-        <v>42.96</v>
+        <v>35.16</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3936,10 +3894,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B183">
-        <v>34.96</v>
+        <v>35.16</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3950,10 +3908,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B184">
-        <v>40.96</v>
+        <v>33.16</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3964,10 +3922,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B185">
-        <v>39.06</v>
+        <v>31.36</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3978,10 +3936,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B186">
-        <v>38.56</v>
+        <v>30.762</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3992,44 +3950,16 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
       <c r="D187">
         <v>90</v>
       </c>
       <c r="E187" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2">
-        <v>46269.9375</v>
-      </c>
-      <c r="B188">
-        <v>0.96</v>
-      </c>
-      <c r="D188">
-        <v>91</v>
-      </c>
-      <c r="E188" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>46269.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="D189">
-        <v>92</v>
-      </c>
-      <c r="E189" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,856 +31,856 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
-  </si>
-  <si>
-    <t>20.09.202639</t>
-  </si>
-  <si>
-    <t>20.09.202640</t>
-  </si>
-  <si>
-    <t>20.09.202641</t>
-  </si>
-  <si>
-    <t>20.09.202642</t>
-  </si>
-  <si>
-    <t>20.09.202643</t>
-  </si>
-  <si>
-    <t>20.09.202644</t>
-  </si>
-  <si>
-    <t>20.09.202645</t>
-  </si>
-  <si>
-    <t>20.09.202646</t>
-  </si>
-  <si>
-    <t>20.09.202647</t>
-  </si>
-  <si>
-    <t>20.09.202648</t>
-  </si>
-  <si>
-    <t>20.09.202649</t>
-  </si>
-  <si>
-    <t>20.09.202650</t>
-  </si>
-  <si>
-    <t>20.09.202651</t>
-  </si>
-  <si>
-    <t>20.09.202652</t>
-  </si>
-  <si>
-    <t>20.09.202653</t>
-  </si>
-  <si>
-    <t>20.09.202654</t>
-  </si>
-  <si>
-    <t>20.09.202655</t>
-  </si>
-  <si>
-    <t>20.09.202656</t>
-  </si>
-  <si>
-    <t>20.09.202657</t>
-  </si>
-  <si>
-    <t>20.09.202658</t>
-  </si>
-  <si>
-    <t>20.09.202659</t>
-  </si>
-  <si>
-    <t>20.09.202660</t>
-  </si>
-  <si>
-    <t>20.09.202661</t>
-  </si>
-  <si>
-    <t>20.09.202662</t>
-  </si>
-  <si>
-    <t>20.09.202663</t>
-  </si>
-  <si>
-    <t>20.09.202664</t>
-  </si>
-  <si>
-    <t>20.09.202665</t>
-  </si>
-  <si>
-    <t>20.09.202666</t>
-  </si>
-  <si>
-    <t>20.09.202667</t>
-  </si>
-  <si>
-    <t>20.09.202668</t>
-  </si>
-  <si>
-    <t>20.09.202669</t>
-  </si>
-  <si>
-    <t>20.09.202670</t>
-  </si>
-  <si>
-    <t>20.09.202671</t>
-  </si>
-  <si>
-    <t>20.09.202672</t>
-  </si>
-  <si>
-    <t>20.09.202673</t>
-  </si>
-  <si>
-    <t>20.09.202674</t>
-  </si>
-  <si>
-    <t>20.09.202675</t>
-  </si>
-  <si>
-    <t>20.09.202676</t>
-  </si>
-  <si>
-    <t>20.09.202677</t>
-  </si>
-  <si>
-    <t>20.09.202678</t>
-  </si>
-  <si>
-    <t>20.09.202679</t>
-  </si>
-  <si>
-    <t>20.09.202680</t>
-  </si>
-  <si>
-    <t>20.09.202681</t>
-  </si>
-  <si>
-    <t>20.09.202682</t>
-  </si>
-  <si>
-    <t>20.09.202683</t>
-  </si>
-  <si>
-    <t>20.09.202684</t>
-  </si>
-  <si>
-    <t>20.09.202685</t>
-  </si>
-  <si>
-    <t>20.09.202686</t>
-  </si>
-  <si>
-    <t>20.09.202687</t>
-  </si>
-  <si>
-    <t>20.09.202688</t>
-  </si>
-  <si>
-    <t>20.09.202689</t>
-  </si>
-  <si>
-    <t>20.09.202690</t>
-  </si>
-  <si>
-    <t>20.09.202691</t>
-  </si>
-  <si>
-    <t>20.09.202692</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
+  </si>
+  <si>
+    <t>30.09.202640</t>
+  </si>
+  <si>
+    <t>30.09.202641</t>
+  </si>
+  <si>
+    <t>30.09.202642</t>
+  </si>
+  <si>
+    <t>30.09.202643</t>
+  </si>
+  <si>
+    <t>30.09.202644</t>
+  </si>
+  <si>
+    <t>30.09.202645</t>
+  </si>
+  <si>
+    <t>30.09.202646</t>
+  </si>
+  <si>
+    <t>30.09.202647</t>
+  </si>
+  <si>
+    <t>30.09.202648</t>
+  </si>
+  <si>
+    <t>30.09.202649</t>
+  </si>
+  <si>
+    <t>30.09.202650</t>
+  </si>
+  <si>
+    <t>30.09.202651</t>
+  </si>
+  <si>
+    <t>30.09.202652</t>
+  </si>
+  <si>
+    <t>30.09.202653</t>
+  </si>
+  <si>
+    <t>30.09.202654</t>
+  </si>
+  <si>
+    <t>30.09.202655</t>
+  </si>
+  <si>
+    <t>30.09.202656</t>
+  </si>
+  <si>
+    <t>30.09.202657</t>
+  </si>
+  <si>
+    <t>30.09.202658</t>
+  </si>
+  <si>
+    <t>30.09.202659</t>
+  </si>
+  <si>
+    <t>30.09.202660</t>
+  </si>
+  <si>
+    <t>30.09.202661</t>
+  </si>
+  <si>
+    <t>30.09.202662</t>
+  </si>
+  <si>
+    <t>30.09.202663</t>
+  </si>
+  <si>
+    <t>30.09.202664</t>
+  </si>
+  <si>
+    <t>30.09.202665</t>
+  </si>
+  <si>
+    <t>30.09.202666</t>
+  </si>
+  <si>
+    <t>30.09.202667</t>
+  </si>
+  <si>
+    <t>30.09.202668</t>
+  </si>
+  <si>
+    <t>30.09.202669</t>
+  </si>
+  <si>
+    <t>30.09.202670</t>
+  </si>
+  <si>
+    <t>30.09.202671</t>
+  </si>
+  <si>
+    <t>30.09.202672</t>
+  </si>
+  <si>
+    <t>30.09.202673</t>
+  </si>
+  <si>
+    <t>30.09.202674</t>
+  </si>
+  <si>
+    <t>30.09.202675</t>
+  </si>
+  <si>
+    <t>30.09.202676</t>
+  </si>
+  <si>
+    <t>30.09.202677</t>
+  </si>
+  <si>
+    <t>30.09.202678</t>
+  </si>
+  <si>
+    <t>30.09.202679</t>
+  </si>
+  <si>
+    <t>30.09.202680</t>
+  </si>
+  <si>
+    <t>30.09.202681</t>
+  </si>
+  <si>
+    <t>30.09.202682</t>
+  </si>
+  <si>
+    <t>30.09.202683</t>
+  </si>
+  <si>
+    <t>30.09.202684</t>
+  </si>
+  <si>
+    <t>30.09.202685</t>
+  </si>
+  <si>
+    <t>30.09.202686</t>
+  </si>
+  <si>
+    <t>30.09.202687</t>
+  </si>
+  <si>
+    <t>30.09.202688</t>
+  </si>
+  <si>
+    <t>30.09.202689</t>
+  </si>
+  <si>
+    <t>30.09.202690</t>
+  </si>
+  <si>
+    <t>30.09.202691</t>
+  </si>
+  <si>
+    <t>30.09.202692</t>
   </si>
 </sst>
 </file>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>13.56</v>
+        <v>1.16</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>13.56</v>
+        <v>1.16</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.14</v>
+        <v>1.24</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.14</v>
+        <v>1.24</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>5.14</v>
+        <v>1.24</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>5.14</v>
+        <v>1.24</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>5.14</v>
+        <v>1.24</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>3.14</v>
+        <v>1.24</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.34</v>
+        <v>1.24</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>4.66</v>
+        <v>1.16</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>3.06</v>
+        <v>1.16</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.06</v>
+        <v>1.16</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.06</v>
+        <v>1.16</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>5.064</v>
+        <v>1.168</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.576</v>
+        <v>1.184</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>14.092</v>
+        <v>2.448</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>14.252</v>
+        <v>3.181</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>16.14</v>
+        <v>4.294</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.538</v>
+        <v>10.908</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>31.097</v>
+        <v>31.391</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>59.086</v>
+        <v>40.842</v>
       </c>
       <c r="C27">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1706,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>132.979</v>
+        <v>89.929</v>
       </c>
       <c r="C28">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>228.031</v>
+        <v>192.43</v>
       </c>
       <c r="C29">
-        <v>273</v>
+        <v>194</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1740,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>511.306</v>
+        <v>494.552</v>
       </c>
       <c r="C30">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>670.47</v>
+        <v>670.3630000000001</v>
       </c>
       <c r="C31">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1774,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>870.21</v>
+        <v>870.645</v>
       </c>
       <c r="C32">
-        <v>813</v>
+        <v>853</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1791,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>1063.431</v>
+        <v>1100.164</v>
       </c>
       <c r="C33">
-        <v>998</v>
+        <v>1145</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1808,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>1393.274</v>
+        <v>1469.69</v>
       </c>
       <c r="C34">
-        <v>1229</v>
+        <v>1434</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>1590.06</v>
+        <v>1703.75</v>
       </c>
       <c r="C35">
-        <v>1401</v>
+        <v>1698</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>1811.688</v>
+        <v>1935.042</v>
       </c>
       <c r="C36">
-        <v>1554</v>
+        <v>1882</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>1977.532</v>
+        <v>2163.199</v>
       </c>
       <c r="C37">
-        <v>1704</v>
+        <v>2043</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>2222.037</v>
+        <v>2453.473</v>
       </c>
       <c r="C38">
-        <v>1813</v>
+        <v>2286</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>2363.881</v>
+        <v>2612.775</v>
       </c>
       <c r="C39">
-        <v>1948</v>
+        <v>2372</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>2502.008</v>
+        <v>2742.703</v>
       </c>
       <c r="C40">
-        <v>2000</v>
+        <v>2441</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>2611.342</v>
+        <v>2858.456</v>
       </c>
       <c r="C41">
-        <v>2062</v>
+        <v>2518</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1944,13 +1944,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>2715.648</v>
+        <v>2993.13</v>
       </c>
       <c r="C42">
-        <v>2113</v>
+        <v>2617</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1961,13 +1961,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>2798.179</v>
+        <v>3062.103</v>
       </c>
       <c r="C43">
-        <v>2159</v>
+        <v>2688</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>2866.483</v>
+        <v>2832.429</v>
       </c>
       <c r="C44">
-        <v>2214</v>
+        <v>2761</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1995,13 +1995,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>2912.851</v>
+        <v>2870.645</v>
       </c>
       <c r="C45">
-        <v>2246</v>
+        <v>2809</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>2981.872</v>
+        <v>2911.34</v>
       </c>
       <c r="C46">
-        <v>2259</v>
+        <v>2793</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2029,13 +2029,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>2999.996</v>
+        <v>2935.127</v>
       </c>
       <c r="C47">
-        <v>2282</v>
+        <v>2773</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>3023.408</v>
+        <v>2935.74</v>
       </c>
       <c r="C48">
-        <v>2306</v>
+        <v>2760</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2063,13 +2063,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>3035.697</v>
+        <v>2928.916</v>
       </c>
       <c r="C49">
-        <v>2279</v>
+        <v>2760</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>3028.508</v>
+        <v>2906.463</v>
       </c>
       <c r="C50">
-        <v>2293</v>
+        <v>2626</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>3022.42</v>
+        <v>2880.975</v>
       </c>
       <c r="C51">
-        <v>2374</v>
+        <v>2642</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2114,13 +2114,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>3008.501</v>
+        <v>2849.133</v>
       </c>
       <c r="C52">
-        <v>2357</v>
+        <v>2624</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2131,13 +2131,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>2991.305</v>
+        <v>2800.061</v>
       </c>
       <c r="C53">
-        <v>2276</v>
+        <v>2589</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2148,13 +2148,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>2932.644</v>
+        <v>2709.638</v>
       </c>
       <c r="C54">
-        <v>2329</v>
+        <v>2594</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2165,13 +2165,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>2895.814</v>
+        <v>2635.734</v>
       </c>
       <c r="C55">
-        <v>2351</v>
+        <v>2518</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2182,13 +2182,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>2838.808</v>
+        <v>2535.383</v>
       </c>
       <c r="C56">
-        <v>2343</v>
+        <v>2550</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2199,13 +2199,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>2776.972</v>
+        <v>2460.331</v>
       </c>
       <c r="C57">
-        <v>2325</v>
+        <v>2406</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2216,13 +2216,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>2641.75</v>
+        <v>2273.027</v>
       </c>
       <c r="C58">
-        <v>2327</v>
+        <v>2316</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>2550.745</v>
+        <v>2175.426</v>
       </c>
       <c r="C59">
         <v>2282</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>2450.406</v>
+        <v>2053.964</v>
       </c>
       <c r="C60">
-        <v>2211</v>
+        <v>2093</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2267,13 +2267,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>2341.953</v>
+        <v>1941.099</v>
       </c>
       <c r="C61">
-        <v>2176</v>
+        <v>2006</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2284,13 +2284,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>2184.411</v>
+        <v>1706.851</v>
       </c>
       <c r="C62">
-        <v>2057</v>
+        <v>1817</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2301,13 +2301,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>2028.368</v>
+        <v>1570.593</v>
       </c>
       <c r="C63">
-        <v>1969</v>
+        <v>1681</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2318,13 +2318,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>1884.445</v>
+        <v>1446.983</v>
       </c>
       <c r="C64">
-        <v>1878</v>
+        <v>1514</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2335,13 +2335,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>1726.577</v>
+        <v>1430.74</v>
       </c>
       <c r="C65">
-        <v>1705</v>
+        <v>1355</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2352,13 +2352,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>1419.466</v>
+        <v>1187.067</v>
       </c>
       <c r="C66">
-        <v>1503</v>
+        <v>1127</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2369,13 +2369,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>1228.01</v>
+        <v>1014.184</v>
       </c>
       <c r="C67">
-        <v>1280</v>
+        <v>960</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2386,13 +2386,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>1025.833</v>
+        <v>824.4640000000001</v>
       </c>
       <c r="C68">
-        <v>1082</v>
+        <v>743</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>825.982</v>
+        <v>666.095</v>
       </c>
       <c r="C69">
-        <v>895</v>
+        <v>580</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2420,13 +2420,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>557.951</v>
+        <v>405.28</v>
       </c>
       <c r="C70">
-        <v>688</v>
+        <v>396</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2437,13 +2437,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>400.59</v>
+        <v>257.392</v>
       </c>
       <c r="C71">
-        <v>493</v>
+        <v>256</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2454,13 +2454,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>251.042</v>
+        <v>161.919</v>
       </c>
       <c r="C72">
-        <v>293</v>
+        <v>131</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2471,13 +2471,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>155.945</v>
+        <v>93.892</v>
       </c>
       <c r="C73">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>89.795</v>
+        <v>32.579</v>
       </c>
       <c r="C74">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2505,13 +2505,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>60.68</v>
+        <v>65.94199999999999</v>
       </c>
       <c r="C75">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>52.816</v>
+        <v>64.666</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>59.671</v>
+        <v>63.471</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>64.63800000000001</v>
+        <v>61.106</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>64.322</v>
+        <v>60.994</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>64.602</v>
+        <v>58.846</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>65.77800000000001</v>
+        <v>56.806</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>60.868</v>
+        <v>55.178</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>61.06</v>
+        <v>55.17</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>60.06</v>
+        <v>55.162</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>51.86</v>
+        <v>15.562</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>16.56</v>
+        <v>11.26</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.56</v>
+        <v>10.76</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>14.66</v>
+        <v>10.26</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>12.76</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>10.36</v>
+        <v>4.86</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2777,10 +2777,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>9.460000000000001</v>
+        <v>4.26</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>9.359999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>9.16</v>
+        <v>2.66</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>7.06</v>
+        <v>1.16</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>2.462</v>
+        <v>2.08</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>2.462</v>
+        <v>2.08</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>3.262</v>
+        <v>1.58</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>3.662</v>
+        <v>1.08</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>2.943</v>
+        <v>1.16</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>7.243</v>
+        <v>1.16</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>8.143000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>8.943</v>
+        <v>1.16</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>14.04</v>
+        <v>1.16</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>6.34</v>
+        <v>1.16</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>7.14</v>
+        <v>1.16</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>7.14</v>
+        <v>1.16</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>7.46</v>
+        <v>1.08</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>6.66</v>
+        <v>1.08</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.46</v>
+        <v>1.08</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>6.66</v>
+        <v>1.08</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>7.46</v>
+        <v>1.082</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>7.06</v>
+        <v>1.082</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>7.06</v>
+        <v>1.09</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>7.064</v>
+        <v>1.106</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>11.975</v>
+        <v>1.203</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>6.499</v>
+        <v>1.938</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -3270,10 +3270,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>6.284</v>
+        <v>3.06</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>7.022</v>
+        <v>4.738</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>24.5</v>
+        <v>13.807</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3321,13 +3321,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>51.038</v>
+        <v>18.466</v>
       </c>
       <c r="C123">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>117.445</v>
+        <v>44.213</v>
       </c>
       <c r="C124">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3355,13 +3355,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>206.484</v>
+        <v>107.316</v>
       </c>
       <c r="C125">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3372,13 +3372,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>438.122</v>
+        <v>318.476</v>
       </c>
       <c r="C126">
-        <v>340</v>
+        <v>234</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3389,13 +3389,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>582.117</v>
+        <v>427.509</v>
       </c>
       <c r="C127">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>775.8680000000001</v>
+        <v>585.152</v>
       </c>
       <c r="C128">
-        <v>685</v>
+        <v>597</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>933.4829999999999</v>
+        <v>740.974</v>
       </c>
       <c r="C129">
-        <v>863</v>
+        <v>737</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3440,13 +3440,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>1265.87</v>
+        <v>1070.92</v>
       </c>
       <c r="C130">
-        <v>1040</v>
+        <v>926</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3457,13 +3457,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>1447.957</v>
+        <v>1217.317</v>
       </c>
       <c r="C131">
-        <v>1211</v>
+        <v>1161</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>1646.894</v>
+        <v>1416.664</v>
       </c>
       <c r="C132">
-        <v>1373</v>
+        <v>1345</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3491,13 +3491,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>1820.414</v>
+        <v>1588.567</v>
       </c>
       <c r="C133">
-        <v>1513</v>
+        <v>1660</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>2141.574</v>
+        <v>1852.252</v>
       </c>
       <c r="C134">
-        <v>1672</v>
+        <v>1902</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3525,13 +3525,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>2290.856</v>
+        <v>2000.506</v>
       </c>
       <c r="C135">
-        <v>1767</v>
+        <v>2028</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3542,13 +3542,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>2442.269</v>
+        <v>2140.575</v>
       </c>
       <c r="C136">
-        <v>1825</v>
+        <v>2186</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3559,13 +3559,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>2564.708</v>
+        <v>2261.816</v>
       </c>
       <c r="C137">
-        <v>1882</v>
+        <v>2378</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>2681.767</v>
+        <v>2496.862</v>
       </c>
       <c r="C138">
-        <v>2035</v>
+        <v>2424</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>2768.882</v>
+        <v>2563.515</v>
       </c>
       <c r="C139">
-        <v>2060</v>
+        <v>2499</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3610,13 +3610,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>2842.469</v>
+        <v>2620.821</v>
       </c>
       <c r="C140">
-        <v>2116</v>
+        <v>2664</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3627,13 +3627,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
-        <v>2901.034</v>
+        <v>2690.248</v>
       </c>
       <c r="C141">
-        <v>2137</v>
+        <v>2544</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3644,13 +3644,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>2944.168</v>
+        <v>2763.813</v>
       </c>
       <c r="C142">
-        <v>2182</v>
+        <v>2513</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3661,13 +3661,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>2974.026</v>
+        <v>2772.213</v>
       </c>
       <c r="C143">
-        <v>2284</v>
+        <v>2511</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>2996.905</v>
+        <v>2791.827</v>
       </c>
       <c r="C144">
-        <v>2293</v>
+        <v>2565</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3695,13 +3695,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>2998.416</v>
+        <v>2800.643</v>
       </c>
       <c r="C145">
-        <v>2301</v>
+        <v>2613</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3712,13 +3712,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>3009.218</v>
+        <v>2772.893</v>
       </c>
       <c r="C146">
-        <v>2257</v>
+        <v>2619</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3729,13 +3729,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>3003.331</v>
+        <v>2730.304</v>
       </c>
       <c r="C147">
-        <v>2258</v>
+        <v>2507</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3746,13 +3746,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>2991.429</v>
+        <v>2703.3</v>
       </c>
       <c r="C148">
-        <v>2232</v>
+        <v>2440</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3763,13 +3763,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>2968.915</v>
+        <v>2665.35</v>
       </c>
       <c r="C149">
-        <v>2186</v>
+        <v>2296</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3780,13 +3780,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>2914.371</v>
+        <v>2606.118</v>
       </c>
       <c r="C150">
-        <v>2164</v>
+        <v>2251</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3797,13 +3797,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>2873.22</v>
+        <v>2524.586</v>
       </c>
       <c r="C151">
-        <v>2112</v>
+        <v>2250</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3814,13 +3814,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>2830.902</v>
+        <v>2450.729</v>
       </c>
       <c r="C152">
-        <v>2135</v>
+        <v>2250</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3831,13 +3831,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>2769.783</v>
+        <v>2371.64</v>
       </c>
       <c r="C153">
-        <v>2109</v>
+        <v>2192</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3848,13 +3848,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>2671.25</v>
+        <v>2231.521</v>
       </c>
       <c r="C154">
-        <v>2066</v>
+        <v>2106</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3865,13 +3865,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>2588.036</v>
+        <v>2115.857</v>
       </c>
       <c r="C155">
-        <v>2020</v>
+        <v>1939</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>2495.512</v>
+        <v>1990.617</v>
       </c>
       <c r="C156">
-        <v>1919</v>
+        <v>1858</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3899,13 +3899,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>2399.103</v>
+        <v>1878.916</v>
       </c>
       <c r="C157">
-        <v>1836</v>
+        <v>1848</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3916,13 +3916,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>2209.636</v>
+        <v>1676.271</v>
       </c>
       <c r="C158">
-        <v>1700</v>
+        <v>1652</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3933,13 +3933,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>2073.375</v>
+        <v>1523.212</v>
       </c>
       <c r="C159">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3950,13 +3950,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>1923.078</v>
+        <v>1379.853</v>
       </c>
       <c r="C160">
-        <v>1514</v>
+        <v>1469</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>1760.895</v>
+        <v>1226.917</v>
       </c>
       <c r="C161">
-        <v>1458</v>
+        <v>1387</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3984,13 +3984,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>1437.278</v>
+        <v>993.991</v>
       </c>
       <c r="C162">
-        <v>1310</v>
+        <v>1180</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4001,13 +4001,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>1254.371</v>
+        <v>834.131</v>
       </c>
       <c r="C163">
-        <v>1125</v>
+        <v>958</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4018,13 +4018,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>1051.656</v>
+        <v>682.703</v>
       </c>
       <c r="C164">
-        <v>1016</v>
+        <v>762</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4035,13 +4035,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>857.5839999999999</v>
+        <v>545.025</v>
       </c>
       <c r="C165">
-        <v>832</v>
+        <v>619</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4052,13 +4052,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>565.972</v>
+        <v>312.749</v>
       </c>
       <c r="C166">
-        <v>592</v>
+        <v>440</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4069,13 +4069,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>415.376</v>
+        <v>209.529</v>
       </c>
       <c r="C167">
-        <v>398</v>
+        <v>294</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4086,13 +4086,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>261.591</v>
+        <v>131.847</v>
       </c>
       <c r="C168">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4103,13 +4103,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>157.122</v>
+        <v>68.044</v>
       </c>
       <c r="C169">
-        <v>161</v>
+        <v>48</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>80.075</v>
+        <v>65.90300000000001</v>
       </c>
       <c r="C170">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4137,13 +4137,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>51.007</v>
+        <v>68.39100000000001</v>
       </c>
       <c r="C171">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4154,13 +4154,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>43.854</v>
+        <v>67.877</v>
       </c>
       <c r="C172">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4171,13 +4171,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>44.062</v>
+        <v>67.02800000000001</v>
       </c>
       <c r="C173">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>47.622</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="C174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>48.462</v>
+        <v>66.256</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -4222,10 +4222,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>48.342</v>
+        <v>65.904</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>49.21</v>
+        <v>61.24</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>47.38</v>
+        <v>52.875</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>46.76</v>
+        <v>14.189</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>44.76</v>
+        <v>12.281</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>41.66</v>
+        <v>10.181</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4324,10 +4324,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>6.662</v>
+        <v>4.082</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>6.562</v>
+        <v>9.481999999999999</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>4.162</v>
+        <v>9.282</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4375,10 +4375,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>1.962</v>
+        <v>8.782</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.06</v>
+        <v>3.18</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.06</v>
+        <v>2.88</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>1.06</v>
+        <v>2.38</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>1.06</v>
+        <v>2.28</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -4477,10 +4477,10 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>4.96</v>
+        <v>1.08</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -4732,10 +4732,10 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -4749,10 +4749,10 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -4800,10 +4800,10 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>1.162</v>
+        <v>1.08</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>1.162</v>
+        <v>1.08</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>1.162</v>
+        <v>1.088</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -4851,10 +4851,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>1.17</v>
+        <v>1.104</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>1.361</v>
+        <v>1.222</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>4.96</v>
+        <v>1.342</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -4902,10 +4902,10 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>5.114</v>
+        <v>1.454</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -4919,10 +4919,10 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>5.343</v>
+        <v>1.607</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -4936,10 +4936,10 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>25.325</v>
+        <v>13.429</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -4953,13 +4953,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>48.448</v>
+        <v>19.176</v>
       </c>
       <c r="C219">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4970,13 +4970,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>116.911</v>
+        <v>57.782</v>
       </c>
       <c r="C220">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4987,13 +4987,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>207.832</v>
+        <v>146.852</v>
       </c>
       <c r="C221">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>476.289</v>
+        <v>456.106</v>
       </c>
       <c r="C222">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5021,13 +5021,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>641.2</v>
+        <v>630.788</v>
       </c>
       <c r="C223">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5038,13 +5038,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>839.292</v>
+        <v>895.01</v>
       </c>
       <c r="C224">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5055,13 +5055,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>1059.265</v>
+        <v>1151.509</v>
       </c>
       <c r="C225">
-        <v>938</v>
+        <v>963</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5072,13 +5072,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>1415.803</v>
+        <v>1585.826</v>
       </c>
       <c r="C226">
-        <v>1097</v>
+        <v>1223</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5089,13 +5089,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>1618.376</v>
+        <v>1813.448</v>
       </c>
       <c r="C227">
-        <v>1265</v>
+        <v>1475</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5106,13 +5106,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>1832.221</v>
+        <v>2063.628</v>
       </c>
       <c r="C228">
-        <v>1424</v>
+        <v>1661</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5123,13 +5123,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>2029.992</v>
+        <v>2289.755</v>
       </c>
       <c r="C229">
-        <v>1614</v>
+        <v>1895</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5140,13 +5140,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>2330.164</v>
+        <v>2687.266</v>
       </c>
       <c r="C230">
-        <v>1798</v>
+        <v>2128</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5157,10 +5157,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>2492.244</v>
+        <v>2830.778</v>
+      </c>
+      <c r="C231">
+        <v>2348</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5171,10 +5174,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B232">
-        <v>2644.105</v>
+        <v>2977.207</v>
+      </c>
+      <c r="C232">
+        <v>2468</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5185,10 +5191,10 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B233">
-        <v>2507.971</v>
+        <v>3103.374</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5199,10 +5205,10 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B234">
-        <v>2645.455</v>
+        <v>3262.909</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5213,10 +5219,10 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B235">
-        <v>2626.607</v>
+        <v>3349.309</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5227,10 +5233,10 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B236">
-        <v>2726.665</v>
+        <v>3413.734</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5241,10 +5247,10 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B237">
-        <v>2618.21</v>
+        <v>3471.937</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5255,10 +5261,10 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B238">
-        <v>2444.298</v>
+        <v>3509.55</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5269,10 +5275,10 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B239">
-        <v>2470.978</v>
+        <v>3539.383</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5283,10 +5289,10 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B240">
-        <v>2489.029</v>
+        <v>3560.622</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5297,10 +5303,10 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B241">
-        <v>2502.717</v>
+        <v>3574.442</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5311,10 +5317,10 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B242">
-        <v>2528.601</v>
+        <v>3568.444</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5325,10 +5331,10 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B243">
-        <v>2510.899</v>
+        <v>3564.931</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5339,10 +5345,10 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B244">
-        <v>2493.466</v>
+        <v>3553.282</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5353,10 +5359,10 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B245">
-        <v>2468.98</v>
+        <v>3535.308</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5367,10 +5373,10 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B246">
-        <v>2304.99</v>
+        <v>3494.304</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5381,10 +5387,10 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B247">
-        <v>2267.393</v>
+        <v>3462.053</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5395,10 +5401,10 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B248">
-        <v>2222.629</v>
+        <v>3409.963</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5409,10 +5415,10 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B249">
-        <v>2219.169</v>
+        <v>3353.559</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5423,10 +5429,10 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B250">
-        <v>2177.488</v>
+        <v>3224.779</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5437,10 +5443,10 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B251">
-        <v>2100.828</v>
+        <v>3136.936</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5451,10 +5457,10 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B252">
-        <v>2014.696</v>
+        <v>3035.398</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5465,10 +5471,10 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B253">
-        <v>1921.585</v>
+        <v>2893.48</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5479,10 +5485,10 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B254">
-        <v>2057.194</v>
+        <v>2621.13</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5493,10 +5499,10 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B255">
-        <v>1926.647</v>
+        <v>2430.702</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5507,10 +5513,10 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B256">
-        <v>1813.899</v>
+        <v>2225.928</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5521,10 +5527,10 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B257">
-        <v>1701.357</v>
+        <v>2006.891</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5535,10 +5541,10 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B258">
-        <v>1489.15</v>
+        <v>1617.702</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5549,10 +5555,10 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B259">
-        <v>1292.313</v>
+        <v>1365.998</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5563,10 +5569,10 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B260">
-        <v>1085.41</v>
+        <v>1092.291</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5577,10 +5583,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B261">
-        <v>868.647</v>
+        <v>838.862</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5591,10 +5597,10 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B262">
-        <v>571.021</v>
+        <v>481.849</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5605,10 +5611,10 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B263">
-        <v>412.783</v>
+        <v>307.929</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5619,10 +5625,10 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B264">
-        <v>267.756</v>
+        <v>170.101</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5633,10 +5639,10 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B265">
-        <v>151.396</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5647,10 +5653,10 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B266">
-        <v>50.095</v>
+        <v>22.545</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5661,10 +5667,10 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B267">
-        <v>19.752</v>
+        <v>19.845</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5675,10 +5681,10 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B268">
-        <v>47.119</v>
+        <v>19.387</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5689,10 +5695,10 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B269">
-        <v>50.412</v>
+        <v>18.661</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5703,10 +5709,10 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B270">
-        <v>54.779</v>
+        <v>17.924</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5717,10 +5723,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B271">
-        <v>53.692</v>
+        <v>17.76</v>
       </c>
       <c r="D271">
         <v>78</v>
@@ -5731,10 +5737,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B272">
-        <v>53.582</v>
+        <v>15.708</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -5745,10 +5751,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B273">
-        <v>54.036</v>
+        <v>13.844</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -5759,10 +5765,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B274">
-        <v>51.076</v>
+        <v>12.708</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -5773,10 +5779,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B275">
-        <v>52.66</v>
+        <v>11.788</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -5787,10 +5793,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B276">
-        <v>50.66</v>
+        <v>10.78</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -5801,10 +5807,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B277">
-        <v>47.76</v>
+        <v>7.98</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -5815,10 +5821,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B278">
-        <v>45.26</v>
+        <v>6.78</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -5829,10 +5835,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B279">
-        <v>44.66</v>
+        <v>6.08</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -5843,10 +5849,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B280">
-        <v>9.76</v>
+        <v>5.08</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -5857,10 +5863,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B281">
-        <v>8.26</v>
+        <v>2.98</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -5871,10 +5877,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B282">
-        <v>3.662</v>
+        <v>5.482</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -5885,10 +5891,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B283">
-        <v>2.062</v>
+        <v>3.482</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -5899,10 +5905,10 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B284">
-        <v>1.962</v>
+        <v>2.582</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -5913,10 +5919,10 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B285">
-        <v>1.662</v>
+        <v>1.482</v>
       </c>
       <c r="D285">
         <v>92</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,856 +31,856 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
-  </si>
-  <si>
-    <t>30.09.202640</t>
-  </si>
-  <si>
-    <t>30.09.202641</t>
-  </si>
-  <si>
-    <t>30.09.202642</t>
-  </si>
-  <si>
-    <t>30.09.202643</t>
-  </si>
-  <si>
-    <t>30.09.202644</t>
-  </si>
-  <si>
-    <t>30.09.202645</t>
-  </si>
-  <si>
-    <t>30.09.202646</t>
-  </si>
-  <si>
-    <t>30.09.202647</t>
-  </si>
-  <si>
-    <t>30.09.202648</t>
-  </si>
-  <si>
-    <t>30.09.202649</t>
-  </si>
-  <si>
-    <t>30.09.202650</t>
-  </si>
-  <si>
-    <t>30.09.202651</t>
-  </si>
-  <si>
-    <t>30.09.202652</t>
-  </si>
-  <si>
-    <t>30.09.202653</t>
-  </si>
-  <si>
-    <t>30.09.202654</t>
-  </si>
-  <si>
-    <t>30.09.202655</t>
-  </si>
-  <si>
-    <t>30.09.202656</t>
-  </si>
-  <si>
-    <t>30.09.202657</t>
-  </si>
-  <si>
-    <t>30.09.202658</t>
-  </si>
-  <si>
-    <t>30.09.202659</t>
-  </si>
-  <si>
-    <t>30.09.202660</t>
-  </si>
-  <si>
-    <t>30.09.202661</t>
-  </si>
-  <si>
-    <t>30.09.202662</t>
-  </si>
-  <si>
-    <t>30.09.202663</t>
-  </si>
-  <si>
-    <t>30.09.202664</t>
-  </si>
-  <si>
-    <t>30.09.202665</t>
-  </si>
-  <si>
-    <t>30.09.202666</t>
-  </si>
-  <si>
-    <t>30.09.202667</t>
-  </si>
-  <si>
-    <t>30.09.202668</t>
-  </si>
-  <si>
-    <t>30.09.202669</t>
-  </si>
-  <si>
-    <t>30.09.202670</t>
-  </si>
-  <si>
-    <t>30.09.202671</t>
-  </si>
-  <si>
-    <t>30.09.202672</t>
-  </si>
-  <si>
-    <t>30.09.202673</t>
-  </si>
-  <si>
-    <t>30.09.202674</t>
-  </si>
-  <si>
-    <t>30.09.202675</t>
-  </si>
-  <si>
-    <t>30.09.202676</t>
-  </si>
-  <si>
-    <t>30.09.202677</t>
-  </si>
-  <si>
-    <t>30.09.202678</t>
-  </si>
-  <si>
-    <t>30.09.202679</t>
-  </si>
-  <si>
-    <t>30.09.202680</t>
-  </si>
-  <si>
-    <t>30.09.202681</t>
-  </si>
-  <si>
-    <t>30.09.202682</t>
-  </si>
-  <si>
-    <t>30.09.202683</t>
-  </si>
-  <si>
-    <t>30.09.202684</t>
-  </si>
-  <si>
-    <t>30.09.202685</t>
-  </si>
-  <si>
-    <t>30.09.202686</t>
-  </si>
-  <si>
-    <t>30.09.202687</t>
-  </si>
-  <si>
-    <t>30.09.202688</t>
-  </si>
-  <si>
-    <t>30.09.202689</t>
-  </si>
-  <si>
-    <t>30.09.202690</t>
-  </si>
-  <si>
-    <t>30.09.202691</t>
-  </si>
-  <si>
-    <t>30.09.202692</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
   </si>
 </sst>
 </file>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
-        <v>1.16</v>
+        <v>1.524</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.16</v>
+        <v>2.026</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.16</v>
+        <v>2.926</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>1.16</v>
+        <v>3.841</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.24</v>
+        <v>5.014</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.24</v>
+        <v>6.142</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>1.24</v>
+        <v>7.104</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.24</v>
+        <v>7.976</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.24</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>1.24</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.24</v>
+        <v>10.427</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.24</v>
+        <v>11.119</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>1.16</v>
+        <v>11.662</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.16</v>
+        <v>12.161</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.16</v>
+        <v>12.954</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>1.16</v>
+        <v>13.329</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.16</v>
+        <v>13.608</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.16</v>
+        <v>13.811</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
-        <v>1.168</v>
+        <v>14.133</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.184</v>
+        <v>14.31</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.448</v>
+        <v>16.512</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>3.181</v>
+        <v>17.177</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.294</v>
+        <v>18.228</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.908</v>
+        <v>19.823</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
-        <v>31.391</v>
+        <v>31.557</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
-        <v>40.842</v>
+        <v>41.306</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1706,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>89.929</v>
+        <v>82.729</v>
       </c>
       <c r="C28">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
-        <v>192.43</v>
+        <v>191.031</v>
       </c>
       <c r="C29">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1740,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
-        <v>494.552</v>
+        <v>500.657</v>
       </c>
       <c r="C30">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
-        <v>670.3630000000001</v>
+        <v>698.106</v>
       </c>
       <c r="C31">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1774,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
-        <v>870.645</v>
+        <v>935.159</v>
       </c>
       <c r="C32">
-        <v>853</v>
+        <v>893</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1791,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
-        <v>1100.164</v>
+        <v>1178.19</v>
       </c>
       <c r="C33">
-        <v>1145</v>
+        <v>1169</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1808,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>1469.69</v>
+        <v>1649.822</v>
       </c>
       <c r="C34">
-        <v>1434</v>
+        <v>1457</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>1703.75</v>
+        <v>1886.309</v>
       </c>
       <c r="C35">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>1935.042</v>
+        <v>2140.146</v>
       </c>
       <c r="C36">
-        <v>1882</v>
+        <v>1918</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
-        <v>2163.199</v>
+        <v>2379.496</v>
       </c>
       <c r="C37">
-        <v>2043</v>
+        <v>2203</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
-        <v>2453.473</v>
+        <v>2730.372</v>
       </c>
       <c r="C38">
-        <v>2286</v>
+        <v>2384</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>2612.775</v>
+        <v>2901.825</v>
       </c>
       <c r="C39">
-        <v>2372</v>
+        <v>2543</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>2742.703</v>
+        <v>3044.233</v>
       </c>
       <c r="C40">
-        <v>2441</v>
+        <v>2654</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,13 +1927,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
-        <v>2858.456</v>
-      </c>
-      <c r="C41">
-        <v>2518</v>
+        <v>3173.534</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1944,13 +1941,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>2993.13</v>
-      </c>
-      <c r="C42">
-        <v>2617</v>
+        <v>3360.243</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1961,13 +1955,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>3062.103</v>
-      </c>
-      <c r="C43">
-        <v>2688</v>
+        <v>3421.542</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1978,13 +1969,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
-        <v>2832.429</v>
-      </c>
-      <c r="C44">
-        <v>2761</v>
+        <v>3491.074</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1995,13 +1983,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
-        <v>2870.645</v>
-      </c>
-      <c r="C45">
-        <v>2809</v>
+        <v>3537.677</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2012,13 +1997,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>2911.34</v>
-      </c>
-      <c r="C46">
-        <v>2793</v>
+        <v>3584.559</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2029,13 +2011,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>2935.127</v>
-      </c>
-      <c r="C47">
-        <v>2773</v>
+        <v>3615.223</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2046,13 +2025,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>2935.74</v>
-      </c>
-      <c r="C48">
-        <v>2760</v>
+        <v>3628.19</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2063,13 +2039,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>2928.916</v>
-      </c>
-      <c r="C49">
-        <v>2760</v>
+        <v>3633.948</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2080,13 +2053,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>2906.463</v>
-      </c>
-      <c r="C50">
-        <v>2626</v>
+        <v>3627.517</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2097,13 +2067,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>2880.975</v>
-      </c>
-      <c r="C51">
-        <v>2642</v>
+        <v>3609.923</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2114,13 +2081,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
-        <v>2849.133</v>
-      </c>
-      <c r="C52">
-        <v>2624</v>
+        <v>3593.857</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2131,13 +2095,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
-        <v>2800.061</v>
-      </c>
-      <c r="C53">
-        <v>2589</v>
+        <v>3563.442</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2148,13 +2109,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
-        <v>2709.638</v>
-      </c>
-      <c r="C54">
-        <v>2594</v>
+        <v>3509.612</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2165,13 +2123,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
-        <v>2635.734</v>
-      </c>
-      <c r="C55">
-        <v>2518</v>
+        <v>3449.203</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2182,13 +2137,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
-        <v>2535.383</v>
-      </c>
-      <c r="C56">
-        <v>2550</v>
+        <v>3399.665</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2199,13 +2151,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
-        <v>2460.331</v>
-      </c>
-      <c r="C57">
-        <v>2406</v>
+        <v>3329.072</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2216,13 +2165,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
-        <v>2273.027</v>
-      </c>
-      <c r="C58">
-        <v>2316</v>
+        <v>3191.232</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2233,13 +2179,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
-        <v>2175.426</v>
-      </c>
-      <c r="C59">
-        <v>2282</v>
+        <v>3125.983</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2250,13 +2193,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>2053.964</v>
-      </c>
-      <c r="C60">
-        <v>2093</v>
+        <v>2988.628</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2267,13 +2207,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
-        <v>1941.099</v>
-      </c>
-      <c r="C61">
-        <v>2006</v>
+        <v>2861.23</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2284,13 +2221,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
-        <v>1706.851</v>
-      </c>
-      <c r="C62">
-        <v>1817</v>
+        <v>2569.43</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2301,13 +2235,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>1570.593</v>
-      </c>
-      <c r="C63">
-        <v>1681</v>
+        <v>2355.258</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2318,13 +2249,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>1446.983</v>
-      </c>
-      <c r="C64">
-        <v>1514</v>
+        <v>2165.5</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2335,13 +2263,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>1430.74</v>
-      </c>
-      <c r="C65">
-        <v>1355</v>
+        <v>1956.193</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2352,13 +2277,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>1187.067</v>
-      </c>
-      <c r="C66">
-        <v>1127</v>
+        <v>1548.98</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2369,13 +2291,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>1014.184</v>
-      </c>
-      <c r="C67">
-        <v>960</v>
+        <v>1296.726</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2386,13 +2305,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>824.4640000000001</v>
-      </c>
-      <c r="C68">
-        <v>743</v>
+        <v>1026.731</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2403,13 +2319,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>666.095</v>
-      </c>
-      <c r="C69">
-        <v>580</v>
+        <v>798.251</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2420,13 +2333,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>405.28</v>
-      </c>
-      <c r="C70">
-        <v>396</v>
+        <v>453.684</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2437,13 +2347,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>257.392</v>
-      </c>
-      <c r="C71">
-        <v>256</v>
+        <v>285.474</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2454,13 +2361,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
-        <v>161.919</v>
-      </c>
-      <c r="C72">
-        <v>131</v>
+        <v>153.166</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2471,13 +2375,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>93.892</v>
-      </c>
-      <c r="C73">
-        <v>51</v>
+        <v>76.855</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2488,13 +2389,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>32.579</v>
-      </c>
-      <c r="C74">
-        <v>6</v>
+        <v>23.393</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2505,13 +2403,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>65.94199999999999</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
+        <v>20.107</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2522,13 +2417,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>64.666</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
+        <v>57.521</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2539,13 +2431,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
-        <v>63.471</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
+        <v>57.077</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2556,13 +2445,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
-        <v>61.106</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
+        <v>61.16</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2573,13 +2459,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>60.994</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
+        <v>61.26</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2590,13 +2473,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>58.846</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
+        <v>59.26</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2607,13 +2487,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>56.806</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
+        <v>57.26</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2624,13 +2501,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
-        <v>55.178</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
+        <v>49.78</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2641,13 +2515,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>55.17</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2658,13 +2529,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
-        <v>55.162</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
+        <v>48.28</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2675,13 +2543,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>15.562</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
+        <v>45.88</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2692,13 +2557,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>11.26</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2709,13 +2571,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>10.76</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2726,13 +2585,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>10.26</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2743,13 +2599,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2760,13 +2613,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.86</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2777,13 +2627,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
-        <v>4.26</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2794,13 +2641,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
-        <v>3.76</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2811,13 +2655,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
-        <v>2.66</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2828,13 +2669,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.16</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2845,13 +2683,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
-        <v>1.16</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2862,13 +2697,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.16</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2879,13 +2711,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.16</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2896,13 +2725,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>2.08</v>
-      </c>
-      <c r="C98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2913,13 +2739,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>2.08</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2930,13 +2753,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.58</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2947,14 +2767,11 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
         <v>1.08</v>
       </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
       <c r="D101">
         <v>4</v>
       </c>
@@ -2964,14 +2781,11 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
         <v>1.16</v>
       </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
       <c r="D102">
         <v>5</v>
       </c>
@@ -2981,14 +2795,11 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
         <v>1.16</v>
       </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
       <c r="D103">
         <v>6</v>
       </c>
@@ -2998,14 +2809,11 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
         <v>1.16</v>
       </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
       <c r="D104">
         <v>7</v>
       </c>
@@ -3015,14 +2823,11 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
         <v>1.16</v>
       </c>
-      <c r="C105">
-        <v>0</v>
-      </c>
       <c r="D105">
         <v>8</v>
       </c>
@@ -3032,14 +2837,11 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
         <v>1.16</v>
       </c>
-      <c r="C106">
-        <v>0</v>
-      </c>
       <c r="D106">
         <v>9</v>
       </c>
@@ -3049,14 +2851,11 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
         <v>1.16</v>
       </c>
-      <c r="C107">
-        <v>0</v>
-      </c>
       <c r="D107">
         <v>10</v>
       </c>
@@ -3066,14 +2865,11 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
         <v>1.16</v>
       </c>
-      <c r="C108">
-        <v>0</v>
-      </c>
       <c r="D108">
         <v>11</v>
       </c>
@@ -3083,14 +2879,11 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
         <v>1.16</v>
       </c>
-      <c r="C109">
-        <v>0</v>
-      </c>
       <c r="D109">
         <v>12</v>
       </c>
@@ -3100,14 +2893,11 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
         <v>1.08</v>
       </c>
-      <c r="C110">
-        <v>0</v>
-      </c>
       <c r="D110">
         <v>13</v>
       </c>
@@ -3117,14 +2907,11 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
         <v>1.08</v>
       </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
       <c r="D111">
         <v>14</v>
       </c>
@@ -3134,14 +2921,11 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
         <v>1.08</v>
       </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
       <c r="D112">
         <v>15</v>
       </c>
@@ -3151,14 +2935,11 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
         <v>1.08</v>
       </c>
-      <c r="C113">
-        <v>0</v>
-      </c>
       <c r="D113">
         <v>16</v>
       </c>
@@ -3168,13 +2949,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.082</v>
-      </c>
-      <c r="C114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3185,13 +2963,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.082</v>
-      </c>
-      <c r="C115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3202,13 +2977,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>1.09</v>
-      </c>
-      <c r="C116">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3219,13 +2991,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.106</v>
-      </c>
-      <c r="C117">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3236,13 +3005,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.203</v>
-      </c>
-      <c r="C118">
-        <v>0</v>
+        <v>6.136</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3253,13 +3019,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>1.938</v>
-      </c>
-      <c r="C119">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3270,13 +3033,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>3.06</v>
-      </c>
-      <c r="C120">
-        <v>0</v>
+        <v>6.292</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3287,13 +3047,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
-        <v>4.738</v>
-      </c>
-      <c r="C121">
-        <v>0</v>
+        <v>6.518</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3304,13 +3061,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
-        <v>13.807</v>
-      </c>
-      <c r="C122">
-        <v>0</v>
+        <v>34.105</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3321,13 +3075,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>18.466</v>
-      </c>
-      <c r="C123">
-        <v>0</v>
+        <v>38.062</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3338,13 +3089,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>44.213</v>
-      </c>
-      <c r="C124">
-        <v>38</v>
+        <v>71.636</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3355,13 +3103,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>107.316</v>
-      </c>
-      <c r="C125">
-        <v>108</v>
+        <v>170.932</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3372,13 +3117,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>318.476</v>
-      </c>
-      <c r="C126">
-        <v>234</v>
+        <v>473.609</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3389,13 +3131,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>427.509</v>
-      </c>
-      <c r="C127">
-        <v>402</v>
+        <v>663.602</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3406,13 +3145,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>585.152</v>
-      </c>
-      <c r="C128">
-        <v>597</v>
+        <v>914.564</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3423,13 +3159,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
-        <v>740.974</v>
-      </c>
-      <c r="C129">
-        <v>737</v>
+        <v>1123.735</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3440,13 +3173,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>1070.92</v>
-      </c>
-      <c r="C130">
-        <v>926</v>
+        <v>1609.161</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3457,13 +3187,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
-        <v>1217.317</v>
-      </c>
-      <c r="C131">
-        <v>1161</v>
+        <v>1839.916</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3474,13 +3201,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
-        <v>1416.664</v>
-      </c>
-      <c r="C132">
-        <v>1345</v>
+        <v>2097.468</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3491,13 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
-        <v>1588.567</v>
-      </c>
-      <c r="C133">
-        <v>1660</v>
+        <v>2298.652</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3508,13 +3229,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>1852.252</v>
-      </c>
-      <c r="C134">
-        <v>1902</v>
+        <v>2658.818</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3525,13 +3243,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
-        <v>2000.506</v>
-      </c>
-      <c r="C135">
-        <v>2028</v>
+        <v>2784.942</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3542,13 +3257,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
-        <v>2140.575</v>
-      </c>
-      <c r="C136">
-        <v>2186</v>
+        <v>2851.02</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3559,13 +3271,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
-        <v>2261.816</v>
-      </c>
-      <c r="C137">
-        <v>2378</v>
+        <v>2955.481</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3576,13 +3285,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>2496.862</v>
-      </c>
-      <c r="C138">
-        <v>2424</v>
+        <v>3259.556</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3593,13 +3299,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>2563.515</v>
-      </c>
-      <c r="C139">
-        <v>2499</v>
+        <v>3320.168</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3610,13 +3313,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
-        <v>2620.821</v>
-      </c>
-      <c r="C140">
-        <v>2664</v>
+        <v>3395.347</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3627,13 +3327,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
-        <v>2690.248</v>
-      </c>
-      <c r="C141">
-        <v>2544</v>
+        <v>3444.815</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3644,13 +3341,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
-        <v>2763.813</v>
-      </c>
-      <c r="C142">
-        <v>2513</v>
+        <v>3470.931</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3661,13 +3355,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
-        <v>2772.213</v>
-      </c>
-      <c r="C143">
-        <v>2511</v>
+        <v>3504.315</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3678,13 +3369,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>2791.827</v>
-      </c>
-      <c r="C144">
-        <v>2565</v>
+        <v>3520.716</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3695,13 +3383,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
-        <v>2800.643</v>
-      </c>
-      <c r="C145">
-        <v>2613</v>
+        <v>3520.654</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3712,13 +3397,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
-        <v>2772.893</v>
-      </c>
-      <c r="C146">
-        <v>2619</v>
+        <v>3514.954</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3729,13 +3411,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>2730.304</v>
-      </c>
-      <c r="C147">
-        <v>2507</v>
+        <v>3507.644</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3746,13 +3425,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
-        <v>2703.3</v>
-      </c>
-      <c r="C148">
-        <v>2440</v>
+        <v>3481.496</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3763,13 +3439,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>2665.35</v>
-      </c>
-      <c r="C149">
-        <v>2296</v>
+        <v>3439.166</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3780,13 +3453,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>2606.118</v>
-      </c>
-      <c r="C150">
-        <v>2251</v>
+        <v>3397.818</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3797,13 +3467,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>2524.586</v>
-      </c>
-      <c r="C151">
-        <v>2250</v>
+        <v>3344.79</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3814,13 +3481,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
-        <v>2450.729</v>
-      </c>
-      <c r="C152">
-        <v>2250</v>
+        <v>3282.256</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3831,13 +3495,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
-        <v>2371.64</v>
-      </c>
-      <c r="C153">
-        <v>2192</v>
+        <v>3200.154</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3848,13 +3509,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
-        <v>2231.521</v>
-      </c>
-      <c r="C154">
-        <v>2106</v>
+        <v>3059.287</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3865,13 +3523,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
-        <v>2115.857</v>
-      </c>
-      <c r="C155">
-        <v>1939</v>
+        <v>2984.805</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3882,13 +3537,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
-        <v>1990.617</v>
-      </c>
-      <c r="C156">
-        <v>1858</v>
+        <v>2851.775</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3899,13 +3551,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
-        <v>1878.916</v>
-      </c>
-      <c r="C157">
-        <v>1848</v>
+        <v>2711.831</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3916,13 +3565,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
-        <v>1676.271</v>
-      </c>
-      <c r="C158">
-        <v>1652</v>
+        <v>2409.418</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3933,13 +3579,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
-        <v>1523.212</v>
-      </c>
-      <c r="C159">
-        <v>1565</v>
+        <v>2192.687</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3950,13 +3593,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>1379.853</v>
-      </c>
-      <c r="C160">
-        <v>1469</v>
+        <v>1978.295</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3967,13 +3607,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>1226.917</v>
-      </c>
-      <c r="C161">
-        <v>1387</v>
+        <v>1764.303</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3984,13 +3621,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>993.991</v>
-      </c>
-      <c r="C162">
-        <v>1180</v>
+        <v>1419.99</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4001,13 +3635,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>834.131</v>
-      </c>
-      <c r="C163">
-        <v>958</v>
+        <v>1185.241</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4018,13 +3649,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>682.703</v>
-      </c>
-      <c r="C164">
-        <v>762</v>
+        <v>927.716</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4035,13 +3663,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>545.025</v>
-      </c>
-      <c r="C165">
-        <v>619</v>
+        <v>728.037</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4052,13 +3677,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>312.749</v>
-      </c>
-      <c r="C166">
-        <v>440</v>
+        <v>396.721</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4069,13 +3691,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>209.529</v>
-      </c>
-      <c r="C167">
-        <v>294</v>
+        <v>259.521</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4086,13 +3705,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>131.847</v>
-      </c>
-      <c r="C168">
-        <v>141</v>
+        <v>136.901</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4103,13 +3719,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
-        <v>68.044</v>
-      </c>
-      <c r="C169">
-        <v>48</v>
+        <v>73.70699999999999</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4120,13 +3733,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
-        <v>65.90300000000001</v>
-      </c>
-      <c r="C170">
-        <v>9</v>
+        <v>28.821</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4137,13 +3747,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
-        <v>68.39100000000001</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
+        <v>77.455</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4154,13 +3761,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
-        <v>67.877</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
+        <v>77.685</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4171,13 +3775,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
-        <v>67.02800000000001</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
+        <v>77.53400000000001</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4188,13 +3789,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
-        <v>66.31999999999999</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4205,13 +3803,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>66.256</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
+        <v>76.86</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4222,13 +3817,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
-        <v>65.904</v>
-      </c>
-      <c r="C176">
-        <v>0</v>
+        <v>74.66</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4239,13 +3831,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>61.24</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
+        <v>72.86</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4256,13 +3845,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>52.875</v>
-      </c>
-      <c r="C178">
-        <v>0</v>
+        <v>67.58</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4273,13 +3859,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>14.189</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
+        <v>16.58</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4290,13 +3873,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>12.281</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4307,13 +3887,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>10.181</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
+        <v>13.652</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4324,13 +3901,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>4.082</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
+        <v>12.88</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4341,13 +3915,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>9.481999999999999</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
+        <v>12.08</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4358,13 +3929,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>9.282</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
+        <v>10.88</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4375,13 +3943,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
-        <v>8.782</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4392,13 +3957,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>3.18</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4409,13 +3971,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>2.88</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4426,13 +3985,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>2.38</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4443,13 +3999,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
-        <v>2.28</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4460,14 +4013,11 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
         <v>1.08</v>
       </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
       <c r="D190">
         <v>93</v>
       </c>
@@ -4477,14 +4027,11 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
         <v>1.08</v>
       </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
       <c r="D191">
         <v>94</v>
       </c>
@@ -4494,14 +4041,11 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
         <v>1.08</v>
       </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
       <c r="D192">
         <v>95</v>
       </c>
@@ -4511,13 +4055,10 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>1.08</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
+        <v>1.084</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4528,13 +4069,10 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>2.08</v>
-      </c>
-      <c r="C194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4545,13 +4083,10 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
-        <v>2.08</v>
-      </c>
-      <c r="C195">
-        <v>0</v>
+        <v>1.884</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4562,13 +4097,10 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
-        <v>2.08</v>
-      </c>
-      <c r="C196">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4579,13 +4111,10 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
-        <v>2.08</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4596,13 +4125,10 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>2.16</v>
-      </c>
-      <c r="C198">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4613,13 +4139,10 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>2.16</v>
-      </c>
-      <c r="C199">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D199">
         <v>6</v>
@@ -4630,13 +4153,10 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>2.16</v>
-      </c>
-      <c r="C200">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D200">
         <v>7</v>
@@ -4647,13 +4167,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>2.16</v>
-      </c>
-      <c r="C201">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4664,13 +4181,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>2.16</v>
-      </c>
-      <c r="C202">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -4681,13 +4195,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>2.16</v>
-      </c>
-      <c r="C203">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D203">
         <v>10</v>
@@ -4698,13 +4209,10 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>2.16</v>
-      </c>
-      <c r="C204">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D204">
         <v>11</v>
@@ -4715,13 +4223,10 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>2.16</v>
-      </c>
-      <c r="C205">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -4732,14 +4237,11 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
         <v>1.08</v>
       </c>
-      <c r="C206">
-        <v>0</v>
-      </c>
       <c r="D206">
         <v>13</v>
       </c>
@@ -4749,14 +4251,11 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
         <v>1.08</v>
       </c>
-      <c r="C207">
-        <v>0</v>
-      </c>
       <c r="D207">
         <v>14</v>
       </c>
@@ -4766,13 +4265,10 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>2.08</v>
-      </c>
-      <c r="C208">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -4783,14 +4279,11 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
         <v>1.08</v>
       </c>
-      <c r="C209">
-        <v>0</v>
-      </c>
       <c r="D209">
         <v>16</v>
       </c>
@@ -4800,14 +4293,11 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
         <v>1.08</v>
       </c>
-      <c r="C210">
-        <v>0</v>
-      </c>
       <c r="D210">
         <v>17</v>
       </c>
@@ -4817,14 +4307,11 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
         <v>1.08</v>
       </c>
-      <c r="C211">
-        <v>0</v>
-      </c>
       <c r="D211">
         <v>18</v>
       </c>
@@ -4834,13 +4321,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>1.088</v>
-      </c>
-      <c r="C212">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -4851,13 +4335,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>1.104</v>
-      </c>
-      <c r="C213">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -4868,13 +4349,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>1.222</v>
-      </c>
-      <c r="C214">
-        <v>0</v>
+        <v>3.683</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4885,13 +4363,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>1.342</v>
-      </c>
-      <c r="C215">
-        <v>0</v>
+        <v>3.759</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4902,13 +4377,10 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>1.454</v>
-      </c>
-      <c r="C216">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4919,13 +4391,10 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>1.607</v>
-      </c>
-      <c r="C217">
-        <v>0</v>
+        <v>3.952</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4936,13 +4405,10 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>13.429</v>
-      </c>
-      <c r="C218">
-        <v>0</v>
+        <v>12.494</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4953,13 +4419,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>19.176</v>
-      </c>
-      <c r="C219">
-        <v>5</v>
+        <v>15.905</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4970,13 +4433,10 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>57.782</v>
-      </c>
-      <c r="C220">
-        <v>56</v>
+        <v>52.686</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4987,13 +4447,10 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>146.852</v>
-      </c>
-      <c r="C221">
-        <v>161</v>
+        <v>142.407</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5004,13 +4461,10 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>456.106</v>
-      </c>
-      <c r="C222">
-        <v>325</v>
+        <v>405.441</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5021,13 +4475,10 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>630.788</v>
-      </c>
-      <c r="C223">
-        <v>523</v>
+        <v>607.095</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5038,13 +4489,10 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>895.01</v>
-      </c>
-      <c r="C224">
-        <v>743</v>
+        <v>818.942</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5055,13 +4503,10 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>1151.509</v>
-      </c>
-      <c r="C225">
-        <v>963</v>
+        <v>1093.388</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5072,13 +4517,10 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>1585.826</v>
-      </c>
-      <c r="C226">
-        <v>1223</v>
+        <v>1464.961</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5089,13 +4531,10 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B227">
-        <v>1813.448</v>
-      </c>
-      <c r="C227">
-        <v>1475</v>
+        <v>1709.586</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5106,13 +4545,10 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B228">
-        <v>2063.628</v>
-      </c>
-      <c r="C228">
-        <v>1661</v>
+        <v>1983.527</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5123,13 +4559,10 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B229">
-        <v>2289.755</v>
-      </c>
-      <c r="C229">
-        <v>1895</v>
+        <v>2201.657</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5140,13 +4573,10 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B230">
-        <v>2687.266</v>
-      </c>
-      <c r="C230">
-        <v>2128</v>
+        <v>2551.623</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5157,13 +4587,10 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B231">
-        <v>2830.778</v>
-      </c>
-      <c r="C231">
-        <v>2348</v>
+        <v>2715.187</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5174,13 +4601,10 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B232">
-        <v>2977.207</v>
-      </c>
-      <c r="C232">
-        <v>2468</v>
+        <v>2861.44</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5191,10 +4615,10 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B233">
-        <v>3103.374</v>
+        <v>2987.487</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5205,10 +4629,10 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B234">
-        <v>3262.909</v>
+        <v>3151.942</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5219,10 +4643,10 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B235">
-        <v>3349.309</v>
+        <v>3240.309</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5233,10 +4657,10 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B236">
-        <v>3413.734</v>
+        <v>3310.706</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5247,10 +4671,10 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B237">
-        <v>3471.937</v>
+        <v>3366.296</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5261,10 +4685,10 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B238">
-        <v>3509.55</v>
+        <v>3374.007</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5275,10 +4699,10 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B239">
-        <v>3539.383</v>
+        <v>3393.886</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5289,10 +4713,10 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B240">
-        <v>3560.622</v>
+        <v>3411.223</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5303,10 +4727,10 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B241">
-        <v>3574.442</v>
+        <v>3416.168</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5317,10 +4741,10 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B242">
-        <v>3568.444</v>
+        <v>3451.039</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5331,10 +4755,10 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B243">
-        <v>3564.931</v>
+        <v>3433.668</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5345,10 +4769,10 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B244">
-        <v>3553.282</v>
+        <v>3420.693</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5359,10 +4783,10 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B245">
-        <v>3535.308</v>
+        <v>3399.492</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5373,10 +4797,10 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B246">
-        <v>3494.304</v>
+        <v>3355.819</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5387,10 +4811,10 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B247">
-        <v>3462.053</v>
+        <v>3310.072</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5401,10 +4825,10 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B248">
-        <v>3409.963</v>
+        <v>3251.246</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5415,10 +4839,10 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B249">
-        <v>3353.559</v>
+        <v>3193.931</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5429,10 +4853,10 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B250">
-        <v>3224.779</v>
+        <v>3082.772</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5443,10 +4867,10 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B251">
-        <v>3136.936</v>
+        <v>2987.186</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5457,10 +4881,10 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B252">
-        <v>3035.398</v>
+        <v>2864.465</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5471,10 +4895,10 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B253">
-        <v>2893.48</v>
+        <v>2736.522</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5485,10 +4909,10 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B254">
-        <v>2621.13</v>
+        <v>2494.313</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5499,10 +4923,10 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B255">
-        <v>2430.702</v>
+        <v>2308.932</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5513,10 +4937,10 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B256">
-        <v>2225.928</v>
+        <v>2082.994</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5527,10 +4951,10 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B257">
-        <v>2006.891</v>
+        <v>1867.71</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5541,10 +4965,10 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B258">
-        <v>1617.702</v>
+        <v>1460.85</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5555,10 +4979,10 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B259">
-        <v>1365.998</v>
+        <v>1211.642</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5569,10 +4993,10 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B260">
-        <v>1092.291</v>
+        <v>941.423</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5583,10 +5007,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B261">
-        <v>838.862</v>
+        <v>711.698</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5597,10 +5021,10 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B262">
-        <v>481.849</v>
+        <v>409.568</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5611,10 +5035,10 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B263">
-        <v>307.929</v>
+        <v>249.426</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5625,10 +5049,10 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B264">
-        <v>170.101</v>
+        <v>134.19</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5639,10 +5063,10 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B265">
-        <v>92.40000000000001</v>
+        <v>65.28100000000001</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5653,10 +5077,10 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B266">
-        <v>22.545</v>
+        <v>17.138</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5667,10 +5091,10 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B267">
-        <v>19.845</v>
+        <v>21.39</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5681,10 +5105,10 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B268">
-        <v>19.387</v>
+        <v>70.249</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5695,10 +5119,10 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B269">
-        <v>18.661</v>
+        <v>73.105</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5709,10 +5133,10 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B270">
-        <v>17.924</v>
+        <v>69.982</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5723,10 +5147,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B271">
-        <v>17.76</v>
+        <v>70.88200000000001</v>
       </c>
       <c r="D271">
         <v>78</v>
@@ -5737,10 +5161,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B272">
-        <v>15.708</v>
+        <v>68.268</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -5751,10 +5175,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B273">
-        <v>13.844</v>
+        <v>67.724</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -5765,10 +5189,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B274">
-        <v>12.708</v>
+        <v>60.584</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -5779,10 +5203,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B275">
-        <v>11.788</v>
+        <v>60.084</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -5793,10 +5217,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B276">
-        <v>10.78</v>
+        <v>12.484</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -5807,10 +5231,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B277">
-        <v>7.98</v>
+        <v>8.984</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -5821,10 +5245,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B278">
-        <v>6.78</v>
+        <v>5.884</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -5835,10 +5259,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B279">
-        <v>6.08</v>
+        <v>5.584</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -5849,10 +5273,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B280">
-        <v>5.08</v>
+        <v>5.38</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -5863,10 +5287,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B281">
-        <v>2.98</v>
+        <v>5.08</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -5877,10 +5301,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B282">
-        <v>5.482</v>
+        <v>4.98</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -5891,10 +5315,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B283">
-        <v>3.482</v>
+        <v>4.18</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -5905,10 +5329,10 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B284">
-        <v>2.582</v>
+        <v>3.58</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -5919,10 +5343,10 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B285">
-        <v>1.482</v>
+        <v>3.48</v>
       </c>
       <c r="D285">
         <v>92</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,582 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>01.10.20261</t>
-  </si>
-  <si>
-    <t>01.10.20262</t>
-  </si>
-  <si>
-    <t>01.10.20263</t>
-  </si>
-  <si>
-    <t>01.10.20264</t>
-  </si>
-  <si>
-    <t>01.10.20265</t>
-  </si>
-  <si>
-    <t>01.10.20266</t>
-  </si>
-  <si>
-    <t>01.10.20267</t>
-  </si>
-  <si>
-    <t>01.10.20268</t>
-  </si>
-  <si>
-    <t>01.10.20269</t>
-  </si>
-  <si>
-    <t>01.10.202610</t>
-  </si>
-  <si>
-    <t>01.10.202611</t>
-  </si>
-  <si>
-    <t>01.10.202612</t>
-  </si>
-  <si>
-    <t>01.10.202613</t>
-  </si>
-  <si>
-    <t>01.10.202614</t>
-  </si>
-  <si>
-    <t>01.10.202615</t>
-  </si>
-  <si>
-    <t>01.10.202616</t>
-  </si>
-  <si>
-    <t>01.10.202617</t>
-  </si>
-  <si>
-    <t>01.10.202618</t>
-  </si>
-  <si>
-    <t>01.10.202619</t>
-  </si>
-  <si>
-    <t>01.10.202620</t>
-  </si>
-  <si>
-    <t>01.10.202621</t>
-  </si>
-  <si>
-    <t>01.10.202622</t>
-  </si>
-  <si>
-    <t>01.10.202623</t>
-  </si>
-  <si>
-    <t>01.10.202624</t>
-  </si>
-  <si>
-    <t>01.10.202625</t>
-  </si>
-  <si>
-    <t>01.10.202626</t>
-  </si>
-  <si>
-    <t>01.10.202627</t>
-  </si>
-  <si>
-    <t>01.10.202628</t>
-  </si>
-  <si>
-    <t>01.10.202629</t>
-  </si>
-  <si>
-    <t>01.10.202630</t>
-  </si>
-  <si>
-    <t>01.10.202631</t>
-  </si>
-  <si>
-    <t>01.10.202632</t>
-  </si>
-  <si>
-    <t>01.10.202633</t>
-  </si>
-  <si>
-    <t>01.10.202634</t>
-  </si>
-  <si>
-    <t>01.10.202635</t>
-  </si>
-  <si>
-    <t>01.10.202636</t>
-  </si>
-  <si>
-    <t>01.10.202637</t>
-  </si>
-  <si>
-    <t>01.10.202638</t>
-  </si>
-  <si>
-    <t>01.10.202639</t>
-  </si>
-  <si>
-    <t>01.10.202640</t>
-  </si>
-  <si>
-    <t>01.10.202641</t>
-  </si>
-  <si>
-    <t>01.10.202642</t>
-  </si>
-  <si>
-    <t>01.10.202643</t>
-  </si>
-  <si>
-    <t>01.10.202644</t>
-  </si>
-  <si>
-    <t>01.10.202645</t>
-  </si>
-  <si>
-    <t>01.10.202646</t>
-  </si>
-  <si>
-    <t>01.10.202647</t>
-  </si>
-  <si>
-    <t>01.10.202648</t>
-  </si>
-  <si>
-    <t>01.10.202649</t>
-  </si>
-  <si>
-    <t>01.10.202650</t>
-  </si>
-  <si>
-    <t>01.10.202651</t>
-  </si>
-  <si>
-    <t>01.10.202652</t>
-  </si>
-  <si>
-    <t>01.10.202653</t>
-  </si>
-  <si>
-    <t>01.10.202654</t>
-  </si>
-  <si>
-    <t>01.10.202655</t>
-  </si>
-  <si>
-    <t>01.10.202656</t>
-  </si>
-  <si>
-    <t>01.10.202657</t>
-  </si>
-  <si>
-    <t>01.10.202658</t>
-  </si>
-  <si>
-    <t>01.10.202659</t>
-  </si>
-  <si>
-    <t>01.10.202660</t>
-  </si>
-  <si>
-    <t>01.10.202661</t>
-  </si>
-  <si>
-    <t>01.10.202662</t>
-  </si>
-  <si>
-    <t>01.10.202663</t>
-  </si>
-  <si>
-    <t>01.10.202664</t>
-  </si>
-  <si>
-    <t>01.10.202665</t>
-  </si>
-  <si>
-    <t>01.10.202666</t>
-  </si>
-  <si>
-    <t>01.10.202667</t>
-  </si>
-  <si>
-    <t>01.10.202668</t>
-  </si>
-  <si>
-    <t>01.10.202669</t>
-  </si>
-  <si>
-    <t>01.10.202670</t>
-  </si>
-  <si>
-    <t>01.10.202671</t>
-  </si>
-  <si>
-    <t>01.10.202672</t>
-  </si>
-  <si>
-    <t>01.10.202673</t>
-  </si>
-  <si>
-    <t>01.10.202674</t>
-  </si>
-  <si>
-    <t>01.10.202675</t>
-  </si>
-  <si>
-    <t>01.10.202676</t>
-  </si>
-  <si>
-    <t>01.10.202677</t>
-  </si>
-  <si>
-    <t>01.10.202678</t>
-  </si>
-  <si>
-    <t>01.10.202679</t>
-  </si>
-  <si>
-    <t>01.10.202680</t>
-  </si>
-  <si>
-    <t>01.10.202681</t>
-  </si>
-  <si>
-    <t>01.10.202682</t>
-  </si>
-  <si>
-    <t>01.10.202683</t>
-  </si>
-  <si>
-    <t>01.10.202684</t>
-  </si>
-  <si>
-    <t>01.10.202685</t>
-  </si>
-  <si>
-    <t>01.10.202686</t>
-  </si>
-  <si>
-    <t>01.10.202687</t>
-  </si>
-  <si>
-    <t>01.10.202688</t>
-  </si>
-  <si>
-    <t>01.10.202689</t>
-  </si>
-  <si>
-    <t>01.10.202690</t>
-  </si>
-  <si>
-    <t>01.10.202691</t>
-  </si>
-  <si>
-    <t>01.10.202692</t>
-  </si>
-  <si>
-    <t>01.10.202693</t>
-  </si>
-  <si>
-    <t>01.10.202694</t>
-  </si>
-  <si>
-    <t>01.10.202695</t>
-  </si>
-  <si>
-    <t>01.10.202696</t>
-  </si>
-  <si>
-    <t>02.10.20261</t>
-  </si>
-  <si>
-    <t>02.10.20262</t>
-  </si>
-  <si>
-    <t>02.10.20263</t>
-  </si>
-  <si>
-    <t>02.10.20264</t>
-  </si>
-  <si>
-    <t>02.10.20265</t>
-  </si>
-  <si>
-    <t>02.10.20266</t>
-  </si>
-  <si>
-    <t>02.10.20267</t>
-  </si>
-  <si>
-    <t>02.10.20268</t>
-  </si>
-  <si>
-    <t>02.10.20269</t>
-  </si>
-  <si>
-    <t>02.10.202610</t>
-  </si>
-  <si>
-    <t>02.10.202611</t>
-  </si>
-  <si>
-    <t>02.10.202612</t>
-  </si>
-  <si>
-    <t>02.10.202613</t>
-  </si>
-  <si>
-    <t>02.10.202614</t>
-  </si>
-  <si>
-    <t>02.10.202615</t>
-  </si>
-  <si>
-    <t>02.10.202616</t>
-  </si>
-  <si>
-    <t>02.10.202617</t>
-  </si>
-  <si>
-    <t>02.10.202618</t>
-  </si>
-  <si>
-    <t>02.10.202619</t>
-  </si>
-  <si>
-    <t>02.10.202620</t>
-  </si>
-  <si>
-    <t>02.10.202621</t>
-  </si>
-  <si>
-    <t>02.10.202622</t>
-  </si>
-  <si>
-    <t>02.10.202623</t>
-  </si>
-  <si>
-    <t>02.10.202624</t>
-  </si>
-  <si>
-    <t>02.10.202625</t>
-  </si>
-  <si>
-    <t>02.10.202626</t>
-  </si>
-  <si>
-    <t>02.10.202627</t>
-  </si>
-  <si>
-    <t>02.10.202628</t>
-  </si>
-  <si>
-    <t>02.10.202629</t>
-  </si>
-  <si>
-    <t>02.10.202630</t>
-  </si>
-  <si>
-    <t>02.10.202631</t>
-  </si>
-  <si>
-    <t>02.10.202632</t>
-  </si>
-  <si>
-    <t>02.10.202633</t>
-  </si>
-  <si>
-    <t>02.10.202634</t>
-  </si>
-  <si>
-    <t>02.10.202635</t>
-  </si>
-  <si>
-    <t>02.10.202636</t>
-  </si>
-  <si>
-    <t>02.10.202637</t>
-  </si>
-  <si>
-    <t>02.10.202638</t>
-  </si>
-  <si>
-    <t>02.10.202639</t>
-  </si>
-  <si>
-    <t>02.10.202640</t>
-  </si>
-  <si>
-    <t>02.10.202641</t>
-  </si>
-  <si>
-    <t>02.10.202642</t>
-  </si>
-  <si>
-    <t>02.10.202643</t>
-  </si>
-  <si>
-    <t>02.10.202644</t>
-  </si>
-  <si>
-    <t>02.10.202645</t>
-  </si>
-  <si>
-    <t>02.10.202646</t>
-  </si>
-  <si>
-    <t>02.10.202647</t>
-  </si>
-  <si>
-    <t>02.10.202648</t>
-  </si>
-  <si>
-    <t>02.10.202649</t>
-  </si>
-  <si>
-    <t>02.10.202650</t>
-  </si>
-  <si>
-    <t>02.10.202651</t>
-  </si>
-  <si>
-    <t>02.10.202652</t>
-  </si>
-  <si>
-    <t>02.10.202653</t>
-  </si>
-  <si>
-    <t>02.10.202654</t>
-  </si>
-  <si>
-    <t>02.10.202655</t>
-  </si>
-  <si>
-    <t>02.10.202656</t>
-  </si>
-  <si>
-    <t>02.10.202657</t>
-  </si>
-  <si>
-    <t>02.10.202658</t>
-  </si>
-  <si>
-    <t>02.10.202659</t>
-  </si>
-  <si>
-    <t>02.10.202660</t>
-  </si>
-  <si>
-    <t>02.10.202661</t>
-  </si>
-  <si>
-    <t>02.10.202662</t>
-  </si>
-  <si>
-    <t>02.10.202663</t>
-  </si>
-  <si>
-    <t>02.10.202664</t>
-  </si>
-  <si>
-    <t>02.10.202665</t>
-  </si>
-  <si>
-    <t>02.10.202666</t>
-  </si>
-  <si>
-    <t>02.10.202667</t>
-  </si>
-  <si>
-    <t>02.10.202668</t>
-  </si>
-  <si>
-    <t>02.10.202669</t>
-  </si>
-  <si>
-    <t>02.10.202670</t>
-  </si>
-  <si>
-    <t>02.10.202671</t>
-  </si>
-  <si>
-    <t>02.10.202672</t>
-  </si>
-  <si>
-    <t>02.10.202673</t>
-  </si>
-  <si>
-    <t>02.10.202674</t>
-  </si>
-  <si>
-    <t>02.10.202675</t>
-  </si>
-  <si>
-    <t>02.10.202676</t>
-  </si>
-  <si>
-    <t>02.10.202677</t>
-  </si>
-  <si>
-    <t>02.10.202678</t>
-  </si>
-  <si>
-    <t>02.10.202679</t>
-  </si>
-  <si>
-    <t>02.10.202680</t>
-  </si>
-  <si>
-    <t>02.10.202681</t>
-  </si>
-  <si>
-    <t>02.10.202682</t>
-  </si>
-  <si>
-    <t>02.10.202683</t>
-  </si>
-  <si>
-    <t>02.10.202684</t>
-  </si>
-  <si>
-    <t>02.10.202685</t>
-  </si>
-  <si>
-    <t>02.10.202686</t>
-  </si>
-  <si>
-    <t>02.10.202687</t>
-  </si>
-  <si>
-    <t>02.10.202688</t>
-  </si>
-  <si>
-    <t>02.10.202689</t>
-  </si>
-  <si>
-    <t>02.10.202690</t>
-  </si>
-  <si>
-    <t>02.10.202691</t>
-  </si>
-  <si>
-    <t>02.10.202692</t>
-  </si>
-  <si>
-    <t>02.10.202693</t>
-  </si>
-  <si>
-    <t>02.10.202694</t>
-  </si>
-  <si>
-    <t>02.10.202695</t>
-  </si>
-  <si>
-    <t>02.10.202696</t>
-  </si>
-  <si>
     <t>03.10.20261</t>
   </si>
   <si>
@@ -881,6 +305,291 @@
   </si>
   <si>
     <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1264,13 +973,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>1.524</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1281,13 +987,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46296.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.026</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+        <v>1.884</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1298,13 +1001,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46296.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>2.926</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1315,13 +1015,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46296.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>3.841</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1332,13 +1029,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46296.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>5.014</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1349,13 +1043,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46296.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>6.142</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1366,13 +1057,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46296.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>7.104</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1383,13 +1071,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46296.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>7.976</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1400,13 +1085,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46296.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1417,13 +1099,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46296.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>9.441000000000001</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1434,13 +1113,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46296.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>10.427</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1451,13 +1127,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46296.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>11.119</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1468,13 +1141,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46296.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>11.662</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1485,13 +1155,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46296.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>12.161</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1502,13 +1169,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46296.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>12.954</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1519,13 +1183,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46296.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>13.329</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1536,13 +1197,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46296.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>13.608</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1553,13 +1211,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46296.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>13.811</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1570,13 +1225,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46296.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>14.133</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1587,13 +1239,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46296.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>14.31</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1604,13 +1253,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46296.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>16.512</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
+        <v>3.683</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1621,13 +1267,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46296.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>17.177</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
+        <v>3.759</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1638,13 +1281,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46296.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>18.228</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1655,13 +1295,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46296.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>19.823</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
+        <v>3.952</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1672,13 +1309,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46296.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>31.557</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
+        <v>12.494</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1689,13 +1323,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46296.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>41.306</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
+        <v>15.905</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1337,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46296.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>82.729</v>
-      </c>
-      <c r="C28">
-        <v>57</v>
+        <v>52.686</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1351,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46296.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>191.031</v>
-      </c>
-      <c r="C29">
-        <v>179</v>
+        <v>142.407</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1365,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46296.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>500.657</v>
-      </c>
-      <c r="C30">
-        <v>384</v>
+        <v>405.441</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1379,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46296.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>698.106</v>
-      </c>
-      <c r="C31">
-        <v>638</v>
+        <v>607.095</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1393,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46296.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>935.159</v>
-      </c>
-      <c r="C32">
-        <v>893</v>
+        <v>818.942</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1407,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46296.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>1178.19</v>
-      </c>
-      <c r="C33">
-        <v>1169</v>
+        <v>1093.388</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1421,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46296.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>1649.822</v>
-      </c>
-      <c r="C34">
-        <v>1457</v>
+        <v>1464.961</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1435,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46296.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>1886.309</v>
-      </c>
-      <c r="C35">
-        <v>1694</v>
+        <v>1709.586</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1449,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46296.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>2140.146</v>
-      </c>
-      <c r="C36">
-        <v>1918</v>
+        <v>1983.527</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1463,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46296.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>2379.496</v>
-      </c>
-      <c r="C37">
-        <v>2203</v>
+        <v>2201.657</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1477,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46296.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>2730.372</v>
-      </c>
-      <c r="C38">
-        <v>2384</v>
+        <v>2551.623</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1491,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46296.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>2901.825</v>
-      </c>
-      <c r="C39">
-        <v>2543</v>
+        <v>2715.187</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1505,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46296.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>3044.233</v>
-      </c>
-      <c r="C40">
-        <v>2654</v>
+        <v>2861.44</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,10 +1519,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46296.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>3173.534</v>
+        <v>2987.487</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1941,10 +1533,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46296.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>3360.243</v>
+        <v>3151.942</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1955,10 +1547,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46296.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>3421.542</v>
+        <v>3240.309</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1969,10 +1561,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46296.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>3491.074</v>
+        <v>3310.706</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1983,10 +1575,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46296.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>3537.677</v>
+        <v>3366.296</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1997,10 +1589,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46296.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>3584.559</v>
+        <v>3374.007</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2011,10 +1603,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46296.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>3615.223</v>
+        <v>3393.886</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2025,10 +1617,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46296.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>3628.19</v>
+        <v>3411.223</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2039,10 +1631,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46296.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>3633.948</v>
+        <v>3416.168</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2053,10 +1645,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46296.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>3627.517</v>
+        <v>3451.039</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2067,10 +1659,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46296.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>3609.923</v>
+        <v>3433.668</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2081,10 +1673,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46296.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>3593.857</v>
+        <v>3420.693</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2095,10 +1687,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46296.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>3563.442</v>
+        <v>3399.492</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2109,10 +1701,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46296.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>3509.612</v>
+        <v>3355.819</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2123,10 +1715,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46296.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>3449.203</v>
+        <v>3310.072</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2137,10 +1729,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46296.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>3399.665</v>
+        <v>3251.246</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2151,10 +1743,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46296.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>3329.072</v>
+        <v>3193.931</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2165,10 +1757,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46296.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>3191.232</v>
+        <v>3082.772</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2179,10 +1771,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46296.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>3125.983</v>
+        <v>2987.186</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2193,10 +1785,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46296.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>2988.628</v>
+        <v>2864.465</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2207,10 +1799,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46296.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>2861.23</v>
+        <v>2736.522</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2221,10 +1813,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46296.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>2569.43</v>
+        <v>2494.313</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2235,10 +1827,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46296.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>2355.258</v>
+        <v>2308.932</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2249,10 +1841,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46296.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>2165.5</v>
+        <v>2082.994</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2263,10 +1855,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46296.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>1956.193</v>
+        <v>1867.71</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2277,10 +1869,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46296.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>1548.98</v>
+        <v>1460.85</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2291,10 +1883,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46296.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>1296.726</v>
+        <v>1211.642</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2305,10 +1897,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46296.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>1026.731</v>
+        <v>941.423</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2319,10 +1911,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46296.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>798.251</v>
+        <v>711.698</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2333,10 +1925,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46296.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>453.684</v>
+        <v>409.568</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2347,10 +1939,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46296.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>285.474</v>
+        <v>249.426</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2361,10 +1953,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46296.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>153.166</v>
+        <v>134.19</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2375,10 +1967,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46296.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>76.855</v>
+        <v>65.28100000000001</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2389,10 +1981,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46296.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>23.393</v>
+        <v>17.138</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2403,10 +1995,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46296.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>20.107</v>
+        <v>21.39</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2417,10 +2009,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46296.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>57.521</v>
+        <v>70.249</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2431,10 +2023,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46296.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>57.077</v>
+        <v>73.105</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2445,10 +2037,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46296.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>61.16</v>
+        <v>69.982</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2459,10 +2051,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46296.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>61.26</v>
+        <v>70.88200000000001</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2473,10 +2065,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46296.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>59.26</v>
+        <v>68.268</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2487,10 +2079,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46296.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>57.26</v>
+        <v>67.724</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2501,10 +2093,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46296.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>49.78</v>
+        <v>60.584</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2515,10 +2107,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46296.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>48.48</v>
+        <v>60.084</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2529,10 +2121,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46296.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>48.28</v>
+        <v>12.484</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2543,10 +2135,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46296.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>45.88</v>
+        <v>8.984</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2557,10 +2149,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46296.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>7.58</v>
+        <v>5.884</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2571,10 +2163,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46296.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.38</v>
+        <v>5.584</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2585,10 +2177,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46296.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>4.68</v>
+        <v>5.38</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2599,10 +2191,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46296.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>3.48</v>
+        <v>5.08</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2613,10 +2205,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46296.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.48</v>
+        <v>4.98</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2627,10 +2219,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46296.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>3.58</v>
+        <v>4.18</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2641,10 +2233,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46296.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>3.38</v>
+        <v>3.58</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2655,10 +2247,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46296.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2669,7 +2261,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46296.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B94">
         <v>1.08</v>
@@ -2683,7 +2275,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46296.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B95">
         <v>1.08</v>
@@ -2697,7 +2289,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46296.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B96">
         <v>1.08</v>
@@ -2711,10 +2303,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46296.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.08</v>
+        <v>1.084</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2725,10 +2317,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B98">
-        <v>1.08</v>
+        <v>1.78</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2739,10 +2331,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46297.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.08</v>
+        <v>1.084</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2753,7 +2345,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46297.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B100">
         <v>1.08</v>
@@ -2767,7 +2359,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46297.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B101">
         <v>1.08</v>
@@ -2781,7 +2373,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46297.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B102">
         <v>1.16</v>
@@ -2795,7 +2387,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46297.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B103">
         <v>1.16</v>
@@ -2809,7 +2401,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46297.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B104">
         <v>1.16</v>
@@ -2823,7 +2415,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46297.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B105">
         <v>1.16</v>
@@ -2837,7 +2429,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46297.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B106">
         <v>1.16</v>
@@ -2851,7 +2443,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46297.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B107">
         <v>1.16</v>
@@ -2865,7 +2457,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46297.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B108">
         <v>1.16</v>
@@ -2879,7 +2471,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46297.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B109">
         <v>1.16</v>
@@ -2893,7 +2485,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46297.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B110">
         <v>1.08</v>
@@ -2907,7 +2499,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46297.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B111">
         <v>1.08</v>
@@ -2921,7 +2513,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46297.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B112">
         <v>1.08</v>
@@ -2935,7 +2527,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46297.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B113">
         <v>1.08</v>
@@ -2949,7 +2541,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46297.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B114">
         <v>1.08</v>
@@ -2963,7 +2555,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46297.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B115">
         <v>1.08</v>
@@ -2977,7 +2569,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46297.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B116">
         <v>1.08</v>
@@ -2991,7 +2583,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46297.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B117">
         <v>1.08</v>
@@ -3005,10 +2597,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46297.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>6.136</v>
+        <v>2.679</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3019,10 +2611,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46297.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>6.2</v>
+        <v>2.795</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3033,10 +2625,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46297.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>6.292</v>
+        <v>2.898</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3047,10 +2639,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46297.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>6.518</v>
+        <v>3.065</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3061,10 +2653,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46297.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>34.105</v>
+        <v>12.095</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3075,10 +2667,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46297.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>38.062</v>
+        <v>14.951</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3089,10 +2681,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46297.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>71.636</v>
+        <v>41.999</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3103,10 +2695,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46297.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>170.932</v>
+        <v>130.165</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3117,10 +2709,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46297.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>473.609</v>
+        <v>415.901</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3131,10 +2723,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46297.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>663.602</v>
+        <v>624.016</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3145,10 +2737,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46297.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>914.564</v>
+        <v>838.8920000000001</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3159,10 +2751,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46297.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>1123.735</v>
+        <v>1069.664</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3173,10 +2765,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46297.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>1609.161</v>
+        <v>1504.16</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3187,10 +2779,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46297.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>1839.916</v>
+        <v>1749.545</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3201,10 +2793,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46297.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>2097.468</v>
+        <v>2000.739</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +2807,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46297.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>2298.652</v>
+        <v>2223.396</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3229,10 +2821,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46297.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>2658.818</v>
+        <v>2576.91</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3243,10 +2835,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46297.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>2784.942</v>
+        <v>2739.877</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3257,10 +2849,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46297.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>2851.02</v>
+        <v>2890.956</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,10 +2863,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46297.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>2955.481</v>
+        <v>2990.111</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3285,10 +2877,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46297.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>3259.556</v>
+        <v>3170.235</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3299,10 +2891,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46297.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>3320.168</v>
+        <v>3253.768</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3313,10 +2905,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46297.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>3395.347</v>
+        <v>3318.067</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3327,10 +2919,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46297.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>3444.815</v>
+        <v>3319.086</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3341,10 +2933,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46297.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>3470.931</v>
+        <v>3376.091</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3355,10 +2947,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46297.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>3504.315</v>
+        <v>3371.73</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3369,10 +2961,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46297.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>3520.716</v>
+        <v>3395.102</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3383,10 +2975,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46297.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>3520.654</v>
+        <v>3386.406</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3397,10 +2989,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46297.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>3514.954</v>
+        <v>3387.84</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3411,10 +3003,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46297.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>3507.644</v>
+        <v>3377.45</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3425,10 +3017,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46297.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>3481.496</v>
+        <v>3360.19</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3439,10 +3031,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46297.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>3439.166</v>
+        <v>3330.88</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3453,10 +3045,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46297.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>3397.818</v>
+        <v>3297.269</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3467,10 +3059,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46297.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>3344.79</v>
+        <v>3253.336</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3481,10 +3073,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46297.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>3282.256</v>
+        <v>3200.916</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3495,10 +3087,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46297.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>3200.154</v>
+        <v>3138.313</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3509,10 +3101,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46297.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>3059.287</v>
+        <v>3018.6</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3523,10 +3115,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46297.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>2984.805</v>
+        <v>2923.411</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3537,10 +3129,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46297.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>2851.775</v>
+        <v>2826.209</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3551,10 +3143,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46297.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>2711.831</v>
+        <v>2731.052</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3565,10 +3157,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46297.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>2409.418</v>
+        <v>2461.736</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3579,10 +3171,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46297.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>2192.687</v>
+        <v>2279.912</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3593,10 +3185,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46297.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>1978.295</v>
+        <v>2071.161</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3607,10 +3199,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46297.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>1764.303</v>
+        <v>1851.096</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3621,10 +3213,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46297.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>1419.99</v>
+        <v>1457.302</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3635,10 +3227,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46297.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>1185.241</v>
+        <v>1201.027</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3649,10 +3241,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46297.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>927.716</v>
+        <v>932.765</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3663,10 +3255,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46297.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>728.037</v>
+        <v>694.253</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3677,10 +3269,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46297.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>396.721</v>
+        <v>378.203</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3691,10 +3283,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46297.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>259.521</v>
+        <v>235.084</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3705,10 +3297,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46297.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>136.901</v>
+        <v>113.12</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3719,10 +3311,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46297.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>73.70699999999999</v>
+        <v>48.889</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3733,10 +3325,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46297.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>28.821</v>
+        <v>14.25</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3747,10 +3339,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46297.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>77.455</v>
+        <v>18.674</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3761,10 +3353,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46297.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>77.685</v>
+        <v>17.586</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3775,10 +3367,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46297.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>77.53400000000001</v>
+        <v>66.206</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3789,10 +3381,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46297.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>76.95999999999999</v>
+        <v>65.068</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3803,10 +3395,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46297.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>76.86</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3817,10 +3409,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46297.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>74.66</v>
+        <v>63.168</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3831,10 +3423,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46297.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>72.86</v>
+        <v>61.624</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3845,10 +3437,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46297.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>67.58</v>
+        <v>55.184</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3859,10 +3451,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46297.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>16.58</v>
+        <v>54.084</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3873,10 +3465,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46297.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>15.28</v>
+        <v>52.384</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3887,10 +3479,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46297.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>13.652</v>
+        <v>3.384</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3901,10 +3493,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46297.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>12.88</v>
+        <v>1.884</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3915,10 +3507,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46297.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>12.08</v>
+        <v>1.884</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3929,10 +3521,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46297.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>10.88</v>
+        <v>1.88</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3943,10 +3535,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46297.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>10.08</v>
+        <v>1.88</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3957,10 +3549,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46297.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>4.38</v>
+        <v>1.88</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3971,10 +3563,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46297.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>4.08</v>
+        <v>1.88</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3985,1374 +3577,16 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46297.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>3.78</v>
+        <v>1.08</v>
       </c>
       <c r="D188">
         <v>91</v>
       </c>
       <c r="E188" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>46297.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>3.28</v>
-      </c>
-      <c r="D189">
-        <v>92</v>
-      </c>
-      <c r="E189" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="2">
-        <v>46297.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>1.08</v>
-      </c>
-      <c r="D190">
-        <v>93</v>
-      </c>
-      <c r="E190" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="2">
-        <v>46297.96875</v>
-      </c>
-      <c r="B191">
-        <v>1.08</v>
-      </c>
-      <c r="D191">
-        <v>94</v>
-      </c>
-      <c r="E191" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="2">
-        <v>46297.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>1.08</v>
-      </c>
-      <c r="D192">
-        <v>95</v>
-      </c>
-      <c r="E192" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="2">
-        <v>46297.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>1.084</v>
-      </c>
-      <c r="D193">
-        <v>96</v>
-      </c>
-      <c r="E193" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" s="2">
-        <v>46298</v>
-      </c>
-      <c r="B194">
-        <v>1.88</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" s="2">
-        <v>46298.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>1.884</v>
-      </c>
-      <c r="D195">
-        <v>2</v>
-      </c>
-      <c r="E195" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
-      <c r="A196" s="2">
-        <v>46298.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>1.88</v>
-      </c>
-      <c r="D196">
-        <v>3</v>
-      </c>
-      <c r="E196" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" s="2">
-        <v>46298.03125</v>
-      </c>
-      <c r="B197">
-        <v>1.88</v>
-      </c>
-      <c r="D197">
-        <v>4</v>
-      </c>
-      <c r="E197" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" s="2">
-        <v>46298.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>1.66</v>
-      </c>
-      <c r="D198">
-        <v>5</v>
-      </c>
-      <c r="E198" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" s="2">
-        <v>46298.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>1.16</v>
-      </c>
-      <c r="D199">
-        <v>6</v>
-      </c>
-      <c r="E199" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" s="2">
-        <v>46298.0625</v>
-      </c>
-      <c r="B200">
-        <v>1.16</v>
-      </c>
-      <c r="D200">
-        <v>7</v>
-      </c>
-      <c r="E200" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" s="2">
-        <v>46298.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>1.16</v>
-      </c>
-      <c r="D201">
-        <v>8</v>
-      </c>
-      <c r="E201" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" s="2">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>1.16</v>
-      </c>
-      <c r="D202">
-        <v>9</v>
-      </c>
-      <c r="E202" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" s="2">
-        <v>46298.09375</v>
-      </c>
-      <c r="B203">
-        <v>1.16</v>
-      </c>
-      <c r="D203">
-        <v>10</v>
-      </c>
-      <c r="E203" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" s="2">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>1.16</v>
-      </c>
-      <c r="D204">
-        <v>11</v>
-      </c>
-      <c r="E204" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" s="2">
-        <v>46298.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>1.16</v>
-      </c>
-      <c r="D205">
-        <v>12</v>
-      </c>
-      <c r="E205" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" s="2">
-        <v>46298.125</v>
-      </c>
-      <c r="B206">
-        <v>1.08</v>
-      </c>
-      <c r="D206">
-        <v>13</v>
-      </c>
-      <c r="E206" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" s="2">
-        <v>46298.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>1.08</v>
-      </c>
-      <c r="D207">
-        <v>14</v>
-      </c>
-      <c r="E207" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" s="2">
-        <v>46298.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>1.08</v>
-      </c>
-      <c r="D208">
-        <v>15</v>
-      </c>
-      <c r="E208" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" s="2">
-        <v>46298.15625</v>
-      </c>
-      <c r="B209">
-        <v>1.08</v>
-      </c>
-      <c r="D209">
-        <v>16</v>
-      </c>
-      <c r="E209" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
-      <c r="A210" s="2">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>1.08</v>
-      </c>
-      <c r="D210">
-        <v>17</v>
-      </c>
-      <c r="E210" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
-      <c r="A211" s="2">
-        <v>46298.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>1.08</v>
-      </c>
-      <c r="D211">
-        <v>18</v>
-      </c>
-      <c r="E211" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
-      <c r="A212" s="2">
-        <v>46298.1875</v>
-      </c>
-      <c r="B212">
-        <v>1.08</v>
-      </c>
-      <c r="D212">
-        <v>19</v>
-      </c>
-      <c r="E212" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
-      <c r="A213" s="2">
-        <v>46298.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>1.08</v>
-      </c>
-      <c r="D213">
-        <v>20</v>
-      </c>
-      <c r="E213" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
-      <c r="A214" s="2">
-        <v>46298.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>3.683</v>
-      </c>
-      <c r="D214">
-        <v>21</v>
-      </c>
-      <c r="E214" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
-      <c r="A215" s="2">
-        <v>46298.21875</v>
-      </c>
-      <c r="B215">
-        <v>3.759</v>
-      </c>
-      <c r="D215">
-        <v>22</v>
-      </c>
-      <c r="E215" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
-      <c r="A216" s="2">
-        <v>46298.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>3.85</v>
-      </c>
-      <c r="D216">
-        <v>23</v>
-      </c>
-      <c r="E216" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
-      <c r="A217" s="2">
-        <v>46298.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>3.952</v>
-      </c>
-      <c r="D217">
-        <v>24</v>
-      </c>
-      <c r="E217" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
-      <c r="A218" s="2">
-        <v>46298.25</v>
-      </c>
-      <c r="B218">
-        <v>12.494</v>
-      </c>
-      <c r="D218">
-        <v>25</v>
-      </c>
-      <c r="E218" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
-      <c r="A219" s="2">
-        <v>46298.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>15.905</v>
-      </c>
-      <c r="D219">
-        <v>26</v>
-      </c>
-      <c r="E219" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
-      <c r="A220" s="2">
-        <v>46298.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>52.686</v>
-      </c>
-      <c r="D220">
-        <v>27</v>
-      </c>
-      <c r="E220" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
-      <c r="A221" s="2">
-        <v>46298.28125</v>
-      </c>
-      <c r="B221">
-        <v>142.407</v>
-      </c>
-      <c r="D221">
-        <v>28</v>
-      </c>
-      <c r="E221" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
-      <c r="A222" s="2">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>405.441</v>
-      </c>
-      <c r="D222">
-        <v>29</v>
-      </c>
-      <c r="E222" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
-      <c r="A223" s="2">
-        <v>46298.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>607.095</v>
-      </c>
-      <c r="D223">
-        <v>30</v>
-      </c>
-      <c r="E223" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
-      <c r="A224" s="2">
-        <v>46298.3125</v>
-      </c>
-      <c r="B224">
-        <v>818.942</v>
-      </c>
-      <c r="D224">
-        <v>31</v>
-      </c>
-      <c r="E224" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
-      <c r="A225" s="2">
-        <v>46298.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>1093.388</v>
-      </c>
-      <c r="D225">
-        <v>32</v>
-      </c>
-      <c r="E225" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
-      <c r="A226" s="2">
-        <v>46298.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>1464.961</v>
-      </c>
-      <c r="D226">
-        <v>33</v>
-      </c>
-      <c r="E226" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
-      <c r="A227" s="2">
-        <v>46298.34375</v>
-      </c>
-      <c r="B227">
-        <v>1709.586</v>
-      </c>
-      <c r="D227">
-        <v>34</v>
-      </c>
-      <c r="E227" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
-      <c r="A228" s="2">
-        <v>46298.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>1983.527</v>
-      </c>
-      <c r="D228">
-        <v>35</v>
-      </c>
-      <c r="E228" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
-      <c r="A229" s="2">
-        <v>46298.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>2201.657</v>
-      </c>
-      <c r="D229">
-        <v>36</v>
-      </c>
-      <c r="E229" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
-      <c r="A230" s="2">
-        <v>46298.375</v>
-      </c>
-      <c r="B230">
-        <v>2551.623</v>
-      </c>
-      <c r="D230">
-        <v>37</v>
-      </c>
-      <c r="E230" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
-      <c r="A231" s="2">
-        <v>46298.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>2715.187</v>
-      </c>
-      <c r="D231">
-        <v>38</v>
-      </c>
-      <c r="E231" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
-      <c r="A232" s="2">
-        <v>46298.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>2861.44</v>
-      </c>
-      <c r="D232">
-        <v>39</v>
-      </c>
-      <c r="E232" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
-      <c r="A233" s="2">
-        <v>46298.40625</v>
-      </c>
-      <c r="B233">
-        <v>2987.487</v>
-      </c>
-      <c r="D233">
-        <v>40</v>
-      </c>
-      <c r="E233" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
-      <c r="A234" s="2">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>3151.942</v>
-      </c>
-      <c r="D234">
-        <v>41</v>
-      </c>
-      <c r="E234" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
-      <c r="A235" s="2">
-        <v>46298.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>3240.309</v>
-      </c>
-      <c r="D235">
-        <v>42</v>
-      </c>
-      <c r="E235" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
-      <c r="A236" s="2">
-        <v>46298.4375</v>
-      </c>
-      <c r="B236">
-        <v>3310.706</v>
-      </c>
-      <c r="D236">
-        <v>43</v>
-      </c>
-      <c r="E236" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
-      <c r="A237" s="2">
-        <v>46298.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>3366.296</v>
-      </c>
-      <c r="D237">
-        <v>44</v>
-      </c>
-      <c r="E237" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
-      <c r="A238" s="2">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>3374.007</v>
-      </c>
-      <c r="D238">
-        <v>45</v>
-      </c>
-      <c r="E238" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
-      <c r="A239" s="2">
-        <v>46298.46875</v>
-      </c>
-      <c r="B239">
-        <v>3393.886</v>
-      </c>
-      <c r="D239">
-        <v>46</v>
-      </c>
-      <c r="E239" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
-      <c r="A240" s="2">
-        <v>46298.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>3411.223</v>
-      </c>
-      <c r="D240">
-        <v>47</v>
-      </c>
-      <c r="E240" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
-      <c r="A241" s="2">
-        <v>46298.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>3416.168</v>
-      </c>
-      <c r="D241">
-        <v>48</v>
-      </c>
-      <c r="E241" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
-      <c r="A242" s="2">
-        <v>46298.5</v>
-      </c>
-      <c r="B242">
-        <v>3451.039</v>
-      </c>
-      <c r="D242">
-        <v>49</v>
-      </c>
-      <c r="E242" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
-      <c r="A243" s="2">
-        <v>46298.51041666666</v>
-      </c>
-      <c r="B243">
-        <v>3433.668</v>
-      </c>
-      <c r="D243">
-        <v>50</v>
-      </c>
-      <c r="E243" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
-      <c r="A244" s="2">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="B244">
-        <v>3420.693</v>
-      </c>
-      <c r="D244">
-        <v>51</v>
-      </c>
-      <c r="E244" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
-      <c r="A245" s="2">
-        <v>46298.53125</v>
-      </c>
-      <c r="B245">
-        <v>3399.492</v>
-      </c>
-      <c r="D245">
-        <v>52</v>
-      </c>
-      <c r="E245" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
-      <c r="A246" s="2">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="B246">
-        <v>3355.819</v>
-      </c>
-      <c r="D246">
-        <v>53</v>
-      </c>
-      <c r="E246" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
-      <c r="A247" s="2">
-        <v>46298.55208333334</v>
-      </c>
-      <c r="B247">
-        <v>3310.072</v>
-      </c>
-      <c r="D247">
-        <v>54</v>
-      </c>
-      <c r="E247" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
-      <c r="A248" s="2">
-        <v>46298.5625</v>
-      </c>
-      <c r="B248">
-        <v>3251.246</v>
-      </c>
-      <c r="D248">
-        <v>55</v>
-      </c>
-      <c r="E248" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
-      <c r="A249" s="2">
-        <v>46298.57291666666</v>
-      </c>
-      <c r="B249">
-        <v>3193.931</v>
-      </c>
-      <c r="D249">
-        <v>56</v>
-      </c>
-      <c r="E249" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
-      <c r="A250" s="2">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="B250">
-        <v>3082.772</v>
-      </c>
-      <c r="D250">
-        <v>57</v>
-      </c>
-      <c r="E250" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
-      <c r="A251" s="2">
-        <v>46298.59375</v>
-      </c>
-      <c r="B251">
-        <v>2987.186</v>
-      </c>
-      <c r="D251">
-        <v>58</v>
-      </c>
-      <c r="E251" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
-      <c r="A252" s="2">
-        <v>46298.60416666666</v>
-      </c>
-      <c r="B252">
-        <v>2864.465</v>
-      </c>
-      <c r="D252">
-        <v>59</v>
-      </c>
-      <c r="E252" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
-      <c r="A253" s="2">
-        <v>46298.61458333334</v>
-      </c>
-      <c r="B253">
-        <v>2736.522</v>
-      </c>
-      <c r="D253">
-        <v>60</v>
-      </c>
-      <c r="E253" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
-      <c r="A254" s="2">
-        <v>46298.625</v>
-      </c>
-      <c r="B254">
-        <v>2494.313</v>
-      </c>
-      <c r="D254">
-        <v>61</v>
-      </c>
-      <c r="E254" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
-      <c r="A255" s="2">
-        <v>46298.63541666666</v>
-      </c>
-      <c r="B255">
-        <v>2308.932</v>
-      </c>
-      <c r="D255">
-        <v>62</v>
-      </c>
-      <c r="E255" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
-      <c r="A256" s="2">
-        <v>46298.64583333334</v>
-      </c>
-      <c r="B256">
-        <v>2082.994</v>
-      </c>
-      <c r="D256">
-        <v>63</v>
-      </c>
-      <c r="E256" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
-      <c r="A257" s="2">
-        <v>46298.65625</v>
-      </c>
-      <c r="B257">
-        <v>1867.71</v>
-      </c>
-      <c r="D257">
-        <v>64</v>
-      </c>
-      <c r="E257" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
-      <c r="A258" s="2">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="B258">
-        <v>1460.85</v>
-      </c>
-      <c r="D258">
-        <v>65</v>
-      </c>
-      <c r="E258" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
-      <c r="A259" s="2">
-        <v>46298.67708333334</v>
-      </c>
-      <c r="B259">
-        <v>1211.642</v>
-      </c>
-      <c r="D259">
-        <v>66</v>
-      </c>
-      <c r="E259" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
-      <c r="A260" s="2">
-        <v>46298.6875</v>
-      </c>
-      <c r="B260">
-        <v>941.423</v>
-      </c>
-      <c r="D260">
-        <v>67</v>
-      </c>
-      <c r="E260" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
-      <c r="A261" s="2">
-        <v>46298.69791666666</v>
-      </c>
-      <c r="B261">
-        <v>711.698</v>
-      </c>
-      <c r="D261">
-        <v>68</v>
-      </c>
-      <c r="E261" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
-      <c r="A262" s="2">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="B262">
-        <v>409.568</v>
-      </c>
-      <c r="D262">
-        <v>69</v>
-      </c>
-      <c r="E262" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
-      <c r="A263" s="2">
-        <v>46298.71875</v>
-      </c>
-      <c r="B263">
-        <v>249.426</v>
-      </c>
-      <c r="D263">
-        <v>70</v>
-      </c>
-      <c r="E263" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
-      <c r="A264" s="2">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="B264">
-        <v>134.19</v>
-      </c>
-      <c r="D264">
-        <v>71</v>
-      </c>
-      <c r="E264" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
-      <c r="A265" s="2">
-        <v>46298.73958333334</v>
-      </c>
-      <c r="B265">
-        <v>65.28100000000001</v>
-      </c>
-      <c r="D265">
-        <v>72</v>
-      </c>
-      <c r="E265" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
-      <c r="A266" s="2">
-        <v>46298.75</v>
-      </c>
-      <c r="B266">
-        <v>17.138</v>
-      </c>
-      <c r="D266">
-        <v>73</v>
-      </c>
-      <c r="E266" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
-      <c r="A267" s="2">
-        <v>46298.76041666666</v>
-      </c>
-      <c r="B267">
-        <v>21.39</v>
-      </c>
-      <c r="D267">
-        <v>74</v>
-      </c>
-      <c r="E267" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
-      <c r="A268" s="2">
-        <v>46298.77083333334</v>
-      </c>
-      <c r="B268">
-        <v>70.249</v>
-      </c>
-      <c r="D268">
-        <v>75</v>
-      </c>
-      <c r="E268" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
-      <c r="A269" s="2">
-        <v>46298.78125</v>
-      </c>
-      <c r="B269">
-        <v>73.105</v>
-      </c>
-      <c r="D269">
-        <v>76</v>
-      </c>
-      <c r="E269" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
-      <c r="A270" s="2">
-        <v>46298.79166666666</v>
-      </c>
-      <c r="B270">
-        <v>69.982</v>
-      </c>
-      <c r="D270">
-        <v>77</v>
-      </c>
-      <c r="E270" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
-      <c r="A271" s="2">
-        <v>46298.80208333334</v>
-      </c>
-      <c r="B271">
-        <v>70.88200000000001</v>
-      </c>
-      <c r="D271">
-        <v>78</v>
-      </c>
-      <c r="E271" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
-      <c r="A272" s="2">
-        <v>46298.8125</v>
-      </c>
-      <c r="B272">
-        <v>68.268</v>
-      </c>
-      <c r="D272">
-        <v>79</v>
-      </c>
-      <c r="E272" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5">
-      <c r="A273" s="2">
-        <v>46298.82291666666</v>
-      </c>
-      <c r="B273">
-        <v>67.724</v>
-      </c>
-      <c r="D273">
-        <v>80</v>
-      </c>
-      <c r="E273" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
-      <c r="A274" s="2">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="B274">
-        <v>60.584</v>
-      </c>
-      <c r="D274">
-        <v>81</v>
-      </c>
-      <c r="E274" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
-      <c r="A275" s="2">
-        <v>46298.84375</v>
-      </c>
-      <c r="B275">
-        <v>60.084</v>
-      </c>
-      <c r="D275">
-        <v>82</v>
-      </c>
-      <c r="E275" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
-      <c r="A276" s="2">
-        <v>46298.85416666666</v>
-      </c>
-      <c r="B276">
-        <v>12.484</v>
-      </c>
-      <c r="D276">
-        <v>83</v>
-      </c>
-      <c r="E276" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
-      <c r="A277" s="2">
-        <v>46298.86458333334</v>
-      </c>
-      <c r="B277">
-        <v>8.984</v>
-      </c>
-      <c r="D277">
-        <v>84</v>
-      </c>
-      <c r="E277" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
-      <c r="A278" s="2">
-        <v>46298.875</v>
-      </c>
-      <c r="B278">
-        <v>5.884</v>
-      </c>
-      <c r="D278">
-        <v>85</v>
-      </c>
-      <c r="E278" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
-      <c r="A279" s="2">
-        <v>46298.88541666666</v>
-      </c>
-      <c r="B279">
-        <v>5.584</v>
-      </c>
-      <c r="D279">
-        <v>86</v>
-      </c>
-      <c r="E279" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
-      <c r="A280" s="2">
-        <v>46298.89583333334</v>
-      </c>
-      <c r="B280">
-        <v>5.38</v>
-      </c>
-      <c r="D280">
-        <v>87</v>
-      </c>
-      <c r="E280" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
-      <c r="A281" s="2">
-        <v>46298.90625</v>
-      </c>
-      <c r="B281">
-        <v>5.08</v>
-      </c>
-      <c r="D281">
-        <v>88</v>
-      </c>
-      <c r="E281" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5">
-      <c r="A282" s="2">
-        <v>46298.91666666666</v>
-      </c>
-      <c r="B282">
-        <v>4.98</v>
-      </c>
-      <c r="D282">
-        <v>89</v>
-      </c>
-      <c r="E282" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
-      <c r="A283" s="2">
-        <v>46298.92708333334</v>
-      </c>
-      <c r="B283">
-        <v>4.18</v>
-      </c>
-      <c r="D283">
-        <v>90</v>
-      </c>
-      <c r="E283" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
-      <c r="A284" s="2">
-        <v>46298.9375</v>
-      </c>
-      <c r="B284">
-        <v>3.58</v>
-      </c>
-      <c r="D284">
-        <v>91</v>
-      </c>
-      <c r="E284" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
-      <c r="A285" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B285">
-        <v>3.48</v>
-      </c>
-      <c r="D285">
-        <v>92</v>
-      </c>
-      <c r="E285" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <si>
     <t>Timestamp</t>
   </si>
@@ -590,6 +590,855 @@
   </si>
   <si>
     <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
+  </si>
+  <si>
+    <t>07.10.202642</t>
+  </si>
+  <si>
+    <t>07.10.202643</t>
+  </si>
+  <si>
+    <t>07.10.202644</t>
+  </si>
+  <si>
+    <t>07.10.202645</t>
+  </si>
+  <si>
+    <t>07.10.202646</t>
+  </si>
+  <si>
+    <t>07.10.202647</t>
+  </si>
+  <si>
+    <t>07.10.202648</t>
+  </si>
+  <si>
+    <t>07.10.202649</t>
+  </si>
+  <si>
+    <t>07.10.202650</t>
+  </si>
+  <si>
+    <t>07.10.202651</t>
+  </si>
+  <si>
+    <t>07.10.202652</t>
+  </si>
+  <si>
+    <t>07.10.202653</t>
+  </si>
+  <si>
+    <t>07.10.202654</t>
+  </si>
+  <si>
+    <t>07.10.202655</t>
+  </si>
+  <si>
+    <t>07.10.202656</t>
+  </si>
+  <si>
+    <t>07.10.202657</t>
+  </si>
+  <si>
+    <t>07.10.202658</t>
+  </si>
+  <si>
+    <t>07.10.202659</t>
+  </si>
+  <si>
+    <t>07.10.202660</t>
+  </si>
+  <si>
+    <t>07.10.202661</t>
+  </si>
+  <si>
+    <t>07.10.202662</t>
+  </si>
+  <si>
+    <t>07.10.202663</t>
+  </si>
+  <si>
+    <t>07.10.202664</t>
+  </si>
+  <si>
+    <t>07.10.202665</t>
+  </si>
+  <si>
+    <t>07.10.202666</t>
+  </si>
+  <si>
+    <t>07.10.202667</t>
+  </si>
+  <si>
+    <t>07.10.202668</t>
+  </si>
+  <si>
+    <t>07.10.202669</t>
+  </si>
+  <si>
+    <t>07.10.202670</t>
+  </si>
+  <si>
+    <t>07.10.202671</t>
+  </si>
+  <si>
+    <t>07.10.202672</t>
+  </si>
+  <si>
+    <t>07.10.202673</t>
+  </si>
+  <si>
+    <t>07.10.202674</t>
+  </si>
+  <si>
+    <t>07.10.202675</t>
+  </si>
+  <si>
+    <t>07.10.202676</t>
+  </si>
+  <si>
+    <t>07.10.202677</t>
+  </si>
+  <si>
+    <t>07.10.202678</t>
+  </si>
+  <si>
+    <t>07.10.202679</t>
+  </si>
+  <si>
+    <t>07.10.202680</t>
+  </si>
+  <si>
+    <t>07.10.202681</t>
+  </si>
+  <si>
+    <t>07.10.202682</t>
+  </si>
+  <si>
+    <t>07.10.202683</t>
+  </si>
+  <si>
+    <t>07.10.202684</t>
+  </si>
+  <si>
+    <t>07.10.202685</t>
+  </si>
+  <si>
+    <t>07.10.202686</t>
   </si>
 </sst>
 </file>
@@ -951,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E471"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -978,6 +1827,9 @@
       <c r="B2">
         <v>1.88</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
@@ -992,6 +1844,9 @@
       <c r="B3">
         <v>1.884</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3">
         <v>2</v>
       </c>
@@ -1006,6 +1861,9 @@
       <c r="B4">
         <v>1.88</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
         <v>3</v>
       </c>
@@ -1020,6 +1878,9 @@
       <c r="B5">
         <v>1.88</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5">
         <v>4</v>
       </c>
@@ -1034,6 +1895,9 @@
       <c r="B6">
         <v>1.66</v>
       </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="D6">
         <v>5</v>
       </c>
@@ -1048,6 +1912,9 @@
       <c r="B7">
         <v>1.16</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
       <c r="D7">
         <v>6</v>
       </c>
@@ -1062,6 +1929,9 @@
       <c r="B8">
         <v>1.16</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
       <c r="D8">
         <v>7</v>
       </c>
@@ -1076,6 +1946,9 @@
       <c r="B9">
         <v>1.16</v>
       </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
       <c r="D9">
         <v>8</v>
       </c>
@@ -1090,6 +1963,9 @@
       <c r="B10">
         <v>1.16</v>
       </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
       <c r="D10">
         <v>9</v>
       </c>
@@ -1104,6 +1980,9 @@
       <c r="B11">
         <v>1.16</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
       <c r="D11">
         <v>10</v>
       </c>
@@ -1118,6 +1997,9 @@
       <c r="B12">
         <v>1.16</v>
       </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
       <c r="D12">
         <v>11</v>
       </c>
@@ -1132,6 +2014,9 @@
       <c r="B13">
         <v>1.16</v>
       </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
       <c r="D13">
         <v>12</v>
       </c>
@@ -1146,6 +2031,9 @@
       <c r="B14">
         <v>1.08</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="D14">
         <v>13</v>
       </c>
@@ -1160,6 +2048,9 @@
       <c r="B15">
         <v>1.08</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="D15">
         <v>14</v>
       </c>
@@ -1174,6 +2065,9 @@
       <c r="B16">
         <v>1.08</v>
       </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="D16">
         <v>15</v>
       </c>
@@ -1188,6 +2082,9 @@
       <c r="B17">
         <v>1.08</v>
       </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
       <c r="D17">
         <v>16</v>
       </c>
@@ -1202,6 +2099,9 @@
       <c r="B18">
         <v>1.08</v>
       </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
       <c r="D18">
         <v>17</v>
       </c>
@@ -1216,6 +2116,9 @@
       <c r="B19">
         <v>1.08</v>
       </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
       <c r="D19">
         <v>18</v>
       </c>
@@ -1230,6 +2133,9 @@
       <c r="B20">
         <v>1.08</v>
       </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
       <c r="D20">
         <v>19</v>
       </c>
@@ -1244,6 +2150,9 @@
       <c r="B21">
         <v>1.08</v>
       </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
       <c r="D21">
         <v>20</v>
       </c>
@@ -1258,6 +2167,9 @@
       <c r="B22">
         <v>3.683</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="D22">
         <v>21</v>
       </c>
@@ -1272,6 +2184,9 @@
       <c r="B23">
         <v>3.759</v>
       </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
       <c r="D23">
         <v>22</v>
       </c>
@@ -1286,6 +2201,9 @@
       <c r="B24">
         <v>3.85</v>
       </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
       <c r="D24">
         <v>23</v>
       </c>
@@ -1300,6 +2218,9 @@
       <c r="B25">
         <v>3.952</v>
       </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="D25">
         <v>24</v>
       </c>
@@ -1314,6 +2235,9 @@
       <c r="B26">
         <v>12.494</v>
       </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
       <c r="D26">
         <v>25</v>
       </c>
@@ -1328,6 +2252,9 @@
       <c r="B27">
         <v>15.905</v>
       </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
       <c r="D27">
         <v>26</v>
       </c>
@@ -1342,6 +2269,9 @@
       <c r="B28">
         <v>52.686</v>
       </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
       <c r="D28">
         <v>27</v>
       </c>
@@ -1356,6 +2286,9 @@
       <c r="B29">
         <v>142.407</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
       <c r="D29">
         <v>28</v>
       </c>
@@ -1370,6 +2303,9 @@
       <c r="B30">
         <v>405.441</v>
       </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
       <c r="D30">
         <v>29</v>
       </c>
@@ -1384,6 +2320,9 @@
       <c r="B31">
         <v>607.095</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="D31">
         <v>30</v>
       </c>
@@ -1398,6 +2337,9 @@
       <c r="B32">
         <v>818.942</v>
       </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
       <c r="D32">
         <v>31</v>
       </c>
@@ -1412,6 +2354,9 @@
       <c r="B33">
         <v>1093.388</v>
       </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="D33">
         <v>32</v>
       </c>
@@ -1426,6 +2371,9 @@
       <c r="B34">
         <v>1464.961</v>
       </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
       <c r="D34">
         <v>33</v>
       </c>
@@ -1440,6 +2388,9 @@
       <c r="B35">
         <v>1709.586</v>
       </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
       <c r="D35">
         <v>34</v>
       </c>
@@ -1454,6 +2405,9 @@
       <c r="B36">
         <v>1983.527</v>
       </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
       <c r="D36">
         <v>35</v>
       </c>
@@ -1468,6 +2422,9 @@
       <c r="B37">
         <v>2201.657</v>
       </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
       <c r="D37">
         <v>36</v>
       </c>
@@ -1482,6 +2439,9 @@
       <c r="B38">
         <v>2551.623</v>
       </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38">
         <v>37</v>
       </c>
@@ -1496,6 +2456,9 @@
       <c r="B39">
         <v>2715.187</v>
       </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
       <c r="D39">
         <v>38</v>
       </c>
@@ -1510,6 +2473,9 @@
       <c r="B40">
         <v>2861.44</v>
       </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
       <c r="D40">
         <v>39</v>
       </c>
@@ -1524,6 +2490,9 @@
       <c r="B41">
         <v>2987.487</v>
       </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
       <c r="D41">
         <v>40</v>
       </c>
@@ -1538,6 +2507,9 @@
       <c r="B42">
         <v>3151.942</v>
       </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
       <c r="D42">
         <v>41</v>
       </c>
@@ -1552,6 +2524,9 @@
       <c r="B43">
         <v>3240.309</v>
       </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
       <c r="D43">
         <v>42</v>
       </c>
@@ -1566,6 +2541,9 @@
       <c r="B44">
         <v>3310.706</v>
       </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
       <c r="D44">
         <v>43</v>
       </c>
@@ -1580,6 +2558,9 @@
       <c r="B45">
         <v>3366.296</v>
       </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
       <c r="D45">
         <v>44</v>
       </c>
@@ -1594,6 +2575,9 @@
       <c r="B46">
         <v>3374.007</v>
       </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
       <c r="D46">
         <v>45</v>
       </c>
@@ -1608,6 +2592,9 @@
       <c r="B47">
         <v>3393.886</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
       <c r="D47">
         <v>46</v>
       </c>
@@ -1622,6 +2609,9 @@
       <c r="B48">
         <v>3411.223</v>
       </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
       <c r="D48">
         <v>47</v>
       </c>
@@ -1636,6 +2626,9 @@
       <c r="B49">
         <v>3416.168</v>
       </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
       <c r="D49">
         <v>48</v>
       </c>
@@ -1650,6 +2643,9 @@
       <c r="B50">
         <v>3451.039</v>
       </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
       <c r="D50">
         <v>49</v>
       </c>
@@ -1664,6 +2660,9 @@
       <c r="B51">
         <v>3433.668</v>
       </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
       <c r="D51">
         <v>50</v>
       </c>
@@ -1678,6 +2677,9 @@
       <c r="B52">
         <v>3420.693</v>
       </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
       <c r="D52">
         <v>51</v>
       </c>
@@ -1692,6 +2694,9 @@
       <c r="B53">
         <v>3399.492</v>
       </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
       <c r="D53">
         <v>52</v>
       </c>
@@ -1706,6 +2711,9 @@
       <c r="B54">
         <v>3355.819</v>
       </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
       <c r="D54">
         <v>53</v>
       </c>
@@ -1720,6 +2728,9 @@
       <c r="B55">
         <v>3310.072</v>
       </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
       <c r="D55">
         <v>54</v>
       </c>
@@ -1734,6 +2745,9 @@
       <c r="B56">
         <v>3251.246</v>
       </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
       <c r="D56">
         <v>55</v>
       </c>
@@ -1748,6 +2762,9 @@
       <c r="B57">
         <v>3193.931</v>
       </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
       <c r="D57">
         <v>56</v>
       </c>
@@ -1762,6 +2779,9 @@
       <c r="B58">
         <v>3082.772</v>
       </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
       <c r="D58">
         <v>57</v>
       </c>
@@ -1776,6 +2796,9 @@
       <c r="B59">
         <v>2987.186</v>
       </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
       <c r="D59">
         <v>58</v>
       </c>
@@ -1790,6 +2813,9 @@
       <c r="B60">
         <v>2864.465</v>
       </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
       <c r="D60">
         <v>59</v>
       </c>
@@ -1804,6 +2830,9 @@
       <c r="B61">
         <v>2736.522</v>
       </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
       <c r="D61">
         <v>60</v>
       </c>
@@ -1818,6 +2847,9 @@
       <c r="B62">
         <v>2494.313</v>
       </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
       <c r="D62">
         <v>61</v>
       </c>
@@ -1832,6 +2864,9 @@
       <c r="B63">
         <v>2308.932</v>
       </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
       <c r="D63">
         <v>62</v>
       </c>
@@ -1846,6 +2881,9 @@
       <c r="B64">
         <v>2082.994</v>
       </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
       <c r="D64">
         <v>63</v>
       </c>
@@ -1860,6 +2898,9 @@
       <c r="B65">
         <v>1867.71</v>
       </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
       <c r="D65">
         <v>64</v>
       </c>
@@ -1874,6 +2915,9 @@
       <c r="B66">
         <v>1460.85</v>
       </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
       <c r="D66">
         <v>65</v>
       </c>
@@ -1888,6 +2932,9 @@
       <c r="B67">
         <v>1211.642</v>
       </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
       <c r="D67">
         <v>66</v>
       </c>
@@ -1902,6 +2949,9 @@
       <c r="B68">
         <v>941.423</v>
       </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
       <c r="D68">
         <v>67</v>
       </c>
@@ -1916,6 +2966,9 @@
       <c r="B69">
         <v>711.698</v>
       </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
       <c r="D69">
         <v>68</v>
       </c>
@@ -1930,6 +2983,9 @@
       <c r="B70">
         <v>409.568</v>
       </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
       <c r="D70">
         <v>69</v>
       </c>
@@ -1944,6 +3000,9 @@
       <c r="B71">
         <v>249.426</v>
       </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
       <c r="D71">
         <v>70</v>
       </c>
@@ -1958,6 +3017,9 @@
       <c r="B72">
         <v>134.19</v>
       </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
       <c r="D72">
         <v>71</v>
       </c>
@@ -1972,6 +3034,9 @@
       <c r="B73">
         <v>65.28100000000001</v>
       </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
       <c r="D73">
         <v>72</v>
       </c>
@@ -1986,6 +3051,9 @@
       <c r="B74">
         <v>17.138</v>
       </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
       <c r="D74">
         <v>73</v>
       </c>
@@ -2000,6 +3068,9 @@
       <c r="B75">
         <v>21.39</v>
       </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
       <c r="D75">
         <v>74</v>
       </c>
@@ -2014,6 +3085,9 @@
       <c r="B76">
         <v>70.249</v>
       </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
       <c r="D76">
         <v>75</v>
       </c>
@@ -2028,6 +3102,9 @@
       <c r="B77">
         <v>73.105</v>
       </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
       <c r="D77">
         <v>76</v>
       </c>
@@ -2042,6 +3119,9 @@
       <c r="B78">
         <v>69.982</v>
       </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
       <c r="D78">
         <v>77</v>
       </c>
@@ -2056,6 +3136,9 @@
       <c r="B79">
         <v>70.88200000000001</v>
       </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
       <c r="D79">
         <v>78</v>
       </c>
@@ -2070,6 +3153,9 @@
       <c r="B80">
         <v>68.268</v>
       </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
       <c r="D80">
         <v>79</v>
       </c>
@@ -2084,6 +3170,9 @@
       <c r="B81">
         <v>67.724</v>
       </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
       <c r="D81">
         <v>80</v>
       </c>
@@ -2098,6 +3187,9 @@
       <c r="B82">
         <v>60.584</v>
       </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
       <c r="D82">
         <v>81</v>
       </c>
@@ -2112,6 +3204,9 @@
       <c r="B83">
         <v>60.084</v>
       </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
       <c r="D83">
         <v>82</v>
       </c>
@@ -2126,6 +3221,9 @@
       <c r="B84">
         <v>12.484</v>
       </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
       <c r="D84">
         <v>83</v>
       </c>
@@ -2140,6 +3238,9 @@
       <c r="B85">
         <v>8.984</v>
       </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
       <c r="D85">
         <v>84</v>
       </c>
@@ -2154,6 +3255,9 @@
       <c r="B86">
         <v>5.884</v>
       </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
       <c r="D86">
         <v>85</v>
       </c>
@@ -2168,6 +3272,9 @@
       <c r="B87">
         <v>5.584</v>
       </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
       <c r="D87">
         <v>86</v>
       </c>
@@ -2182,6 +3289,9 @@
       <c r="B88">
         <v>5.38</v>
       </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
       <c r="D88">
         <v>87</v>
       </c>
@@ -2196,6 +3306,9 @@
       <c r="B89">
         <v>5.08</v>
       </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
       <c r="D89">
         <v>88</v>
       </c>
@@ -2210,6 +3323,9 @@
       <c r="B90">
         <v>4.98</v>
       </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
       <c r="D90">
         <v>89</v>
       </c>
@@ -2224,6 +3340,9 @@
       <c r="B91">
         <v>4.18</v>
       </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
       <c r="D91">
         <v>90</v>
       </c>
@@ -2238,6 +3357,9 @@
       <c r="B92">
         <v>3.58</v>
       </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
       <c r="D92">
         <v>91</v>
       </c>
@@ -2252,6 +3374,9 @@
       <c r="B93">
         <v>3.48</v>
       </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
       <c r="D93">
         <v>92</v>
       </c>
@@ -2266,6 +3391,9 @@
       <c r="B94">
         <v>1.08</v>
       </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
       <c r="D94">
         <v>93</v>
       </c>
@@ -2280,6 +3408,9 @@
       <c r="B95">
         <v>1.08</v>
       </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
       <c r="D95">
         <v>94</v>
       </c>
@@ -2294,6 +3425,9 @@
       <c r="B96">
         <v>1.08</v>
       </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
       <c r="D96">
         <v>95</v>
       </c>
@@ -2308,6 +3442,9 @@
       <c r="B97">
         <v>1.084</v>
       </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
       <c r="D97">
         <v>96</v>
       </c>
@@ -2322,6 +3459,9 @@
       <c r="B98">
         <v>1.78</v>
       </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
       <c r="D98">
         <v>1</v>
       </c>
@@ -2336,6 +3476,9 @@
       <c r="B99">
         <v>1.084</v>
       </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
       <c r="D99">
         <v>2</v>
       </c>
@@ -2350,6 +3493,9 @@
       <c r="B100">
         <v>1.08</v>
       </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
       <c r="D100">
         <v>3</v>
       </c>
@@ -2364,6 +3510,9 @@
       <c r="B101">
         <v>1.08</v>
       </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
       <c r="D101">
         <v>4</v>
       </c>
@@ -2378,6 +3527,9 @@
       <c r="B102">
         <v>1.16</v>
       </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
       <c r="D102">
         <v>5</v>
       </c>
@@ -2392,6 +3544,9 @@
       <c r="B103">
         <v>1.16</v>
       </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
       <c r="D103">
         <v>6</v>
       </c>
@@ -2406,6 +3561,9 @@
       <c r="B104">
         <v>1.16</v>
       </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
       <c r="D104">
         <v>7</v>
       </c>
@@ -2420,6 +3578,9 @@
       <c r="B105">
         <v>1.16</v>
       </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
       <c r="D105">
         <v>8</v>
       </c>
@@ -2434,6 +3595,9 @@
       <c r="B106">
         <v>1.16</v>
       </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
       <c r="D106">
         <v>9</v>
       </c>
@@ -2448,6 +3612,9 @@
       <c r="B107">
         <v>1.16</v>
       </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
       <c r="D107">
         <v>10</v>
       </c>
@@ -2460,7 +3627,10 @@
         <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.16</v>
+        <v>1.66</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2474,7 +3644,10 @@
         <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.16</v>
+        <v>1.66</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2488,7 +3661,10 @@
         <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>1.08</v>
+        <v>1.58</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2504,6 +3680,9 @@
       <c r="B111">
         <v>1.08</v>
       </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
       <c r="D111">
         <v>14</v>
       </c>
@@ -2518,6 +3697,9 @@
       <c r="B112">
         <v>1.08</v>
       </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
       <c r="D112">
         <v>15</v>
       </c>
@@ -2532,6 +3714,9 @@
       <c r="B113">
         <v>1.08</v>
       </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
       <c r="D113">
         <v>16</v>
       </c>
@@ -2546,6 +3731,9 @@
       <c r="B114">
         <v>1.08</v>
       </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
       <c r="D114">
         <v>17</v>
       </c>
@@ -2560,6 +3748,9 @@
       <c r="B115">
         <v>1.08</v>
       </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
       <c r="D115">
         <v>18</v>
       </c>
@@ -2574,6 +3765,9 @@
       <c r="B116">
         <v>1.08</v>
       </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
       <c r="D116">
         <v>19</v>
       </c>
@@ -2588,6 +3782,9 @@
       <c r="B117">
         <v>1.08</v>
       </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
       <c r="D117">
         <v>20</v>
       </c>
@@ -2600,7 +3797,10 @@
         <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>2.679</v>
+        <v>5.179</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2614,7 +3814,10 @@
         <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>2.795</v>
+        <v>5.295</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2628,7 +3831,10 @@
         <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>2.898</v>
+        <v>5.398</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2642,7 +3848,10 @@
         <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>3.065</v>
+        <v>5.565</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2656,7 +3865,10 @@
         <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>12.095</v>
+        <v>15.895</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2670,7 +3882,10 @@
         <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>14.951</v>
+        <v>18.851</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2684,7 +3899,10 @@
         <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>41.999</v>
+        <v>54.017</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2698,7 +3916,10 @@
         <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>130.165</v>
+        <v>146.109</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2712,7 +3933,10 @@
         <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>415.901</v>
+        <v>426.098</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2726,7 +3950,10 @@
         <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>624.016</v>
+        <v>633.59</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2740,7 +3967,10 @@
         <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>838.8920000000001</v>
+        <v>857.647</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -2754,7 +3984,10 @@
         <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>1069.664</v>
+        <v>1093.743</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -2768,7 +4001,10 @@
         <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>1504.16</v>
+        <v>1542.282</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -2782,7 +4018,10 @@
         <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>1749.545</v>
+        <v>1794.591</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -2796,7 +4035,10 @@
         <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>2000.739</v>
+        <v>2051.985</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -2810,7 +4052,10 @@
         <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>2223.396</v>
+        <v>2284.662</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -2824,7 +4069,10 @@
         <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>2576.91</v>
+        <v>2651.428</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -2838,7 +4086,10 @@
         <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>2739.877</v>
+        <v>2825.262</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -2852,7 +4103,10 @@
         <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>2890.956</v>
+        <v>3005.977</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -2866,7 +4120,10 @@
         <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>2990.111</v>
+        <v>3116.493</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -2880,7 +4137,10 @@
         <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>3170.235</v>
+        <v>3287.693</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -2894,7 +4154,10 @@
         <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>3253.768</v>
+        <v>3366.795</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -2908,7 +4171,10 @@
         <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>3318.067</v>
+        <v>3424.73</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -2922,7 +4188,10 @@
         <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>3319.086</v>
+        <v>3438.371</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -2936,7 +4205,10 @@
         <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>3376.091</v>
+        <v>3449.123</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -2950,7 +4222,10 @@
         <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>3371.73</v>
+        <v>3474.524</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -2964,7 +4239,10 @@
         <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>3395.102</v>
+        <v>3482.02</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -2978,7 +4256,10 @@
         <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>3386.406</v>
+        <v>3479.513</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -2992,7 +4273,10 @@
         <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>3387.84</v>
+        <v>3467.627</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3006,7 +4290,10 @@
         <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>3377.45</v>
+        <v>3462.126</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3020,7 +4307,10 @@
         <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>3360.19</v>
+        <v>3455.392</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3034,7 +4324,10 @@
         <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>3330.88</v>
+        <v>3423.806</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3048,7 +4341,10 @@
         <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>3297.269</v>
+        <v>3408.338</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3062,7 +4358,10 @@
         <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>3253.336</v>
+        <v>3360.871</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3076,7 +4375,10 @@
         <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>3200.916</v>
+        <v>3301.957</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3090,7 +4392,10 @@
         <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>3138.313</v>
+        <v>3238.946</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3104,7 +4409,10 @@
         <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>3018.6</v>
+        <v>3144.104</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3118,7 +4426,10 @@
         <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>2923.411</v>
+        <v>3031.715</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3132,7 +4443,10 @@
         <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>2826.209</v>
+        <v>2912.475</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3146,7 +4460,10 @@
         <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>2731.052</v>
+        <v>2802.887</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3160,7 +4477,10 @@
         <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>2461.736</v>
+        <v>2546.279</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3174,7 +4494,10 @@
         <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>2279.912</v>
+        <v>2357.005</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3188,7 +4511,10 @@
         <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>2071.161</v>
+        <v>2141.6</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3202,7 +4528,10 @@
         <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>1851.096</v>
+        <v>1923.587</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3216,7 +4545,10 @@
         <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>1457.302</v>
+        <v>1538.392</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3230,7 +4562,10 @@
         <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>1201.027</v>
+        <v>1281.551</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3244,7 +4579,10 @@
         <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>932.765</v>
+        <v>987.958</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3258,7 +4596,10 @@
         <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>694.253</v>
+        <v>747.318</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3272,7 +4613,10 @@
         <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>378.203</v>
+        <v>452.429</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3286,7 +4630,10 @@
         <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>235.084</v>
+        <v>286.726</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3300,7 +4647,10 @@
         <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>113.12</v>
+        <v>128.174</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3314,7 +4664,10 @@
         <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>48.889</v>
+        <v>58.757</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3328,7 +4681,10 @@
         <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>14.25</v>
+        <v>57.35</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3342,7 +4698,10 @@
         <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>18.674</v>
+        <v>27.774</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3356,7 +4715,10 @@
         <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>17.586</v>
+        <v>26.686</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3370,7 +4732,10 @@
         <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>66.206</v>
+        <v>27.806</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3384,7 +4749,10 @@
         <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>65.068</v>
+        <v>24.378</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3398,7 +4766,10 @@
         <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>65.16800000000001</v>
+        <v>24.478</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3412,7 +4783,10 @@
         <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>63.168</v>
+        <v>22.478</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3426,7 +4800,10 @@
         <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>61.624</v>
+        <v>20.734</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3440,7 +4817,10 @@
         <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>55.184</v>
+        <v>13.087</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3454,7 +4834,10 @@
         <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>54.084</v>
+        <v>11.587</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3468,7 +4851,10 @@
         <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>52.384</v>
+        <v>9.887</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3482,7 +4868,10 @@
         <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>3.384</v>
+        <v>7.987</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3496,7 +4885,10 @@
         <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>1.884</v>
+        <v>8.686999999999999</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3510,7 +4902,10 @@
         <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>1.884</v>
+        <v>7.084</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3524,7 +4919,10 @@
         <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.88</v>
+        <v>6.28</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3538,7 +4936,10 @@
         <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>1.88</v>
+        <v>5.18</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3552,7 +4953,10 @@
         <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.88</v>
+        <v>6.08</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3566,7 +4970,10 @@
         <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.88</v>
+        <v>5.88</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3580,13 +4987,4689 @@
         <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>1.08</v>
+        <v>4.78</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
       </c>
       <c r="D188">
         <v>91</v>
       </c>
       <c r="E188" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>4.18</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>1.08</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>1.08</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>1.08</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>1.08</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>1.08</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>1.08</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1.08</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>1.08</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1.16</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1.16</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>1.16</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1.16</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1.16</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>1.16</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1.16</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1.16</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>1.08</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1.08</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1.08</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>1.08</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1.08</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1.08</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>1.08</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1.08</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5.688</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>6.219</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>7.044</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>9.321</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>70.337</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>75.94799999999999</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>109.456</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>205.043</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>443.22</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>630.162</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>868.883</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1095.102</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1576.764</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>1821.818</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>2129.922</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>2359.078</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>2808.149</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3002.086</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3147.549</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>3287.528</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>3491.577</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>3556.852</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>3596.975</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>3646.434</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>3683.278</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>3700.468</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>3711.903</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>3722.611</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>3716.808</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>3718.804</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>3697.112</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>3699.713</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>3626.544</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>3588.98</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>3517.663</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>3436.465</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>3282.264</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>3172.71</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3017.812</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>2855.603</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>2544.374</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>2330.172</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>2066.325</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>1817.147</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1472.074</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1216.172</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>955.5940000000001</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>730.602</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>391.085</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>253.619</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>144.224</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>80.27</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>87.818</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>83.938</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>82.89700000000001</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>84.43300000000001</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>84.66</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>82.863</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>81.319</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>25.683</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>21.083</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>19.683</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>22.783</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>15.383</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>14.38</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>19.68</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>15.18</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>14.58</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>18.48</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>18.48</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>14.58</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1.08</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>1.08</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1.08</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1.08</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>1.08</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>1.08</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>1.08</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>1.08</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>1.16</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>1.16</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>1.16</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>1.16</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>1.16</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>1.16</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>1.16</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>1.16</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>1.08</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>1.08</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>1.08</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>1.08</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>1.08</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>1.08</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>1.08</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>1.08</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>4.624</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>5.093</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5.891</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>7.157</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>18.752</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>21.908</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>48.13</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>122.106</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>388.159</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>558.537</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>777.186</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>990.5069999999999</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1378.698</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>1626.804</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1903.422</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>2112.801</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>2528.509</v>
+      </c>
+      <c r="C326">
+        <v>2154</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2723.344</v>
+      </c>
+      <c r="C327">
+        <v>2270</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2893.649</v>
+      </c>
+      <c r="C328">
+        <v>2390</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>3034.096</v>
+      </c>
+      <c r="C329">
+        <v>2480</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>3246.238</v>
+      </c>
+      <c r="C330">
+        <v>2628</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>3382.759</v>
+      </c>
+      <c r="C331">
+        <v>2688</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>3364.861</v>
+      </c>
+      <c r="C332">
+        <v>2743</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3424.585</v>
+      </c>
+      <c r="C333">
+        <v>2808</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>3486.743</v>
+      </c>
+      <c r="C334">
+        <v>2893</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>3522.212</v>
+      </c>
+      <c r="C335">
+        <v>2935</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>3551.865</v>
+      </c>
+      <c r="C336">
+        <v>2920</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>3563.275</v>
+      </c>
+      <c r="C337">
+        <v>2978</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>3565.904</v>
+      </c>
+      <c r="C338">
+        <v>2943</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>3573.573</v>
+      </c>
+      <c r="C339">
+        <v>2904</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>3553.887</v>
+      </c>
+      <c r="C340">
+        <v>2878</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>3494.556</v>
+      </c>
+      <c r="C341">
+        <v>2884</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>3430.246</v>
+      </c>
+      <c r="C342">
+        <v>2850</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>3387.734</v>
+      </c>
+      <c r="C343">
+        <v>2874</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>3336.574</v>
+      </c>
+      <c r="C344">
+        <v>2780</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>3270.589</v>
+      </c>
+      <c r="C345">
+        <v>2696</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>3145.063</v>
+      </c>
+      <c r="C346">
+        <v>2688</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>3048.558</v>
+      </c>
+      <c r="C347">
+        <v>2624</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>2933.53</v>
+      </c>
+      <c r="C348">
+        <v>2553</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>2787.888</v>
+      </c>
+      <c r="C349">
+        <v>2445</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>2485.777</v>
+      </c>
+      <c r="C350">
+        <v>2205</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>2275.508</v>
+      </c>
+      <c r="C351">
+        <v>1957</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>2026.972</v>
+      </c>
+      <c r="C352">
+        <v>1768</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>1802.388</v>
+      </c>
+      <c r="C353">
+        <v>1601</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1418.782</v>
+      </c>
+      <c r="C354">
+        <v>1345</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1159.825</v>
+      </c>
+      <c r="C355">
+        <v>1095</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>908.866</v>
+      </c>
+      <c r="C356">
+        <v>852</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>680.451</v>
+      </c>
+      <c r="C357">
+        <v>613</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>358.868</v>
+      </c>
+      <c r="C358">
+        <v>347</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>230.517</v>
+      </c>
+      <c r="C359">
+        <v>164</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>119.57</v>
+      </c>
+      <c r="C360">
+        <v>50</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>72.40300000000001</v>
+      </c>
+      <c r="C361">
+        <v>2</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>87.947</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>94.232</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>96.188</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>95.67400000000001</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>89.685</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>88.66</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>83.66</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>27.38</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>26.58</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>12.18</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>25.18</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>9.68</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>23.68</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>23.18</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>18.88</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>11.08</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>11.08</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>11.08</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1.08</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>1.08</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>1.08</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>1.08</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1.08</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>1.08</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>1.08</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>1.08</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>1.08</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>1.16</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>1.16</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>1.16</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>1.16</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>1.16</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>1.16</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>1.16</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>1.16</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>1.08</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>1.08</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>1.08</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>1.08</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>1.081</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>1.081</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>1.081</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>1.081</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>1.126</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>1.186</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>1.25</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>1.398</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>6.577</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>7.65</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>25.129</v>
+      </c>
+      <c r="C412">
+        <v>28</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>90.494</v>
+      </c>
+      <c r="C413">
+        <v>111</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>355.092</v>
+      </c>
+      <c r="C414">
+        <v>270</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>513.593</v>
+      </c>
+      <c r="C415">
+        <v>490</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>701.203</v>
+      </c>
+      <c r="C416">
+        <v>731</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>897.447</v>
+      </c>
+      <c r="C417">
+        <v>976</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1315.768</v>
+      </c>
+      <c r="C418">
+        <v>1231</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>1537.795</v>
+      </c>
+      <c r="C419">
+        <v>1504</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>1805.559</v>
+      </c>
+      <c r="C420">
+        <v>1719</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>2020.392</v>
+      </c>
+      <c r="C421">
+        <v>1901</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>2370.704</v>
+      </c>
+      <c r="C422">
+        <v>2079</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>2532.931</v>
+      </c>
+      <c r="C423">
+        <v>2248</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>2680.769</v>
+      </c>
+      <c r="C424">
+        <v>2401</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>2792.879</v>
+      </c>
+      <c r="C425">
+        <v>2503</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>2962.088</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>3048.37</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>3084.796</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>3143.064</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>3194.727</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>3231.85</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>3238.587</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>3231.765</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>3224.09</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>3221.94</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>3197.811</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>3154.602</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>3101.591</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>3049.772</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>2978.25</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>2889.75</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>2746.633</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>2647.392</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>2552.551</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>2407.756</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>2089.921</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>1895.083</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>1679.348</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>1469.681</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1132.102</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>920.672</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>717.648</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>548.357</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>287.262</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>171.651</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>83.946</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>44.35</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>67.901</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>72.58799999999999</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>71.248</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>66.86</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>66.45099999999999</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>64.393</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>73.16</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>7.981</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>18.481</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>4.281</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1.881</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>1.28</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>1.08</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -593,6 +305,276 @@
   </si>
   <si>
     <t>08.10.202692</t>
+  </si>
+  <si>
+    <t>08.10.202693</t>
+  </si>
+  <si>
+    <t>08.10.202694</t>
+  </si>
+  <si>
+    <t>08.10.202695</t>
+  </si>
+  <si>
+    <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
   </si>
 </sst>
 </file>
@@ -954,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -976,10 +958,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -993,10 +975,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1010,10 +992,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1027,10 +1009,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1044,10 +1026,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1061,10 +1043,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1078,10 +1060,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1095,10 +1077,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1112,10 +1094,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1129,10 +1111,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1146,10 +1128,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1163,10 +1145,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1180,10 +1162,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1197,10 +1179,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1214,10 +1196,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1231,10 +1213,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1248,10 +1230,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1265,10 +1247,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1282,10 +1264,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1299,10 +1281,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1316,10 +1298,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.126</v>
+        <v>1.404</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1333,10 +1315,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>1.186</v>
+        <v>1.46</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1350,10 +1332,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.25</v>
+        <v>1.516</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1367,10 +1349,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.398</v>
+        <v>2.392</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1384,10 +1366,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>6.577</v>
+        <v>8.105</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1401,10 +1383,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>7.65</v>
+        <v>8.808</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1418,13 +1400,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>25.129</v>
+        <v>24.065</v>
       </c>
       <c r="C28">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1417,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>90.494</v>
+        <v>83.989</v>
       </c>
       <c r="C29">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1434,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>355.092</v>
+        <v>353.717</v>
       </c>
       <c r="C30">
-        <v>270</v>
+        <v>212</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1451,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>513.593</v>
+        <v>512.051</v>
       </c>
       <c r="C31">
-        <v>490</v>
+        <v>379</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1468,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>701.203</v>
+        <v>713.5839999999999</v>
       </c>
       <c r="C32">
-        <v>731</v>
+        <v>566</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1485,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>897.447</v>
+        <v>946.412</v>
       </c>
       <c r="C33">
-        <v>976</v>
+        <v>758</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1502,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>1315.768</v>
+        <v>1393.733</v>
       </c>
       <c r="C34">
-        <v>1231</v>
+        <v>994</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1519,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>1537.795</v>
+        <v>1638.932</v>
       </c>
       <c r="C35">
-        <v>1504</v>
+        <v>1252</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1536,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>1805.559</v>
+        <v>1932.419</v>
       </c>
       <c r="C36">
-        <v>1719</v>
+        <v>1488</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1553,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>2020.392</v>
+        <v>2158.212</v>
       </c>
       <c r="C37">
-        <v>1901</v>
+        <v>1723</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1570,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>2370.704</v>
+        <v>2534.821</v>
       </c>
       <c r="C38">
-        <v>2079</v>
+        <v>1960</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1587,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>2532.931</v>
+        <v>2691.343</v>
       </c>
       <c r="C39">
-        <v>2248</v>
+        <v>2125</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1604,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>2680.769</v>
+        <v>2846.543</v>
       </c>
       <c r="C40">
-        <v>2401</v>
+        <v>2280</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1621,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>2792.879</v>
+        <v>2980.398</v>
       </c>
       <c r="C41">
-        <v>2503</v>
+        <v>2418</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1638,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>2962.088</v>
+        <v>3162.815</v>
       </c>
       <c r="C42">
-        <v>2578</v>
+        <v>2496</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1655,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>3048.37</v>
+        <v>3256.443</v>
       </c>
       <c r="C43">
-        <v>2650</v>
+        <v>2586</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1672,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>3084.796</v>
+        <v>3323.02</v>
       </c>
       <c r="C44">
-        <v>2677</v>
+        <v>2655</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1689,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>3143.064</v>
+        <v>3385.007</v>
       </c>
       <c r="C45">
-        <v>2741</v>
+        <v>2696</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1706,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>3194.727</v>
+        <v>3421.434</v>
       </c>
       <c r="C46">
-        <v>2756</v>
+        <v>2744</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1723,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>3231.85</v>
+        <v>3425.481</v>
       </c>
       <c r="C47">
-        <v>2770</v>
+        <v>2798</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1740,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>3238.587</v>
+        <v>3449.048</v>
       </c>
       <c r="C48">
-        <v>2795</v>
+        <v>2772</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1757,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>3231.765</v>
+        <v>3458.695</v>
       </c>
       <c r="C49">
-        <v>2801</v>
+        <v>2717</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1774,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>3224.09</v>
+        <v>3453.312</v>
       </c>
       <c r="C50">
-        <v>2774</v>
+        <v>2725</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1791,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>3221.94</v>
+        <v>3447.407</v>
       </c>
       <c r="C51">
-        <v>2758</v>
+        <v>2737</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1808,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>3197.811</v>
+        <v>3432.25</v>
       </c>
       <c r="C52">
-        <v>2740</v>
+        <v>2815</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1825,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>3154.602</v>
+        <v>3411.417</v>
       </c>
       <c r="C53">
-        <v>2726</v>
+        <v>2850</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1842,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>3101.591</v>
+        <v>3367.026</v>
       </c>
       <c r="C54">
-        <v>2715</v>
+        <v>2834</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1859,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>3049.772</v>
+        <v>3320.276</v>
       </c>
       <c r="C55">
-        <v>2635</v>
+        <v>2804</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1876,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>2978.25</v>
+        <v>3264.118</v>
       </c>
       <c r="C56">
-        <v>2626</v>
+        <v>2748</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1893,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>2889.75</v>
+        <v>3192.026</v>
       </c>
       <c r="C57">
-        <v>2557</v>
+        <v>2676</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1910,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>2746.633</v>
+        <v>3042.421</v>
       </c>
       <c r="C58">
-        <v>2432</v>
+        <v>2541</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1927,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>2647.392</v>
+        <v>2946.881</v>
       </c>
       <c r="C59">
-        <v>2354</v>
+        <v>2459</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1944,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>2552.551</v>
+        <v>2819.201</v>
       </c>
       <c r="C60">
-        <v>2254</v>
+        <v>2320</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1961,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>2407.756</v>
+        <v>2676.905</v>
       </c>
       <c r="C61">
-        <v>2163</v>
+        <v>2213</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1978,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>2089.921</v>
+        <v>2349.818</v>
       </c>
       <c r="C62">
-        <v>1944</v>
+        <v>2019</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +1995,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>1895.083</v>
+        <v>2173.086</v>
       </c>
       <c r="C63">
-        <v>1701</v>
+        <v>1797</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2012,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>1679.348</v>
+        <v>1936.963</v>
       </c>
       <c r="C64">
-        <v>1518</v>
+        <v>1566</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2029,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>1469.681</v>
+        <v>1717.447</v>
       </c>
       <c r="C65">
-        <v>1331</v>
+        <v>1393</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2046,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>1132.102</v>
+        <v>1310.342</v>
       </c>
       <c r="C66">
-        <v>1043</v>
+        <v>1151</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2063,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>920.672</v>
+        <v>1063.868</v>
       </c>
       <c r="C67">
-        <v>821</v>
+        <v>906</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2080,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>717.648</v>
+        <v>784.668</v>
       </c>
       <c r="C68">
-        <v>625</v>
+        <v>676</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2097,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>548.357</v>
+        <v>579.869</v>
       </c>
       <c r="C69">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2114,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>287.262</v>
+        <v>292.141</v>
       </c>
       <c r="C70">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2131,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>171.651</v>
+        <v>168.447</v>
       </c>
       <c r="C71">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2148,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>83.946</v>
+        <v>80.754</v>
       </c>
       <c r="C72">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2165,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>44.35</v>
+        <v>44.781</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,10 +2182,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>67.901</v>
+        <v>57.467</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2217,10 +2199,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>72.84999999999999</v>
+        <v>61.771</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2234,10 +2216,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>72.58799999999999</v>
+        <v>61.335</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2251,10 +2233,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>71.248</v>
+        <v>61.285</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2268,10 +2250,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>66.86</v>
+        <v>60.023</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2285,10 +2267,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>66.45099999999999</v>
+        <v>56.898</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2302,10 +2284,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>64.393</v>
+        <v>49.623</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2319,10 +2301,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>73.16</v>
+        <v>48.215</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2336,10 +2318,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>7.981</v>
+        <v>41.668</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2353,10 +2335,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>18.481</v>
+        <v>40.468</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2370,10 +2352,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>4.281</v>
+        <v>39.968</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2387,10 +2369,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.881</v>
+        <v>37.668</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2404,10 +2386,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1.28</v>
+        <v>6.268</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2421,10 +2403,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>1.08</v>
+        <v>9.968</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2438,10 +2420,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.08</v>
+        <v>10.368</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2455,10 +2437,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>1.08</v>
+        <v>9.868</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2472,10 +2454,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.08</v>
+        <v>6.268</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2489,10 +2471,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.08</v>
+        <v>6.468</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2506,10 +2488,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1.08</v>
+        <v>5.668</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2523,10 +2505,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.08</v>
+        <v>5.868</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2540,10 +2522,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.68</v>
+        <v>1.468</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2557,10 +2539,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2574,10 +2556,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2591,10 +2573,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2608,10 +2590,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2625,10 +2607,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2642,10 +2624,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2659,10 +2641,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2676,10 +2658,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2693,10 +2675,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2710,10 +2692,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2727,10 +2709,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2744,10 +2726,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2761,10 +2743,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2778,10 +2760,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2795,10 +2777,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2812,10 +2794,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2829,10 +2811,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2846,10 +2828,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2863,10 +2845,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2880,10 +2862,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2897,10 +2879,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2914,10 +2896,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2931,10 +2913,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2948,10 +2930,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.404</v>
+        <v>5.424</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2965,10 +2947,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>1.46</v>
+        <v>7.745</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2982,10 +2964,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>1.516</v>
+        <v>12.747</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2999,10 +2981,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.392</v>
+        <v>15.03</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3016,10 +2998,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>8.105</v>
+        <v>16.988</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3033,10 +3015,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>8.808</v>
+        <v>18.363</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3050,10 +3032,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>24.065</v>
+        <v>26.633</v>
       </c>
       <c r="C124">
         <v>18</v>
@@ -3067,13 +3049,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>83.989</v>
+        <v>79.69199999999999</v>
       </c>
       <c r="C125">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3066,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>353.717</v>
+        <v>292.474</v>
       </c>
       <c r="C126">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3083,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>512.051</v>
+        <v>411.968</v>
       </c>
       <c r="C127">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3100,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>713.5839999999999</v>
+        <v>561.978</v>
       </c>
       <c r="C128">
-        <v>566</v>
+        <v>506</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3117,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>946.412</v>
+        <v>715.95</v>
       </c>
       <c r="C129">
-        <v>758</v>
+        <v>667</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3134,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>1393.733</v>
+        <v>1081.646</v>
       </c>
       <c r="C130">
-        <v>994</v>
+        <v>872</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3151,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>1638.932</v>
+        <v>1260.477</v>
       </c>
       <c r="C131">
-        <v>1252</v>
+        <v>1130</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3168,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>1932.419</v>
+        <v>1446.872</v>
       </c>
       <c r="C132">
-        <v>1488</v>
+        <v>1323</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3185,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>2158.212</v>
-      </c>
-      <c r="C133">
-        <v>1723</v>
+        <v>1605.797</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,10 +3199,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>2534.821</v>
+        <v>1877.772</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3234,10 +3213,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
-        <v>2691.343</v>
+        <v>2015.456</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3248,10 +3227,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>2846.543</v>
+        <v>2144.366</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3262,10 +3241,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>2980.398</v>
+        <v>2248.442</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3276,10 +3255,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>3162.815</v>
+        <v>2406.253</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3290,10 +3269,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
-        <v>3256.443</v>
+        <v>2483.122</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3304,10 +3283,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
-        <v>3323.02</v>
+        <v>2540.829</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3318,10 +3297,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
-        <v>3385.007</v>
+        <v>2588.211</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3332,10 +3311,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
-        <v>3421.434</v>
+        <v>2639.579</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3346,10 +3325,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
-        <v>3425.481</v>
+        <v>2668.686</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3360,10 +3339,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
-        <v>3449.048</v>
+        <v>2684.824</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3374,10 +3353,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
-        <v>3458.695</v>
+        <v>2699.849</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3388,10 +3367,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
-        <v>3453.312</v>
+        <v>2699.154</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3402,10 +3381,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
-        <v>3447.407</v>
+        <v>2695.11</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3416,10 +3395,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
-        <v>3432.25</v>
+        <v>2683.931</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3430,10 +3409,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
-        <v>3411.417</v>
+        <v>2659.795</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3444,10 +3423,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
-        <v>3367.026</v>
+        <v>2615.994</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3458,10 +3437,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
-        <v>3320.276</v>
+        <v>2578.677</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3472,10 +3451,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
-        <v>3264.118</v>
+        <v>2534.749</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3486,10 +3465,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
-        <v>3192.026</v>
+        <v>2476.706</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3500,10 +3479,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
-        <v>3042.421</v>
+        <v>2333.684</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3514,10 +3493,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
-        <v>2946.881</v>
+        <v>2233.524</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3528,10 +3507,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
-        <v>2819.201</v>
+        <v>2102.376</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3542,10 +3521,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
-        <v>2676.905</v>
+        <v>1972.053</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3556,10 +3535,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
-        <v>2349.818</v>
+        <v>1680.023</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3570,10 +3549,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
-        <v>2173.086</v>
+        <v>1518.555</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3584,10 +3563,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
-        <v>1936.963</v>
+        <v>1351.391</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3598,10 +3577,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
-        <v>1717.447</v>
+        <v>1193.892</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3612,10 +3591,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
-        <v>1310.342</v>
+        <v>877.867</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3626,10 +3605,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
-        <v>1063.868</v>
+        <v>712.401</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3640,10 +3619,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
-        <v>784.668</v>
+        <v>543.579</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3654,10 +3633,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
-        <v>579.869</v>
+        <v>407.269</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3668,10 +3647,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
-        <v>292.141</v>
+        <v>194.551</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3682,10 +3661,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
-        <v>168.447</v>
+        <v>111.596</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3696,10 +3675,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
-        <v>80.754</v>
+        <v>55.187</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3710,10 +3689,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
-        <v>44.781</v>
+        <v>36.275</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3724,10 +3703,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
-        <v>57.467</v>
+        <v>44.085</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3738,10 +3717,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
-        <v>61.771</v>
+        <v>49.415</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3752,10 +3731,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
-        <v>61.335</v>
+        <v>55.086</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3766,10 +3745,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
-        <v>61.285</v>
+        <v>55.178</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3780,10 +3759,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
-        <v>60.023</v>
+        <v>55.032</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3794,10 +3773,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
-        <v>56.898</v>
+        <v>54.932</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3808,10 +3787,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
-        <v>49.623</v>
+        <v>49.632</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3822,10 +3801,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
-        <v>48.215</v>
+        <v>48.932</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3836,10 +3815,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
-        <v>41.668</v>
+        <v>40.652</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3850,10 +3829,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
-        <v>40.468</v>
+        <v>38.052</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3864,10 +3843,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
-        <v>39.968</v>
+        <v>38.052</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3878,10 +3857,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
-        <v>37.668</v>
+        <v>41.352</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3892,10 +3871,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
-        <v>6.268</v>
+        <v>2.152</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3906,100 +3885,16 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
-        <v>9.968</v>
+        <v>1.352</v>
       </c>
       <c r="D183">
         <v>86</v>
       </c>
       <c r="E183" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="2">
-        <v>46303.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>10.368</v>
-      </c>
-      <c r="D184">
-        <v>87</v>
-      </c>
-      <c r="E184" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="2">
-        <v>46303.90625</v>
-      </c>
-      <c r="B185">
-        <v>9.868</v>
-      </c>
-      <c r="D185">
-        <v>88</v>
-      </c>
-      <c r="E185" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2">
-        <v>46303.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>6.268</v>
-      </c>
-      <c r="D186">
-        <v>89</v>
-      </c>
-      <c r="E186" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="2">
-        <v>46303.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>6.468</v>
-      </c>
-      <c r="D187">
-        <v>90</v>
-      </c>
-      <c r="E187" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2">
-        <v>46303.9375</v>
-      </c>
-      <c r="B188">
-        <v>5.668</v>
-      </c>
-      <c r="D188">
-        <v>91</v>
-      </c>
-      <c r="E188" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>46303.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>5.868</v>
-      </c>
-      <c r="D189">
-        <v>92</v>
-      </c>
-      <c r="E189" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -575,6 +287,879 @@
   </si>
   <si>
     <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
+  </si>
+  <si>
+    <t>12.10.202639</t>
+  </si>
+  <si>
+    <t>12.10.202640</t>
+  </si>
+  <si>
+    <t>12.10.202641</t>
+  </si>
+  <si>
+    <t>12.10.202642</t>
+  </si>
+  <si>
+    <t>12.10.202643</t>
+  </si>
+  <si>
+    <t>12.10.202644</t>
+  </si>
+  <si>
+    <t>12.10.202645</t>
+  </si>
+  <si>
+    <t>12.10.202646</t>
+  </si>
+  <si>
+    <t>12.10.202647</t>
+  </si>
+  <si>
+    <t>12.10.202648</t>
+  </si>
+  <si>
+    <t>12.10.202649</t>
+  </si>
+  <si>
+    <t>12.10.202650</t>
+  </si>
+  <si>
+    <t>12.10.202651</t>
+  </si>
+  <si>
+    <t>12.10.202652</t>
+  </si>
+  <si>
+    <t>12.10.202653</t>
+  </si>
+  <si>
+    <t>12.10.202654</t>
+  </si>
+  <si>
+    <t>12.10.202655</t>
+  </si>
+  <si>
+    <t>12.10.202656</t>
+  </si>
+  <si>
+    <t>12.10.202657</t>
+  </si>
+  <si>
+    <t>12.10.202658</t>
+  </si>
+  <si>
+    <t>12.10.202659</t>
+  </si>
+  <si>
+    <t>12.10.202660</t>
+  </si>
+  <si>
+    <t>12.10.202661</t>
+  </si>
+  <si>
+    <t>12.10.202662</t>
+  </si>
+  <si>
+    <t>12.10.202663</t>
+  </si>
+  <si>
+    <t>12.10.202664</t>
+  </si>
+  <si>
+    <t>12.10.202665</t>
+  </si>
+  <si>
+    <t>12.10.202666</t>
+  </si>
+  <si>
+    <t>12.10.202667</t>
+  </si>
+  <si>
+    <t>12.10.202668</t>
+  </si>
+  <si>
+    <t>12.10.202669</t>
+  </si>
+  <si>
+    <t>12.10.202670</t>
+  </si>
+  <si>
+    <t>12.10.202671</t>
+  </si>
+  <si>
+    <t>12.10.202672</t>
+  </si>
+  <si>
+    <t>12.10.202673</t>
+  </si>
+  <si>
+    <t>12.10.202674</t>
+  </si>
+  <si>
+    <t>12.10.202675</t>
+  </si>
+  <si>
+    <t>12.10.202676</t>
+  </si>
+  <si>
+    <t>12.10.202677</t>
+  </si>
+  <si>
+    <t>12.10.202678</t>
+  </si>
+  <si>
+    <t>12.10.202679</t>
+  </si>
+  <si>
+    <t>12.10.202680</t>
+  </si>
+  <si>
+    <t>12.10.202681</t>
+  </si>
+  <si>
+    <t>12.10.202682</t>
+  </si>
+  <si>
+    <t>12.10.202683</t>
+  </si>
+  <si>
+    <t>12.10.202684</t>
+  </si>
+  <si>
+    <t>12.10.202685</t>
+  </si>
+  <si>
+    <t>12.10.202686</t>
+  </si>
+  <si>
+    <t>12.10.202687</t>
+  </si>
+  <si>
+    <t>12.10.202688</t>
+  </si>
+  <si>
+    <t>12.10.202689</t>
   </si>
 </sst>
 </file>
@@ -936,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -958,10 +1543,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -975,10 +1560,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -992,10 +1577,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1009,10 +1594,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1026,10 +1611,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1043,10 +1628,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1060,10 +1645,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1077,10 +1662,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1094,10 +1679,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1111,10 +1696,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1128,10 +1713,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1145,10 +1730,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1162,10 +1747,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1179,10 +1764,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1196,10 +1781,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1213,10 +1798,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1230,10 +1815,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1247,10 +1832,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1264,10 +1849,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1281,10 +1866,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1298,10 +1883,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.404</v>
+        <v>5.424</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1315,10 +1900,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>1.46</v>
+        <v>7.745</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1332,10 +1917,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.516</v>
+        <v>12.747</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1349,10 +1934,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.392</v>
+        <v>15.03</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1366,10 +1951,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>8.105</v>
+        <v>16.988</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1383,10 +1968,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>8.808</v>
+        <v>18.363</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1400,10 +1985,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>24.065</v>
+        <v>26.633</v>
       </c>
       <c r="C28">
         <v>18</v>
@@ -1417,13 +2002,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>83.989</v>
+        <v>79.69199999999999</v>
       </c>
       <c r="C29">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1434,13 +2019,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>353.717</v>
+        <v>292.474</v>
       </c>
       <c r="C30">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1451,13 +2036,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>512.051</v>
+        <v>411.968</v>
       </c>
       <c r="C31">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1468,13 +2053,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>713.5839999999999</v>
+        <v>561.978</v>
       </c>
       <c r="C32">
-        <v>566</v>
+        <v>506</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1485,13 +2070,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>946.412</v>
+        <v>715.95</v>
       </c>
       <c r="C33">
-        <v>758</v>
+        <v>667</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1502,13 +2087,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>1393.733</v>
+        <v>1081.646</v>
       </c>
       <c r="C34">
-        <v>994</v>
+        <v>872</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1519,13 +2104,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>1638.932</v>
+        <v>1260.477</v>
       </c>
       <c r="C35">
-        <v>1252</v>
+        <v>1130</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1536,13 +2121,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>1932.419</v>
+        <v>1446.872</v>
       </c>
       <c r="C36">
-        <v>1488</v>
+        <v>1323</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1553,13 +2138,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>2158.212</v>
+        <v>1605.797</v>
       </c>
       <c r="C37">
-        <v>1723</v>
+        <v>1477</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1570,13 +2155,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>2534.821</v>
+        <v>1877.772</v>
       </c>
       <c r="C38">
-        <v>1960</v>
+        <v>1630</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1587,13 +2172,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>2691.343</v>
+        <v>2015.456</v>
       </c>
       <c r="C39">
-        <v>2125</v>
+        <v>1766</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1604,13 +2189,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>2846.543</v>
+        <v>2144.366</v>
       </c>
       <c r="C40">
-        <v>2280</v>
+        <v>1856</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1621,13 +2206,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>2980.398</v>
+        <v>2248.442</v>
       </c>
       <c r="C41">
-        <v>2418</v>
+        <v>1899</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1638,13 +2223,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>3162.815</v>
+        <v>2406.253</v>
       </c>
       <c r="C42">
-        <v>2496</v>
+        <v>1940</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1655,13 +2240,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>3256.443</v>
+        <v>2483.122</v>
       </c>
       <c r="C43">
-        <v>2586</v>
+        <v>2090</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1672,13 +2257,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>3323.02</v>
+        <v>2540.829</v>
       </c>
       <c r="C44">
-        <v>2655</v>
+        <v>2160</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1689,13 +2274,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>3385.007</v>
+        <v>2588.211</v>
       </c>
       <c r="C45">
-        <v>2696</v>
+        <v>2109</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1706,13 +2291,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>3421.434</v>
+        <v>2639.579</v>
       </c>
       <c r="C46">
-        <v>2744</v>
+        <v>2208</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1723,13 +2308,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>3425.481</v>
+        <v>2668.686</v>
       </c>
       <c r="C47">
-        <v>2798</v>
+        <v>2300</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1740,13 +2325,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>3449.048</v>
+        <v>2684.824</v>
       </c>
       <c r="C48">
-        <v>2772</v>
+        <v>2296</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1757,13 +2342,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>3458.695</v>
+        <v>2699.849</v>
       </c>
       <c r="C49">
-        <v>2717</v>
+        <v>2279</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1774,13 +2359,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>3453.312</v>
+        <v>2699.154</v>
       </c>
       <c r="C50">
-        <v>2725</v>
+        <v>2257</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1791,13 +2376,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>3447.407</v>
+        <v>2695.11</v>
       </c>
       <c r="C51">
-        <v>2737</v>
+        <v>2301</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1808,13 +2393,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>3432.25</v>
+        <v>2683.931</v>
       </c>
       <c r="C52">
-        <v>2815</v>
+        <v>2347</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1825,13 +2410,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>3411.417</v>
+        <v>2659.795</v>
       </c>
       <c r="C53">
-        <v>2850</v>
+        <v>2292</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1842,13 +2427,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>3367.026</v>
+        <v>2615.994</v>
       </c>
       <c r="C54">
-        <v>2834</v>
+        <v>2278</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1859,13 +2444,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>3320.276</v>
+        <v>2578.677</v>
       </c>
       <c r="C55">
-        <v>2804</v>
+        <v>2308</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1876,13 +2461,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>3264.118</v>
+        <v>2534.749</v>
       </c>
       <c r="C56">
-        <v>2748</v>
+        <v>2199</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1893,13 +2478,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>3192.026</v>
+        <v>2476.706</v>
       </c>
       <c r="C57">
-        <v>2676</v>
+        <v>2052</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1910,13 +2495,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>3042.421</v>
+        <v>2333.684</v>
       </c>
       <c r="C58">
-        <v>2541</v>
+        <v>1981</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1927,13 +2512,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>2946.881</v>
+        <v>2233.524</v>
       </c>
       <c r="C59">
-        <v>2459</v>
+        <v>1885</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1944,13 +2529,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>2819.201</v>
+        <v>2102.376</v>
       </c>
       <c r="C60">
-        <v>2320</v>
+        <v>1840</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1961,13 +2546,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>2676.905</v>
+        <v>1972.053</v>
       </c>
       <c r="C61">
-        <v>2213</v>
+        <v>1658</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1978,13 +2563,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>2349.818</v>
+        <v>1680.023</v>
       </c>
       <c r="C62">
-        <v>2019</v>
+        <v>1488</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1995,13 +2580,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>2173.086</v>
+        <v>1518.555</v>
       </c>
       <c r="C63">
-        <v>1797</v>
+        <v>1333</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2012,13 +2597,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>1936.963</v>
+        <v>1351.391</v>
       </c>
       <c r="C64">
-        <v>1566</v>
+        <v>1182</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2029,13 +2614,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>1717.447</v>
+        <v>1193.892</v>
       </c>
       <c r="C65">
-        <v>1393</v>
+        <v>1020</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2046,13 +2631,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>1310.342</v>
+        <v>877.867</v>
       </c>
       <c r="C66">
-        <v>1151</v>
+        <v>794</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2063,13 +2648,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>1063.868</v>
+        <v>712.401</v>
       </c>
       <c r="C67">
-        <v>906</v>
+        <v>678</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2080,13 +2665,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>784.668</v>
+        <v>543.579</v>
       </c>
       <c r="C68">
-        <v>676</v>
+        <v>481</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2097,13 +2682,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>579.869</v>
+        <v>407.269</v>
       </c>
       <c r="C69">
-        <v>470</v>
+        <v>322</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2114,13 +2699,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>292.141</v>
+        <v>194.551</v>
       </c>
       <c r="C70">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2131,13 +2716,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>168.447</v>
+        <v>111.596</v>
       </c>
       <c r="C71">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2148,13 +2733,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>80.754</v>
+        <v>55.187</v>
       </c>
       <c r="C72">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2165,10 +2750,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>44.781</v>
+        <v>36.275</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2182,10 +2767,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>57.467</v>
+        <v>44.085</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2199,10 +2784,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>61.771</v>
+        <v>49.415</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2216,10 +2801,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>61.335</v>
+        <v>55.086</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2233,10 +2818,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>61.285</v>
+        <v>55.178</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2250,10 +2835,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>60.023</v>
+        <v>55.032</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2267,10 +2852,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>56.898</v>
+        <v>54.932</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2284,10 +2869,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>49.623</v>
+        <v>49.632</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2301,10 +2886,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>48.215</v>
+        <v>48.932</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2318,10 +2903,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>41.668</v>
+        <v>40.652</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2335,10 +2920,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>40.468</v>
+        <v>38.052</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2352,10 +2937,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>39.968</v>
+        <v>38.052</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2369,10 +2954,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>37.668</v>
+        <v>41.352</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2386,10 +2971,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>6.268</v>
+        <v>2.152</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2403,10 +2988,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>9.968</v>
+        <v>1.352</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2420,10 +3005,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>10.368</v>
+        <v>1.352</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2437,10 +3022,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>9.868</v>
+        <v>1.352</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2454,10 +3039,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>6.268</v>
+        <v>1.352</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2471,10 +3056,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>6.468</v>
+        <v>1.352</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2488,10 +3073,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>5.668</v>
+        <v>1.352</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2505,10 +3090,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>5.868</v>
+        <v>1.352</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2522,10 +3107,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.468</v>
+        <v>1.352</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2539,10 +3124,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2556,10 +3141,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2573,10 +3158,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2590,7 +3175,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
         <v>1.352</v>
@@ -2607,7 +3192,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
         <v>1.352</v>
@@ -2624,7 +3209,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
         <v>1.352</v>
@@ -2641,7 +3226,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
         <v>1.352</v>
@@ -2658,7 +3243,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
         <v>1.432</v>
@@ -2675,7 +3260,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
         <v>1.432</v>
@@ -2692,7 +3277,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
         <v>1.432</v>
@@ -2709,7 +3294,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
         <v>1.432</v>
@@ -2726,7 +3311,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
         <v>1.432</v>
@@ -2743,7 +3328,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
         <v>1.432</v>
@@ -2760,7 +3345,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
         <v>1.432</v>
@@ -2777,7 +3362,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
         <v>1.432</v>
@@ -2794,7 +3379,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
         <v>1.352</v>
@@ -2811,7 +3396,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
         <v>1.352</v>
@@ -2828,7 +3413,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
         <v>1.352</v>
@@ -2845,7 +3430,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
         <v>1.352</v>
@@ -2862,7 +3447,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
         <v>1.352</v>
@@ -2879,7 +3464,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
         <v>1.352</v>
@@ -2896,7 +3481,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
         <v>1.352</v>
@@ -2913,7 +3498,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
         <v>1.352</v>
@@ -2930,10 +3515,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>5.424</v>
+        <v>1.421</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2947,10 +3532,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>7.745</v>
+        <v>1.449</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2964,10 +3549,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>12.747</v>
+        <v>1.507</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2981,10 +3566,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>15.03</v>
+        <v>1.59</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -2998,10 +3583,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>16.988</v>
+        <v>6.092</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3015,10 +3600,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>18.363</v>
+        <v>6.336</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3032,13 +3617,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>26.633</v>
+        <v>11.055</v>
       </c>
       <c r="C124">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3049,13 +3634,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>79.69199999999999</v>
+        <v>49.465</v>
       </c>
       <c r="C125">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3066,13 +3651,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>292.474</v>
+        <v>237.796</v>
       </c>
       <c r="C126">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3083,13 +3668,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>411.968</v>
+        <v>360.811</v>
       </c>
       <c r="C127">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3100,13 +3685,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>561.978</v>
+        <v>504.326</v>
       </c>
       <c r="C128">
-        <v>506</v>
+        <v>448</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3117,13 +3702,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>715.95</v>
+        <v>658.207</v>
       </c>
       <c r="C129">
-        <v>667</v>
+        <v>583</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3134,13 +3719,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>1081.646</v>
+        <v>1051.35</v>
       </c>
       <c r="C130">
-        <v>872</v>
+        <v>796</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3151,13 +3736,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>1260.477</v>
+        <v>1235.732</v>
       </c>
       <c r="C131">
-        <v>1130</v>
+        <v>941</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3168,13 +3753,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>1446.872</v>
+        <v>1446.327</v>
       </c>
       <c r="C132">
-        <v>1323</v>
+        <v>1079</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3185,10 +3770,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>1605.797</v>
+        <v>1628.141</v>
+      </c>
+      <c r="C133">
+        <v>1210</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3199,10 +3787,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="B134">
-        <v>1877.772</v>
+        <v>1932.716</v>
+      </c>
+      <c r="C134">
+        <v>1365</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3213,10 +3804,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46304.38541666666</v>
+        <v>46305.38541666666</v>
       </c>
       <c r="B135">
-        <v>2015.456</v>
+        <v>2096.54</v>
+      </c>
+      <c r="C135">
+        <v>1525</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3227,10 +3821,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46304.39583333334</v>
+        <v>46305.39583333334</v>
       </c>
       <c r="B136">
-        <v>2144.366</v>
+        <v>2235.367</v>
+      </c>
+      <c r="C136">
+        <v>1624</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3241,10 +3838,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46304.40625</v>
+        <v>46305.40625</v>
       </c>
       <c r="B137">
-        <v>2248.442</v>
+        <v>2351.728</v>
+      </c>
+      <c r="C137">
+        <v>1731</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3255,10 +3855,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46304.41666666666</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="B138">
-        <v>2406.253</v>
+        <v>2514.729</v>
+      </c>
+      <c r="C138">
+        <v>1831</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3269,10 +3872,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46304.42708333334</v>
+        <v>46305.42708333334</v>
       </c>
       <c r="B139">
-        <v>2483.122</v>
+        <v>2599.332</v>
+      </c>
+      <c r="C139">
+        <v>1901</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3283,10 +3889,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46304.4375</v>
+        <v>46305.4375</v>
       </c>
       <c r="B140">
-        <v>2540.829</v>
+        <v>2652.433</v>
+      </c>
+      <c r="C140">
+        <v>2040</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3297,10 +3906,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46304.44791666666</v>
+        <v>46305.44791666666</v>
       </c>
       <c r="B141">
-        <v>2588.211</v>
+        <v>2709.717</v>
+      </c>
+      <c r="C141">
+        <v>2130</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3311,10 +3923,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46304.45833333334</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="B142">
-        <v>2639.579</v>
+        <v>2764.404</v>
+      </c>
+      <c r="C142">
+        <v>2029</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3325,10 +3940,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46304.46875</v>
+        <v>46305.46875</v>
       </c>
       <c r="B143">
-        <v>2668.686</v>
+        <v>2799.423</v>
+      </c>
+      <c r="C143">
+        <v>2124</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3339,10 +3957,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46304.47916666666</v>
+        <v>46305.47916666666</v>
       </c>
       <c r="B144">
-        <v>2684.824</v>
+        <v>2817.119</v>
+      </c>
+      <c r="C144">
+        <v>2049</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3353,10 +3974,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46304.48958333334</v>
+        <v>46305.48958333334</v>
       </c>
       <c r="B145">
-        <v>2699.849</v>
+        <v>2825.443</v>
+      </c>
+      <c r="C145">
+        <v>2061</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3367,10 +3991,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46304.5</v>
+        <v>46305.5</v>
       </c>
       <c r="B146">
-        <v>2699.154</v>
+        <v>2819.028</v>
+      </c>
+      <c r="C146">
+        <v>2217</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3381,10 +4008,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46304.51041666666</v>
+        <v>46305.51041666666</v>
       </c>
       <c r="B147">
-        <v>2695.11</v>
+        <v>2811.989</v>
+      </c>
+      <c r="C147">
+        <v>2191</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3395,10 +4025,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46304.52083333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="B148">
-        <v>2683.931</v>
+        <v>2792.079</v>
+      </c>
+      <c r="C148">
+        <v>2154</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3409,10 +4042,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46304.53125</v>
+        <v>46305.53125</v>
       </c>
       <c r="B149">
-        <v>2659.795</v>
+        <v>2766.57</v>
+      </c>
+      <c r="C149">
+        <v>2161</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3423,10 +4059,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46304.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="B150">
-        <v>2615.994</v>
+        <v>2702.742</v>
+      </c>
+      <c r="C150">
+        <v>2111</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3437,10 +4076,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46304.55208333334</v>
+        <v>46305.55208333334</v>
       </c>
       <c r="B151">
-        <v>2578.677</v>
+        <v>2650.57</v>
+      </c>
+      <c r="C151">
+        <v>2113</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3451,10 +4093,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46304.5625</v>
+        <v>46305.5625</v>
       </c>
       <c r="B152">
-        <v>2534.749</v>
+        <v>2594.567</v>
+      </c>
+      <c r="C152">
+        <v>2069</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3465,10 +4110,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46304.57291666666</v>
+        <v>46305.57291666666</v>
       </c>
       <c r="B153">
-        <v>2476.706</v>
+        <v>2519.222</v>
+      </c>
+      <c r="C153">
+        <v>2003</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3479,10 +4127,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46304.58333333334</v>
+        <v>46305.58333333334</v>
       </c>
       <c r="B154">
-        <v>2333.684</v>
+        <v>2404.944</v>
+      </c>
+      <c r="C154">
+        <v>1902</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3493,10 +4144,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46304.59375</v>
+        <v>46305.59375</v>
       </c>
       <c r="B155">
-        <v>2233.524</v>
+        <v>2295.502</v>
+      </c>
+      <c r="C155">
+        <v>1810</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3507,10 +4161,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46304.60416666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="B156">
-        <v>2102.376</v>
+        <v>2163.746</v>
+      </c>
+      <c r="C156">
+        <v>1740</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3521,10 +4178,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46304.61458333334</v>
+        <v>46305.61458333334</v>
       </c>
       <c r="B157">
-        <v>1972.053</v>
+        <v>2032.367</v>
+      </c>
+      <c r="C157">
+        <v>1654</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3535,10 +4195,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46304.625</v>
+        <v>46305.625</v>
       </c>
       <c r="B158">
-        <v>1680.023</v>
+        <v>1781.321</v>
+      </c>
+      <c r="C158">
+        <v>1523</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3549,10 +4212,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46304.63541666666</v>
+        <v>46305.63541666666</v>
       </c>
       <c r="B159">
-        <v>1518.555</v>
+        <v>1608.768</v>
+      </c>
+      <c r="C159">
+        <v>1367</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3563,10 +4229,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46304.64583333334</v>
+        <v>46305.64583333334</v>
       </c>
       <c r="B160">
-        <v>1351.391</v>
+        <v>1419.464</v>
+      </c>
+      <c r="C160">
+        <v>1237</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3577,10 +4246,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46304.65625</v>
+        <v>46305.65625</v>
       </c>
       <c r="B161">
-        <v>1193.892</v>
+        <v>1233.652</v>
+      </c>
+      <c r="C161">
+        <v>1079</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3591,10 +4263,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46304.66666666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="B162">
-        <v>877.867</v>
+        <v>914.783</v>
+      </c>
+      <c r="C162">
+        <v>851</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3605,10 +4280,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46304.67708333334</v>
+        <v>46305.67708333334</v>
       </c>
       <c r="B163">
-        <v>712.401</v>
+        <v>721.515</v>
+      </c>
+      <c r="C163">
+        <v>648</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3619,10 +4297,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46304.6875</v>
+        <v>46305.6875</v>
       </c>
       <c r="B164">
-        <v>543.579</v>
+        <v>547.9059999999999</v>
+      </c>
+      <c r="C164">
+        <v>483</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3633,10 +4314,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46304.69791666666</v>
+        <v>46305.69791666666</v>
       </c>
       <c r="B165">
-        <v>407.269</v>
+        <v>400.639</v>
+      </c>
+      <c r="C165">
+        <v>311</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3647,10 +4331,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46304.70833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="B166">
-        <v>194.551</v>
+        <v>195.426</v>
+      </c>
+      <c r="C166">
+        <v>136</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3661,10 +4348,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46304.71875</v>
+        <v>46305.71875</v>
       </c>
       <c r="B167">
-        <v>111.596</v>
+        <v>106.857</v>
+      </c>
+      <c r="C167">
+        <v>41</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3675,10 +4365,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46304.72916666666</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="B168">
-        <v>55.187</v>
+        <v>46.54</v>
+      </c>
+      <c r="C168">
+        <v>3</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3689,10 +4382,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46304.73958333334</v>
+        <v>46305.73958333334</v>
       </c>
       <c r="B169">
-        <v>36.275</v>
+        <v>30.556</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3703,10 +4399,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46304.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B170">
-        <v>44.085</v>
+        <v>17.865</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3717,10 +4416,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46304.76041666666</v>
+        <v>46305.76041666666</v>
       </c>
       <c r="B171">
-        <v>49.415</v>
+        <v>65.611</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3731,10 +4433,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46304.77083333334</v>
+        <v>46305.77083333334</v>
       </c>
       <c r="B172">
-        <v>55.086</v>
+        <v>65.595</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3745,10 +4450,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46304.78125</v>
+        <v>46305.78125</v>
       </c>
       <c r="B173">
-        <v>55.178</v>
+        <v>64.79900000000001</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3759,10 +4467,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46304.79166666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="B174">
-        <v>55.032</v>
+        <v>70.34099999999999</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3773,10 +4484,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46304.80208333334</v>
+        <v>46305.80208333334</v>
       </c>
       <c r="B175">
-        <v>54.932</v>
+        <v>70.241</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3787,10 +4501,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46304.8125</v>
+        <v>46305.8125</v>
       </c>
       <c r="B176">
-        <v>49.632</v>
+        <v>66.741</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3801,10 +4518,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46304.82291666666</v>
+        <v>46305.82291666666</v>
       </c>
       <c r="B177">
-        <v>48.932</v>
+        <v>66.041</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3815,10 +4535,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46304.83333333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="B178">
-        <v>40.652</v>
+        <v>59.656</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3829,10 +4552,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46304.84375</v>
+        <v>46305.84375</v>
       </c>
       <c r="B179">
-        <v>38.052</v>
+        <v>10.056</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3843,10 +4569,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46304.85416666666</v>
+        <v>46305.85416666666</v>
       </c>
       <c r="B180">
-        <v>38.052</v>
+        <v>7.756</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3857,10 +4586,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46304.86458333334</v>
+        <v>46305.86458333334</v>
       </c>
       <c r="B181">
-        <v>41.352</v>
+        <v>7.156</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3871,10 +4603,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46304.875</v>
+        <v>46305.875</v>
       </c>
       <c r="B182">
-        <v>2.152</v>
+        <v>8.156000000000001</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3885,16 +4620,3181 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46304.88541666666</v>
+        <v>46305.88541666666</v>
       </c>
       <c r="B183">
-        <v>1.352</v>
+        <v>13.856</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
       </c>
       <c r="D183">
         <v>86</v>
       </c>
       <c r="E183" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>46305.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>13.852</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>87</v>
+      </c>
+      <c r="E184" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46305.90625</v>
+      </c>
+      <c r="B185">
+        <v>13.852</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>13.852</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46305.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>13.852</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46305.9375</v>
+      </c>
+      <c r="B188">
+        <v>7.352</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46305.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>7.352</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>1.352</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46305.96875</v>
+      </c>
+      <c r="B191">
+        <v>1.352</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>1.352</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46305.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>1.352</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>2.152</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>2.152</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1.352</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>1.352</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1.432</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1.432</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>1.432</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1.432</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1.432</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>1.432</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1.432</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1.432</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>1.352</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1.352</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1.352</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>1.352</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1.352</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1.352</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>1.352</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1.352</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1.437</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>1.529</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1.621</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>1.715</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>8.355</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>7.317</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>14.357</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>47.47</v>
+      </c>
+      <c r="C221">
+        <v>38</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>231.213</v>
+      </c>
+      <c r="C222">
+        <v>127</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>336.97</v>
+      </c>
+      <c r="C223">
+        <v>239</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>467.553</v>
+      </c>
+      <c r="C224">
+        <v>359</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>591.511</v>
+      </c>
+      <c r="C225">
+        <v>508</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>877.593</v>
+      </c>
+      <c r="C226">
+        <v>680</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>1030.647</v>
+      </c>
+      <c r="C227">
+        <v>838</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1188.451</v>
+      </c>
+      <c r="C228">
+        <v>1004</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1324.713</v>
+      </c>
+      <c r="C229">
+        <v>1112</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>1593.105</v>
+      </c>
+      <c r="C230">
+        <v>1227</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1705.187</v>
+      </c>
+      <c r="C231">
+        <v>1334</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1801.968</v>
+      </c>
+      <c r="C232">
+        <v>1409</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>1891.282</v>
+      </c>
+      <c r="C233">
+        <v>1471</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1996.168</v>
+      </c>
+      <c r="C234">
+        <v>1524</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2059.594</v>
+      </c>
+      <c r="C235">
+        <v>1530</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>2112.753</v>
+      </c>
+      <c r="C236">
+        <v>1451</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2162.464</v>
+      </c>
+      <c r="C237">
+        <v>1461</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2185.548</v>
+      </c>
+      <c r="C238">
+        <v>1477</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>2204.952</v>
+      </c>
+      <c r="C239">
+        <v>1520</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2214.57</v>
+      </c>
+      <c r="C240">
+        <v>1556</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2219.504</v>
+      </c>
+      <c r="C241">
+        <v>1533</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>2188.184</v>
+      </c>
+      <c r="C242">
+        <v>1577</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>2172.547</v>
+      </c>
+      <c r="C243">
+        <v>1574</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>2143.04</v>
+      </c>
+      <c r="C244">
+        <v>1532</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>2103.704</v>
+      </c>
+      <c r="C245">
+        <v>1540</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>2030.277</v>
+      </c>
+      <c r="C246">
+        <v>1530</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1967.616</v>
+      </c>
+      <c r="C247">
+        <v>1462</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>1897.265</v>
+      </c>
+      <c r="C248">
+        <v>1372</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1821.99</v>
+      </c>
+      <c r="C249">
+        <v>1241</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1681.607</v>
+      </c>
+      <c r="C250">
+        <v>1176</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>1593.426</v>
+      </c>
+      <c r="C251">
+        <v>1096</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1495.377</v>
+      </c>
+      <c r="C252">
+        <v>899</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1387.245</v>
+      </c>
+      <c r="C253">
+        <v>808</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>1155.184</v>
+      </c>
+      <c r="C254">
+        <v>792</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1022.424</v>
+      </c>
+      <c r="C255">
+        <v>698</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>888.968</v>
+      </c>
+      <c r="C256">
+        <v>604</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>760.855</v>
+      </c>
+      <c r="C257">
+        <v>522</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>519.717</v>
+      </c>
+      <c r="C258">
+        <v>404</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>402.631</v>
+      </c>
+      <c r="C259">
+        <v>300</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>301.524</v>
+      </c>
+      <c r="C260">
+        <v>202</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>219.915</v>
+      </c>
+      <c r="C261">
+        <v>141</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>89.599</v>
+      </c>
+      <c r="C262">
+        <v>63</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>47.334</v>
+      </c>
+      <c r="C263">
+        <v>11</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>25.687</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>20.125</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>11.735</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>16.564</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>15.864</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>16.144</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>13.44</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>9.496</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>3.456</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>2.856</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>3.456</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>3.456</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>2.156</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>2.156</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1.352</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>1.352</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1.352</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>1.352</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>1.352</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>1.352</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1.352</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>1.352</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1.352</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1.352</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>0.952</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>1.752</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0.952</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>0.952</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>1.032</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>1.032</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>1.032</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>1.032</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>1.032</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>1.032</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>1.032</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>1.032</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>0.952</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0.952</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0.952</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>0.952</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0.952</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0.952</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>0.952</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0.952</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>1.501</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>1.349</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>1.945</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>2.816</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>6.161</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>8.832000000000001</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>26</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>32.567</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>108.209</v>
+      </c>
+      <c r="C318">
+        <v>23</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>140.421</v>
+      </c>
+      <c r="C319">
+        <v>66</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>180.709</v>
+      </c>
+      <c r="C320">
+        <v>122</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>236.469</v>
+      </c>
+      <c r="C321">
+        <v>180</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>360.811</v>
+      </c>
+      <c r="C322">
+        <v>252</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>410.067</v>
+      </c>
+      <c r="C323">
+        <v>315</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>494.079</v>
+      </c>
+      <c r="C324">
+        <v>398</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>544.504</v>
+      </c>
+      <c r="C325">
+        <v>461</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>651.726</v>
+      </c>
+      <c r="C326">
+        <v>547</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>708.309</v>
+      </c>
+      <c r="C327">
+        <v>594</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>770.194</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46307.40625</v>
+      </c>
+      <c r="B329">
+        <v>809.772</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>881.1180000000001</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46307.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>900.997</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46307.4375</v>
+      </c>
+      <c r="B332">
+        <v>929.372</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46307.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>952.203</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>995.523</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46307.46875</v>
+      </c>
+      <c r="B335">
+        <v>1011.613</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46307.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>1022.468</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46307.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>1021.363</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46307.5</v>
+      </c>
+      <c r="B338">
+        <v>1022.097</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46307.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1015.636</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46307.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1005.446</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46307.53125</v>
+      </c>
+      <c r="B341">
+        <v>990.543</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>951.353</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46307.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>930.3049999999999</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46307.5625</v>
+      </c>
+      <c r="B344">
+        <v>899.8</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46307.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>862.749</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>790.364</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46307.59375</v>
+      </c>
+      <c r="B347">
+        <v>736.884</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>686.338</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46307.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>638.347</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46307.625</v>
+      </c>
+      <c r="B350">
+        <v>556.192</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46307.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>484.935</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46307.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>431.821</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46307.65625</v>
+      </c>
+      <c r="B353">
+        <v>397.364</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>271.685</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46307.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>226.003</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46307.6875</v>
+      </c>
+      <c r="B356">
+        <v>181.263</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46307.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>146.463</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>67.40300000000001</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46307.71875</v>
+      </c>
+      <c r="B359">
+        <v>46.452</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46307.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>39.498</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46307.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>65.842</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46307.75</v>
+      </c>
+      <c r="B362">
+        <v>44.603</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46307.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>44.473</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46307.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>54.469</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46307.78125</v>
+      </c>
+      <c r="B365">
+        <v>56.569</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46307.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>53.132</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46307.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>49.232</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46307.8125</v>
+      </c>
+      <c r="B368">
+        <v>48.732</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46307.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>47.832</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46307.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>45.552</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46307.84375</v>
+      </c>
+      <c r="B371">
+        <v>1.952</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46307.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0.952</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46307.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>2.552</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46307.875</v>
+      </c>
+      <c r="B374">
+        <v>0.952</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46307.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>2.152</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46307.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>2.952</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46307.90625</v>
+      </c>
+      <c r="B377">
+        <v>4.552</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0.952</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -584,6 +296,294 @@
   </si>
   <si>
     <t>13.10.202689</t>
+  </si>
+  <si>
+    <t>13.10.202690</t>
+  </si>
+  <si>
+    <t>13.10.202691</t>
+  </si>
+  <si>
+    <t>13.10.202692</t>
+  </si>
+  <si>
+    <t>13.10.202693</t>
+  </si>
+  <si>
+    <t>13.10.202694</t>
+  </si>
+  <si>
+    <t>13.10.202695</t>
+  </si>
+  <si>
+    <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
+  </si>
+  <si>
+    <t>14.10.202660</t>
+  </si>
+  <si>
+    <t>14.10.202661</t>
+  </si>
+  <si>
+    <t>14.10.202662</t>
+  </si>
+  <si>
+    <t>14.10.202663</t>
+  </si>
+  <si>
+    <t>14.10.202664</t>
+  </si>
+  <si>
+    <t>14.10.202665</t>
+  </si>
+  <si>
+    <t>14.10.202666</t>
+  </si>
+  <si>
+    <t>14.10.202667</t>
+  </si>
+  <si>
+    <t>14.10.202668</t>
+  </si>
+  <si>
+    <t>14.10.202669</t>
+  </si>
+  <si>
+    <t>14.10.202670</t>
+  </si>
+  <si>
+    <t>14.10.202671</t>
+  </si>
+  <si>
+    <t>14.10.202672</t>
+  </si>
+  <si>
+    <t>14.10.202673</t>
+  </si>
+  <si>
+    <t>14.10.202674</t>
+  </si>
+  <si>
+    <t>14.10.202675</t>
+  </si>
+  <si>
+    <t>14.10.202676</t>
+  </si>
+  <si>
+    <t>14.10.202677</t>
+  </si>
+  <si>
+    <t>14.10.202678</t>
+  </si>
+  <si>
+    <t>14.10.202679</t>
+  </si>
+  <si>
+    <t>14.10.202680</t>
+  </si>
+  <si>
+    <t>14.10.202681</t>
+  </si>
+  <si>
+    <t>14.10.202682</t>
+  </si>
+  <si>
+    <t>14.10.202683</t>
+  </si>
+  <si>
+    <t>14.10.202684</t>
+  </si>
+  <si>
+    <t>14.10.202685</t>
+  </si>
+  <si>
+    <t>14.10.202686</t>
+  </si>
+  <si>
+    <t>14.10.202687</t>
+  </si>
+  <si>
+    <t>14.10.202688</t>
+  </si>
+  <si>
+    <t>14.10.202689</t>
   </si>
 </sst>
 </file>
@@ -967,10 +967,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.752</v>
+        <v>1.252</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1069,10 +1069,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.501</v>
+        <v>1.289</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>1.349</v>
+        <v>1.325</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.945</v>
+        <v>1.914</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.816</v>
+        <v>2.745</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>6.161</v>
+        <v>4.824</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>8.832000000000001</v>
+        <v>6.366</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>17.871</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>32.567</v>
+        <v>25.786</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1443,13 +1443,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>108.209</v>
+        <v>79.893</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>140.421</v>
+        <v>114.57</v>
       </c>
       <c r="C31">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>180.709</v>
+        <v>166.381</v>
       </c>
       <c r="C32">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>236.469</v>
+        <v>221.631</v>
       </c>
       <c r="C33">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1511,13 +1511,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>360.811</v>
+        <v>339.799</v>
       </c>
       <c r="C34">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>410.067</v>
+        <v>413.717</v>
       </c>
       <c r="C35">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1545,13 +1545,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>494.079</v>
+        <v>504.761</v>
       </c>
       <c r="C36">
-        <v>398</v>
+        <v>487</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>544.504</v>
+        <v>579.575</v>
       </c>
       <c r="C37">
-        <v>461</v>
+        <v>583</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1579,13 +1579,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>651.726</v>
+        <v>688.427</v>
       </c>
       <c r="C38">
-        <v>547</v>
+        <v>689</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1596,13 +1596,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>708.309</v>
+        <v>767.3680000000001</v>
       </c>
       <c r="C39">
-        <v>594</v>
+        <v>772</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>770.194</v>
+        <v>832.1319999999999</v>
       </c>
       <c r="C40">
-        <v>684</v>
+        <v>842</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1630,13 +1630,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>809.772</v>
+        <v>894.4930000000001</v>
       </c>
       <c r="C41">
-        <v>741</v>
+        <v>944</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>881.1180000000001</v>
+        <v>997.547</v>
       </c>
       <c r="C42">
-        <v>797</v>
+        <v>989</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1664,13 +1664,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>900.997</v>
+        <v>1050.877</v>
       </c>
       <c r="C43">
-        <v>847</v>
+        <v>1037</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1681,13 +1681,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>929.372</v>
+        <v>1094.422</v>
       </c>
       <c r="C44">
-        <v>883</v>
+        <v>1103</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>952.203</v>
+        <v>1134.253</v>
       </c>
       <c r="C45">
-        <v>914</v>
+        <v>1199</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1715,13 +1715,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>995.523</v>
+        <v>1189.527</v>
       </c>
       <c r="C46">
-        <v>888</v>
+        <v>1288</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1732,13 +1732,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>1011.613</v>
+        <v>1206.592</v>
       </c>
       <c r="C47">
-        <v>919</v>
+        <v>1402</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1749,13 +1749,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>1022.468</v>
+        <v>1221.036</v>
       </c>
       <c r="C48">
-        <v>972</v>
+        <v>1501</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1766,13 +1766,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>1021.363</v>
+        <v>1226.241</v>
       </c>
       <c r="C49">
-        <v>963</v>
+        <v>1520</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1783,13 +1783,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>1022.097</v>
+        <v>1244.579</v>
       </c>
       <c r="C50">
-        <v>990</v>
+        <v>1536</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1800,13 +1800,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>1015.636</v>
+        <v>1234.617</v>
       </c>
       <c r="C51">
-        <v>954</v>
+        <v>1529</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1817,13 +1817,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>1005.446</v>
+        <v>1221.321</v>
       </c>
       <c r="C52">
-        <v>949</v>
+        <v>1462</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1834,13 +1834,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>990.543</v>
+        <v>1205.113</v>
       </c>
       <c r="C53">
-        <v>951</v>
+        <v>1375</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1851,13 +1851,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>951.353</v>
+        <v>1172.049</v>
       </c>
       <c r="C54">
-        <v>947</v>
+        <v>1235</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>930.3049999999999</v>
+        <v>1142.258</v>
       </c>
       <c r="C55">
-        <v>912</v>
+        <v>1224</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1885,13 +1885,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>899.8</v>
+        <v>1108.29</v>
       </c>
       <c r="C56">
-        <v>894</v>
+        <v>1183</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>862.749</v>
+        <v>1062.624</v>
       </c>
       <c r="C57">
-        <v>853</v>
+        <v>1099</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1919,13 +1919,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>790.364</v>
+        <v>982.692</v>
       </c>
       <c r="C58">
-        <v>752</v>
+        <v>1001</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1936,13 +1936,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>736.884</v>
+        <v>939.6420000000001</v>
       </c>
       <c r="C59">
-        <v>681</v>
+        <v>956</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1953,13 +1953,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>686.338</v>
+        <v>878.764</v>
       </c>
       <c r="C60">
-        <v>650</v>
+        <v>985</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>638.347</v>
+        <v>830.458</v>
       </c>
       <c r="C61">
-        <v>587</v>
+        <v>850</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>556.192</v>
+        <v>689.139</v>
       </c>
       <c r="C62">
-        <v>515</v>
+        <v>830</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2004,13 +2004,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>484.935</v>
+        <v>617.178</v>
       </c>
       <c r="C63">
-        <v>459</v>
+        <v>664</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2021,13 +2021,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>431.821</v>
+        <v>550.561</v>
       </c>
       <c r="C64">
-        <v>409</v>
+        <v>591</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2038,13 +2038,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>397.364</v>
+        <v>473.79</v>
       </c>
       <c r="C65">
-        <v>340</v>
+        <v>520</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2055,13 +2055,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>271.685</v>
+        <v>350.573</v>
       </c>
       <c r="C66">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2072,13 +2072,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>226.003</v>
+        <v>287.091</v>
       </c>
       <c r="C67">
-        <v>201</v>
+        <v>346</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>181.263</v>
+        <v>221.64</v>
       </c>
       <c r="C68">
-        <v>141</v>
+        <v>276</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>146.463</v>
+        <v>166.727</v>
       </c>
       <c r="C69">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2123,13 +2123,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>67.40300000000001</v>
+        <v>87.72</v>
       </c>
       <c r="C70">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2140,13 +2140,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>46.452</v>
+        <v>59.464</v>
       </c>
       <c r="C71">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>39.498</v>
+        <v>39.771</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>65.842</v>
+        <v>34.298</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>44.603</v>
+        <v>46.348</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>44.473</v>
+        <v>56.29</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>54.469</v>
+        <v>56.574</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>56.569</v>
+        <v>55.174</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>53.132</v>
+        <v>54.032</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>49.232</v>
+        <v>51.132</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>48.732</v>
+        <v>49.732</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>47.832</v>
+        <v>50.632</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>45.552</v>
+        <v>19.852</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>1.952</v>
+        <v>19.152</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.952</v>
+        <v>21.352</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.552</v>
+        <v>21.152</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>0.952</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>2.152</v>
+        <v>21.052</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.952</v>
+        <v>3.252</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>4.552</v>
+        <v>4.052</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
         <v>1.252</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
         <v>1.252</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
         <v>1.252</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
         <v>1.252</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.332</v>
+        <v>1.668</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>1.332</v>
+        <v>1.668</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.332</v>
+        <v>1.568</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2752,10 +2752,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.332</v>
+        <v>2.768</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.252</v>
+        <v>1.388</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.289</v>
+        <v>1.533</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>1.325</v>
+        <v>1.269</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>1.914</v>
+        <v>1.983</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.745</v>
+        <v>3.766</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>4.824</v>
+        <v>9.045</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>6.366</v>
+        <v>12.64</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>17.871</v>
+        <v>18.433</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3058,13 +3058,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>25.786</v>
+        <v>35.339</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3075,13 +3075,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>79.893</v>
+        <v>158.95</v>
       </c>
       <c r="C126">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3092,13 +3092,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>114.57</v>
+        <v>250.122</v>
       </c>
       <c r="C127">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3109,13 +3109,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>166.381</v>
+        <v>351.868</v>
       </c>
       <c r="C128">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3126,13 +3126,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>221.631</v>
+        <v>460.851</v>
       </c>
       <c r="C129">
-        <v>207</v>
+        <v>411</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3143,13 +3143,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>339.799</v>
+        <v>729.88</v>
       </c>
       <c r="C130">
-        <v>305</v>
+        <v>563</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3160,13 +3160,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>413.717</v>
+        <v>883.856</v>
       </c>
       <c r="C131">
-        <v>405</v>
+        <v>705</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3177,13 +3177,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>504.761</v>
+        <v>1044.98</v>
       </c>
       <c r="C132">
-        <v>487</v>
+        <v>915</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3194,13 +3194,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>579.575</v>
+        <v>1190.297</v>
       </c>
       <c r="C133">
-        <v>583</v>
+        <v>1111</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3211,13 +3211,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>688.427</v>
+        <v>1466.624</v>
       </c>
       <c r="C134">
-        <v>689</v>
+        <v>1261</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3228,13 +3228,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>767.3680000000001</v>
+        <v>1619.946</v>
       </c>
       <c r="C135">
-        <v>772</v>
+        <v>1384</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3245,13 +3245,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>832.1319999999999</v>
+        <v>1745.661</v>
       </c>
       <c r="C136">
-        <v>842</v>
+        <v>1497</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3262,13 +3262,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>894.4930000000001</v>
+        <v>1863.256</v>
       </c>
       <c r="C137">
-        <v>944</v>
+        <v>1653</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3279,13 +3279,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>997.547</v>
+        <v>2076.265</v>
       </c>
       <c r="C138">
-        <v>989</v>
+        <v>1829</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3296,13 +3296,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>1050.877</v>
+        <v>2159.4</v>
       </c>
       <c r="C139">
-        <v>1037</v>
+        <v>2016</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3313,13 +3313,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>1094.422</v>
+        <v>2230.061</v>
       </c>
       <c r="C140">
-        <v>1103</v>
+        <v>2084</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3330,13 +3330,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>1134.253</v>
+        <v>2299.546</v>
       </c>
       <c r="C141">
-        <v>1199</v>
+        <v>2182</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3347,13 +3347,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>1189.527</v>
+        <v>2400.656</v>
       </c>
       <c r="C142">
-        <v>1288</v>
+        <v>2179</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3364,13 +3364,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>1206.592</v>
+        <v>2440.426</v>
       </c>
       <c r="C143">
-        <v>1402</v>
+        <v>2294</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3381,13 +3381,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>1221.036</v>
+        <v>2471.592</v>
       </c>
       <c r="C144">
-        <v>1501</v>
+        <v>2311</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3398,13 +3398,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>1226.241</v>
+        <v>2486.946</v>
       </c>
       <c r="C145">
-        <v>1520</v>
+        <v>2196</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>1244.579</v>
+        <v>2519.963</v>
       </c>
       <c r="C146">
-        <v>1536</v>
+        <v>2155</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3432,13 +3432,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>1234.617</v>
+        <v>2520.073</v>
       </c>
       <c r="C147">
-        <v>1529</v>
+        <v>2235</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3449,13 +3449,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>1221.321</v>
+        <v>2517.328</v>
       </c>
       <c r="C148">
-        <v>1462</v>
+        <v>2241</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3466,13 +3466,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>1205.113</v>
+        <v>2502.531</v>
       </c>
       <c r="C149">
-        <v>1375</v>
+        <v>2182</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3483,13 +3483,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>1172.049</v>
+        <v>2477.756</v>
       </c>
       <c r="C150">
-        <v>1235</v>
+        <v>2194</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3500,13 +3500,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>1142.258</v>
+        <v>2442.452</v>
       </c>
       <c r="C151">
-        <v>1224</v>
+        <v>2199</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3517,10 +3517,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>1108.29</v>
+        <v>2415.764</v>
+      </c>
+      <c r="C152">
+        <v>2236</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3531,10 +3534,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B153">
-        <v>1062.624</v>
+        <v>2362.7</v>
+      </c>
+      <c r="C153">
+        <v>2196</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3545,10 +3551,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B154">
-        <v>982.692</v>
+        <v>2245.56</v>
+      </c>
+      <c r="C154">
+        <v>2133</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3559,10 +3568,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B155">
-        <v>939.6420000000001</v>
+        <v>2158.203</v>
+      </c>
+      <c r="C155">
+        <v>2138</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3573,10 +3585,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B156">
-        <v>878.764</v>
+        <v>2062.563</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3587,10 +3599,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B157">
-        <v>830.458</v>
+        <v>1948.063</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3601,10 +3613,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B158">
-        <v>689.139</v>
+        <v>1683.591</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3615,10 +3627,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B159">
-        <v>617.178</v>
+        <v>1523.397</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3629,10 +3641,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B160">
-        <v>550.561</v>
+        <v>1346.441</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3643,10 +3655,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B161">
-        <v>473.79</v>
+        <v>1175.368</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3657,10 +3669,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B162">
-        <v>350.573</v>
+        <v>864.7329999999999</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3671,10 +3683,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B163">
-        <v>287.091</v>
+        <v>692.068</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3685,10 +3697,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B164">
-        <v>221.64</v>
+        <v>510.233</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3699,10 +3711,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B165">
-        <v>166.727</v>
+        <v>363.688</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3713,10 +3725,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B166">
-        <v>87.72</v>
+        <v>210.057</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3727,10 +3739,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B167">
-        <v>59.464</v>
+        <v>124.612</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3741,10 +3753,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B168">
-        <v>39.771</v>
+        <v>85.84</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3755,10 +3767,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B169">
-        <v>34.298</v>
+        <v>72.8</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3769,10 +3781,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B170">
-        <v>46.348</v>
+        <v>49.344</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3783,10 +3795,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B171">
-        <v>56.29</v>
+        <v>55.366</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3797,10 +3809,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B172">
-        <v>56.574</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3811,10 +3823,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B173">
-        <v>55.174</v>
+        <v>68.53400000000001</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3825,10 +3837,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B174">
-        <v>54.032</v>
+        <v>52.568</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3839,10 +3851,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B175">
-        <v>51.132</v>
+        <v>68.16800000000001</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3853,10 +3865,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B176">
-        <v>49.732</v>
+        <v>63.368</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3867,10 +3879,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B177">
-        <v>50.632</v>
+        <v>61.068</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3881,10 +3893,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B178">
-        <v>19.852</v>
+        <v>51.688</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3895,10 +3907,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B179">
-        <v>19.152</v>
+        <v>16.688</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3909,10 +3921,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B180">
-        <v>21.352</v>
+        <v>3.588</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3923,10 +3935,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B181">
-        <v>21.152</v>
+        <v>3.988</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3937,10 +3949,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B182">
-        <v>9.651999999999999</v>
+        <v>14.288</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3951,10 +3963,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B183">
-        <v>21.052</v>
+        <v>4.788</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3965,10 +3977,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B184">
-        <v>3.252</v>
+        <v>3.588</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3979,10 +3991,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B185">
-        <v>4.052</v>
+        <v>4.788</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3993,10 +4005,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
       <c r="D186">
         <v>89</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,559 +31,559 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
-  </si>
-  <si>
-    <t>14.10.202660</t>
-  </si>
-  <si>
-    <t>14.10.202661</t>
-  </si>
-  <si>
-    <t>14.10.202662</t>
-  </si>
-  <si>
-    <t>14.10.202663</t>
-  </si>
-  <si>
-    <t>14.10.202664</t>
-  </si>
-  <si>
-    <t>14.10.202665</t>
-  </si>
-  <si>
-    <t>14.10.202666</t>
-  </si>
-  <si>
-    <t>14.10.202667</t>
-  </si>
-  <si>
-    <t>14.10.202668</t>
-  </si>
-  <si>
-    <t>14.10.202669</t>
-  </si>
-  <si>
-    <t>14.10.202670</t>
-  </si>
-  <si>
-    <t>14.10.202671</t>
-  </si>
-  <si>
-    <t>14.10.202672</t>
-  </si>
-  <si>
-    <t>14.10.202673</t>
-  </si>
-  <si>
-    <t>14.10.202674</t>
-  </si>
-  <si>
-    <t>14.10.202675</t>
-  </si>
-  <si>
-    <t>14.10.202676</t>
-  </si>
-  <si>
-    <t>14.10.202677</t>
-  </si>
-  <si>
-    <t>14.10.202678</t>
-  </si>
-  <si>
-    <t>14.10.202679</t>
-  </si>
-  <si>
-    <t>14.10.202680</t>
-  </si>
-  <si>
-    <t>14.10.202681</t>
-  </si>
-  <si>
-    <t>14.10.202682</t>
-  </si>
-  <si>
-    <t>14.10.202683</t>
-  </si>
-  <si>
-    <t>14.10.202684</t>
-  </si>
-  <si>
-    <t>14.10.202685</t>
-  </si>
-  <si>
-    <t>14.10.202686</t>
-  </si>
-  <si>
-    <t>14.10.202687</t>
-  </si>
-  <si>
-    <t>14.10.202688</t>
-  </si>
-  <si>
-    <t>14.10.202689</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
+  </si>
+  <si>
+    <t>16.10.202653</t>
+  </si>
+  <si>
+    <t>16.10.202654</t>
+  </si>
+  <si>
+    <t>16.10.202655</t>
+  </si>
+  <si>
+    <t>16.10.202656</t>
+  </si>
+  <si>
+    <t>16.10.202657</t>
+  </si>
+  <si>
+    <t>16.10.202658</t>
+  </si>
+  <si>
+    <t>16.10.202659</t>
+  </si>
+  <si>
+    <t>16.10.202660</t>
+  </si>
+  <si>
+    <t>16.10.202661</t>
+  </si>
+  <si>
+    <t>16.10.202662</t>
+  </si>
+  <si>
+    <t>16.10.202663</t>
+  </si>
+  <si>
+    <t>16.10.202664</t>
+  </si>
+  <si>
+    <t>16.10.202665</t>
+  </si>
+  <si>
+    <t>16.10.202666</t>
+  </si>
+  <si>
+    <t>16.10.202667</t>
+  </si>
+  <si>
+    <t>16.10.202668</t>
+  </si>
+  <si>
+    <t>16.10.202669</t>
+  </si>
+  <si>
+    <t>16.10.202670</t>
+  </si>
+  <si>
+    <t>16.10.202671</t>
+  </si>
+  <si>
+    <t>16.10.202672</t>
+  </si>
+  <si>
+    <t>16.10.202673</t>
+  </si>
+  <si>
+    <t>16.10.202674</t>
+  </si>
+  <si>
+    <t>16.10.202675</t>
+  </si>
+  <si>
+    <t>16.10.202676</t>
+  </si>
+  <si>
+    <t>16.10.202677</t>
+  </si>
+  <si>
+    <t>16.10.202678</t>
+  </si>
+  <si>
+    <t>16.10.202679</t>
+  </si>
+  <si>
+    <t>16.10.202680</t>
+  </si>
+  <si>
+    <t>16.10.202681</t>
+  </si>
+  <si>
+    <t>16.10.202682</t>
+  </si>
+  <si>
+    <t>16.10.202683</t>
+  </si>
+  <si>
+    <t>16.10.202684</t>
+  </si>
+  <si>
+    <t>16.10.202685</t>
+  </si>
+  <si>
+    <t>16.10.202686</t>
+  </si>
+  <si>
+    <t>16.10.202687</t>
+  </si>
+  <si>
+    <t>16.10.202688</t>
+  </si>
+  <si>
+    <t>16.10.202689</t>
   </si>
 </sst>
 </file>
@@ -967,10 +967,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.252</v>
+        <v>4.88</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1069,10 +1069,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.332</v>
+        <v>1.16</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.289</v>
+        <v>7.078</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>1.325</v>
+        <v>7.094</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.914</v>
+        <v>7.359</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.745</v>
+        <v>7.787</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>4.824</v>
+        <v>12.519</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.366</v>
+        <v>13.484</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1409,13 +1409,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>17.871</v>
+        <v>16.843</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1426,13 +1426,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>25.786</v>
+        <v>34.053</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1443,13 +1443,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>79.893</v>
+        <v>171.801</v>
       </c>
       <c r="C30">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>114.57</v>
+        <v>260.132</v>
       </c>
       <c r="C31">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>166.381</v>
+        <v>361.61</v>
       </c>
       <c r="C32">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>221.631</v>
+        <v>470.654</v>
       </c>
       <c r="C33">
-        <v>207</v>
+        <v>514</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1511,13 +1511,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>339.799</v>
+        <v>760.75</v>
       </c>
       <c r="C34">
-        <v>305</v>
+        <v>650</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>413.717</v>
+        <v>891.24</v>
       </c>
       <c r="C35">
-        <v>405</v>
+        <v>858</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1545,13 +1545,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>504.761</v>
+        <v>1042.068</v>
       </c>
       <c r="C36">
-        <v>487</v>
+        <v>1061</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>579.575</v>
+        <v>1172.924</v>
       </c>
       <c r="C37">
-        <v>583</v>
+        <v>1170</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1579,13 +1579,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>688.427</v>
+        <v>1416.652</v>
       </c>
       <c r="C38">
-        <v>689</v>
+        <v>1277</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1596,13 +1596,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>767.3680000000001</v>
+        <v>1545.088</v>
       </c>
       <c r="C39">
-        <v>772</v>
+        <v>1280</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>832.1319999999999</v>
+        <v>1677.582</v>
       </c>
       <c r="C40">
-        <v>842</v>
+        <v>1443</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1630,13 +1630,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>894.4930000000001</v>
+        <v>1766.061</v>
       </c>
       <c r="C41">
-        <v>944</v>
+        <v>1448</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>997.547</v>
+        <v>1881.831</v>
       </c>
       <c r="C42">
-        <v>989</v>
+        <v>1387</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1664,13 +1664,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>1050.877</v>
+        <v>1966.715</v>
       </c>
       <c r="C43">
-        <v>1037</v>
+        <v>1417</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1681,13 +1681,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>1094.422</v>
+        <v>2043.585</v>
       </c>
       <c r="C44">
-        <v>1103</v>
+        <v>1417</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>1134.253</v>
+        <v>2096.896</v>
       </c>
       <c r="C45">
-        <v>1199</v>
+        <v>1473</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1715,13 +1715,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>1189.527</v>
+        <v>2148.948</v>
       </c>
       <c r="C46">
-        <v>1288</v>
+        <v>1493</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1732,13 +1732,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>1206.592</v>
+        <v>2157.009</v>
       </c>
       <c r="C47">
-        <v>1402</v>
+        <v>1562</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1749,13 +1749,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>1221.036</v>
+        <v>2161.978</v>
       </c>
       <c r="C48">
-        <v>1501</v>
+        <v>1577</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1766,13 +1766,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>1226.241</v>
+        <v>2156.424</v>
       </c>
       <c r="C49">
-        <v>1520</v>
+        <v>1634</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1783,13 +1783,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>1244.579</v>
+        <v>2132.348</v>
       </c>
       <c r="C50">
-        <v>1536</v>
+        <v>1648</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1800,13 +1800,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>1234.617</v>
+        <v>2111.721</v>
       </c>
       <c r="C51">
-        <v>1529</v>
+        <v>1789</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1817,13 +1817,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>1221.321</v>
+        <v>2081.298</v>
       </c>
       <c r="C52">
-        <v>1462</v>
+        <v>1935</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1834,13 +1834,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>1205.113</v>
+        <v>2045.447</v>
       </c>
       <c r="C53">
-        <v>1375</v>
+        <v>1885</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1851,13 +1851,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>1172.049</v>
+        <v>1949.736</v>
       </c>
       <c r="C54">
-        <v>1235</v>
+        <v>1915</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>1142.258</v>
+        <v>1887.299</v>
       </c>
       <c r="C55">
-        <v>1224</v>
+        <v>1826</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1885,13 +1885,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>1108.29</v>
+        <v>1827.529</v>
       </c>
       <c r="C56">
-        <v>1183</v>
+        <v>1676</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>1062.624</v>
+        <v>1765.357</v>
       </c>
       <c r="C57">
-        <v>1099</v>
+        <v>1709</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1919,13 +1919,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>982.692</v>
+        <v>1626.34</v>
       </c>
       <c r="C58">
-        <v>1001</v>
+        <v>1685</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1936,13 +1936,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>939.6420000000001</v>
+        <v>1543.603</v>
       </c>
       <c r="C59">
-        <v>956</v>
+        <v>1624</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1953,13 +1953,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>878.764</v>
+        <v>1419.536</v>
       </c>
       <c r="C60">
-        <v>985</v>
+        <v>1397</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>830.458</v>
+        <v>1323.283</v>
       </c>
       <c r="C61">
-        <v>850</v>
+        <v>1193</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>689.139</v>
+        <v>1116.083</v>
       </c>
       <c r="C62">
-        <v>830</v>
+        <v>1213</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2004,13 +2004,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>617.178</v>
+        <v>1006.18</v>
       </c>
       <c r="C63">
-        <v>664</v>
+        <v>1061</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2021,13 +2021,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>550.561</v>
+        <v>903.7430000000001</v>
       </c>
       <c r="C64">
-        <v>591</v>
+        <v>915</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2038,13 +2038,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>473.79</v>
+        <v>793.02</v>
       </c>
       <c r="C65">
-        <v>520</v>
+        <v>731</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2055,13 +2055,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>350.573</v>
+        <v>561.5700000000001</v>
       </c>
       <c r="C66">
-        <v>429</v>
+        <v>606</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2072,13 +2072,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>287.091</v>
+        <v>452.069</v>
       </c>
       <c r="C67">
-        <v>346</v>
+        <v>470</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>221.64</v>
+        <v>346.328</v>
       </c>
       <c r="C68">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>166.727</v>
+        <v>256.71</v>
       </c>
       <c r="C69">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2123,13 +2123,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>87.72</v>
+        <v>105.901</v>
       </c>
       <c r="C70">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>59.464</v>
+        <v>56.221</v>
       </c>
       <c r="C71">
         <v>27</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>39.771</v>
+        <v>38.553</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>34.298</v>
+        <v>32.684</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>46.348</v>
+        <v>49.929</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>56.29</v>
+        <v>55.359</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>56.574</v>
+        <v>60.931</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>55.174</v>
+        <v>61.015</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>54.032</v>
+        <v>57.26</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>51.132</v>
+        <v>56.26</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>49.732</v>
+        <v>57.56</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>50.632</v>
+        <v>56.36</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>19.852</v>
+        <v>47.08</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>19.152</v>
+        <v>44.88</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>21.352</v>
+        <v>43.58</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>21.152</v>
+        <v>48.08</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>9.651999999999999</v>
+        <v>23.98</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>21.052</v>
+        <v>23.48</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>3.252</v>
+        <v>21.48</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>4.052</v>
+        <v>20.88</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.252</v>
+        <v>19.48</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.252</v>
+        <v>18.88</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>1.252</v>
+        <v>19.18</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.252</v>
+        <v>19.48</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.252</v>
+        <v>1.08</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.268</v>
+        <v>1.46</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.668</v>
+        <v>1.66</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>1.668</v>
+        <v>1.16</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.568</v>
+        <v>1.16</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2752,10 +2752,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>2.768</v>
+        <v>1.16</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.388</v>
+        <v>1.08</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.533</v>
+        <v>1.022</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>1.269</v>
+        <v>7.554</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>1.983</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>3.766</v>
+        <v>2.453</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>9.045</v>
+        <v>8.285</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>12.64</v>
+        <v>10.025</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>18.433</v>
+        <v>12.802</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3058,13 +3058,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>35.339</v>
+        <v>31.093</v>
       </c>
       <c r="C125">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3075,13 +3075,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>158.95</v>
+        <v>137.296</v>
       </c>
       <c r="C126">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3092,13 +3092,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>250.122</v>
+        <v>203.891</v>
       </c>
       <c r="C127">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3109,13 +3109,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>351.868</v>
+        <v>295.87</v>
       </c>
       <c r="C128">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3126,13 +3126,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>460.851</v>
+        <v>397.35</v>
       </c>
       <c r="C129">
-        <v>411</v>
+        <v>326</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3143,13 +3143,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>729.88</v>
+        <v>644.127</v>
       </c>
       <c r="C130">
-        <v>563</v>
+        <v>436</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3160,13 +3160,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>883.856</v>
+        <v>760.763</v>
       </c>
       <c r="C131">
-        <v>705</v>
+        <v>598</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3177,13 +3177,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>1044.98</v>
+        <v>920.083</v>
       </c>
       <c r="C132">
-        <v>915</v>
+        <v>715</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3194,13 +3194,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>1190.297</v>
+        <v>1042.677</v>
       </c>
       <c r="C133">
-        <v>1111</v>
+        <v>829</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3211,13 +3211,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>1466.624</v>
+        <v>1257.786</v>
       </c>
       <c r="C134">
-        <v>1261</v>
+        <v>977</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3228,13 +3228,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>1619.946</v>
+        <v>1378.822</v>
       </c>
       <c r="C135">
-        <v>1384</v>
+        <v>1109</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3245,13 +3245,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>1745.661</v>
+        <v>1520.97</v>
       </c>
       <c r="C136">
-        <v>1497</v>
+        <v>1270</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3262,13 +3262,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>1863.256</v>
+        <v>1636.746</v>
       </c>
       <c r="C137">
-        <v>1653</v>
+        <v>1325</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3279,13 +3279,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>2076.265</v>
+        <v>1799.183</v>
       </c>
       <c r="C138">
-        <v>1829</v>
+        <v>1391</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3296,13 +3296,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>2159.4</v>
+        <v>1899.548</v>
       </c>
       <c r="C139">
-        <v>2016</v>
+        <v>1538</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3313,13 +3313,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>2230.061</v>
+        <v>2003.66</v>
       </c>
       <c r="C140">
-        <v>2084</v>
+        <v>1657</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3330,13 +3330,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>2299.546</v>
+        <v>2086.015</v>
       </c>
       <c r="C141">
-        <v>2182</v>
+        <v>1750</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3347,13 +3347,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>2400.656</v>
+        <v>2192.551</v>
       </c>
       <c r="C142">
-        <v>2179</v>
+        <v>1848</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3364,13 +3364,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>2440.426</v>
+        <v>2235.983</v>
       </c>
       <c r="C143">
-        <v>2294</v>
+        <v>1910</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3381,13 +3381,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>2471.592</v>
+        <v>2265.774</v>
       </c>
       <c r="C144">
-        <v>2311</v>
+        <v>1978</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3398,13 +3398,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>2486.946</v>
+        <v>2283.944</v>
       </c>
       <c r="C145">
-        <v>2196</v>
+        <v>2153</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>2519.963</v>
+        <v>2255.933</v>
       </c>
       <c r="C146">
-        <v>2155</v>
+        <v>2124</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3432,13 +3432,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>2520.073</v>
+        <v>2235.344</v>
       </c>
       <c r="C147">
-        <v>2235</v>
+        <v>1999</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3449,13 +3449,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>2517.328</v>
+        <v>2205.196</v>
       </c>
       <c r="C148">
-        <v>2241</v>
+        <v>1922</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3466,13 +3466,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
-        <v>2502.531</v>
-      </c>
-      <c r="C149">
-        <v>2182</v>
+        <v>2162.365</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3483,13 +3480,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B150">
-        <v>2477.756</v>
-      </c>
-      <c r="C150">
-        <v>2194</v>
+        <v>2072.878</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3500,13 +3494,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B151">
-        <v>2442.452</v>
-      </c>
-      <c r="C151">
-        <v>2199</v>
+        <v>2007.238</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3517,13 +3508,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B152">
-        <v>2415.764</v>
-      </c>
-      <c r="C152">
-        <v>2236</v>
+        <v>1944.759</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3534,13 +3522,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B153">
-        <v>2362.7</v>
-      </c>
-      <c r="C153">
-        <v>2196</v>
+        <v>1869.705</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3551,13 +3536,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B154">
-        <v>2245.56</v>
-      </c>
-      <c r="C154">
-        <v>2133</v>
+        <v>1722.182</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3568,13 +3550,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B155">
-        <v>2158.203</v>
-      </c>
-      <c r="C155">
-        <v>2138</v>
+        <v>1629.759</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3585,10 +3564,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B156">
-        <v>2062.563</v>
+        <v>1529.686</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3599,10 +3578,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B157">
-        <v>1948.063</v>
+        <v>1429.378</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3613,10 +3592,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B158">
-        <v>1683.591</v>
+        <v>1214.323</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3627,10 +3606,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B159">
-        <v>1523.397</v>
+        <v>1112.456</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3641,10 +3620,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B160">
-        <v>1346.441</v>
+        <v>990.564</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3655,10 +3634,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B161">
-        <v>1175.368</v>
+        <v>867.644</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3669,10 +3648,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B162">
-        <v>864.7329999999999</v>
+        <v>622.653</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3683,10 +3662,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B163">
-        <v>692.068</v>
+        <v>502.217</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3697,10 +3676,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B164">
-        <v>510.233</v>
+        <v>365.38</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3711,10 +3690,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B165">
-        <v>363.688</v>
+        <v>256.264</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3725,10 +3704,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B166">
-        <v>210.057</v>
+        <v>118.902</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3739,10 +3718,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B167">
-        <v>124.612</v>
+        <v>58.81</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3753,10 +3732,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B168">
-        <v>85.84</v>
+        <v>40.696</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3767,10 +3746,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B169">
-        <v>72.8</v>
+        <v>33.985</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3781,10 +3760,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B170">
-        <v>49.344</v>
+        <v>55.406</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3795,10 +3774,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B171">
-        <v>55.366</v>
+        <v>61.149</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3809,10 +3788,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B172">
-        <v>66.65000000000001</v>
+        <v>59.221</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3823,10 +3802,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B173">
-        <v>68.53400000000001</v>
+        <v>60.005</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3837,10 +3816,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B174">
-        <v>52.568</v>
+        <v>57.56</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3851,10 +3830,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B175">
-        <v>68.16800000000001</v>
+        <v>57.26</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3865,10 +3844,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B176">
-        <v>63.368</v>
+        <v>53.96</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3879,10 +3858,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B177">
-        <v>61.068</v>
+        <v>54.46</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3893,10 +3872,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B178">
-        <v>51.688</v>
+        <v>44.38</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3907,10 +3886,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B179">
-        <v>16.688</v>
+        <v>41.18</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3921,10 +3900,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B180">
-        <v>3.588</v>
+        <v>41.08</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3935,10 +3914,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B181">
-        <v>3.988</v>
+        <v>1.88</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3949,10 +3928,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B182">
-        <v>14.288</v>
+        <v>23.48</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3963,10 +3942,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.788</v>
+        <v>21.48</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3977,10 +3956,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B184">
-        <v>3.588</v>
+        <v>19.18</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3991,10 +3970,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B185">
-        <v>4.788</v>
+        <v>2.68</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4005,10 +3984,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
       <c r="D186">
         <v>89</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,559 +31,553 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
-  </si>
-  <si>
-    <t>16.10.202653</t>
-  </si>
-  <si>
-    <t>16.10.202654</t>
-  </si>
-  <si>
-    <t>16.10.202655</t>
-  </si>
-  <si>
-    <t>16.10.202656</t>
-  </si>
-  <si>
-    <t>16.10.202657</t>
-  </si>
-  <si>
-    <t>16.10.202658</t>
-  </si>
-  <si>
-    <t>16.10.202659</t>
-  </si>
-  <si>
-    <t>16.10.202660</t>
-  </si>
-  <si>
-    <t>16.10.202661</t>
-  </si>
-  <si>
-    <t>16.10.202662</t>
-  </si>
-  <si>
-    <t>16.10.202663</t>
-  </si>
-  <si>
-    <t>16.10.202664</t>
-  </si>
-  <si>
-    <t>16.10.202665</t>
-  </si>
-  <si>
-    <t>16.10.202666</t>
-  </si>
-  <si>
-    <t>16.10.202667</t>
-  </si>
-  <si>
-    <t>16.10.202668</t>
-  </si>
-  <si>
-    <t>16.10.202669</t>
-  </si>
-  <si>
-    <t>16.10.202670</t>
-  </si>
-  <si>
-    <t>16.10.202671</t>
-  </si>
-  <si>
-    <t>16.10.202672</t>
-  </si>
-  <si>
-    <t>16.10.202673</t>
-  </si>
-  <si>
-    <t>16.10.202674</t>
-  </si>
-  <si>
-    <t>16.10.202675</t>
-  </si>
-  <si>
-    <t>16.10.202676</t>
-  </si>
-  <si>
-    <t>16.10.202677</t>
-  </si>
-  <si>
-    <t>16.10.202678</t>
-  </si>
-  <si>
-    <t>16.10.202679</t>
-  </si>
-  <si>
-    <t>16.10.202680</t>
-  </si>
-  <si>
-    <t>16.10.202681</t>
-  </si>
-  <si>
-    <t>16.10.202682</t>
-  </si>
-  <si>
-    <t>16.10.202683</t>
-  </si>
-  <si>
-    <t>16.10.202684</t>
-  </si>
-  <si>
-    <t>16.10.202685</t>
-  </si>
-  <si>
-    <t>16.10.202686</t>
-  </si>
-  <si>
-    <t>16.10.202687</t>
-  </si>
-  <si>
-    <t>16.10.202688</t>
-  </si>
-  <si>
-    <t>16.10.202689</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
+  </si>
+  <si>
+    <t>21.10.202636</t>
+  </si>
+  <si>
+    <t>21.10.202637</t>
+  </si>
+  <si>
+    <t>21.10.202638</t>
+  </si>
+  <si>
+    <t>21.10.202639</t>
+  </si>
+  <si>
+    <t>21.10.202640</t>
+  </si>
+  <si>
+    <t>21.10.202641</t>
+  </si>
+  <si>
+    <t>21.10.202642</t>
+  </si>
+  <si>
+    <t>21.10.202643</t>
+  </si>
+  <si>
+    <t>21.10.202644</t>
+  </si>
+  <si>
+    <t>21.10.202645</t>
+  </si>
+  <si>
+    <t>21.10.202646</t>
+  </si>
+  <si>
+    <t>21.10.202647</t>
+  </si>
+  <si>
+    <t>21.10.202648</t>
+  </si>
+  <si>
+    <t>21.10.202649</t>
+  </si>
+  <si>
+    <t>21.10.202650</t>
+  </si>
+  <si>
+    <t>21.10.202651</t>
+  </si>
+  <si>
+    <t>21.10.202652</t>
+  </si>
+  <si>
+    <t>21.10.202653</t>
+  </si>
+  <si>
+    <t>21.10.202654</t>
+  </si>
+  <si>
+    <t>21.10.202655</t>
+  </si>
+  <si>
+    <t>21.10.202656</t>
+  </si>
+  <si>
+    <t>21.10.202657</t>
+  </si>
+  <si>
+    <t>21.10.202658</t>
+  </si>
+  <si>
+    <t>21.10.202659</t>
+  </si>
+  <si>
+    <t>21.10.202660</t>
+  </si>
+  <si>
+    <t>21.10.202661</t>
+  </si>
+  <si>
+    <t>21.10.202662</t>
+  </si>
+  <si>
+    <t>21.10.202663</t>
+  </si>
+  <si>
+    <t>21.10.202664</t>
+  </si>
+  <si>
+    <t>21.10.202665</t>
+  </si>
+  <si>
+    <t>21.10.202666</t>
+  </si>
+  <si>
+    <t>21.10.202667</t>
+  </si>
+  <si>
+    <t>21.10.202668</t>
+  </si>
+  <si>
+    <t>21.10.202669</t>
+  </si>
+  <si>
+    <t>21.10.202670</t>
+  </si>
+  <si>
+    <t>21.10.202671</t>
+  </si>
+  <si>
+    <t>21.10.202672</t>
+  </si>
+  <si>
+    <t>21.10.202673</t>
+  </si>
+  <si>
+    <t>21.10.202674</t>
+  </si>
+  <si>
+    <t>21.10.202675</t>
+  </si>
+  <si>
+    <t>21.10.202676</t>
+  </si>
+  <si>
+    <t>21.10.202677</t>
+  </si>
+  <si>
+    <t>21.10.202678</t>
+  </si>
+  <si>
+    <t>21.10.202679</t>
+  </si>
+  <si>
+    <t>21.10.202680</t>
+  </si>
+  <si>
+    <t>21.10.202681</t>
+  </si>
+  <si>
+    <t>21.10.202682</t>
+  </si>
+  <si>
+    <t>21.10.202683</t>
+  </si>
+  <si>
+    <t>21.10.202684</t>
+  </si>
+  <si>
+    <t>21.10.202685</t>
+  </si>
+  <si>
+    <t>21.10.202686</t>
+  </si>
+  <si>
+    <t>21.10.202687</t>
   </si>
 </sst>
 </file>
@@ -945,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -967,10 +961,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>1.08</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -984,10 +978,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>4.88</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1001,10 +995,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.08</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1018,10 +1012,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1035,10 +1029,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1052,10 +1046,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1069,10 +1063,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1086,10 +1080,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1103,10 +1097,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1120,10 +1114,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1137,10 +1131,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1154,10 +1148,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>7.768</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1171,10 +1165,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1188,10 +1182,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1205,10 +1199,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1222,10 +1216,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1239,10 +1233,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1256,10 +1250,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1273,10 +1267,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1290,10 +1284,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1307,10 +1301,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>7.078</v>
+        <v>1.217</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1324,10 +1318,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>7.094</v>
+        <v>1.273</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1341,10 +1335,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>7.359</v>
+        <v>1.293</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1358,10 +1352,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>7.787</v>
+        <v>1.748</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1375,10 +1369,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>12.519</v>
+        <v>2.958</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1392,10 +1386,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>13.484</v>
+        <v>3.967</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1409,13 +1403,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>16.843</v>
+        <v>7.866</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1426,13 +1420,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>34.053</v>
+        <v>32.013</v>
       </c>
       <c r="C29">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1443,13 +1437,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>171.801</v>
+        <v>112.049</v>
       </c>
       <c r="C30">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1460,13 +1454,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>260.132</v>
+        <v>162.328</v>
       </c>
       <c r="C31">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1477,13 +1471,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>361.61</v>
+        <v>245.703</v>
       </c>
       <c r="C32">
-        <v>367</v>
+        <v>228</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1494,13 +1488,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>470.654</v>
+        <v>337.841</v>
       </c>
       <c r="C33">
-        <v>514</v>
+        <v>337</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1511,13 +1505,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>760.75</v>
+        <v>587.265</v>
       </c>
       <c r="C34">
-        <v>650</v>
+        <v>505</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1528,13 +1522,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>891.24</v>
+        <v>730.514</v>
       </c>
       <c r="C35">
-        <v>858</v>
+        <v>640</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1545,13 +1539,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>1042.068</v>
+        <v>875.218</v>
       </c>
       <c r="C36">
-        <v>1061</v>
+        <v>802</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1562,13 +1556,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>1172.924</v>
+        <v>1034.841</v>
       </c>
       <c r="C37">
-        <v>1170</v>
+        <v>977</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1579,13 +1573,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>1416.652</v>
+        <v>1309.884</v>
       </c>
       <c r="C38">
-        <v>1277</v>
+        <v>1195</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1596,13 +1590,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>1545.088</v>
+        <v>1458.52</v>
       </c>
       <c r="C39">
-        <v>1280</v>
+        <v>1386</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1613,13 +1607,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>1677.582</v>
+        <v>1624.573</v>
       </c>
       <c r="C40">
-        <v>1443</v>
+        <v>1618</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1630,13 +1624,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>1766.061</v>
+        <v>1755.563</v>
       </c>
       <c r="C41">
-        <v>1448</v>
+        <v>1832</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1647,13 +1641,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>1881.831</v>
+        <v>1970.32</v>
       </c>
       <c r="C42">
-        <v>1387</v>
+        <v>1943</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1664,13 +1658,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>1966.715</v>
+        <v>2085.892</v>
       </c>
       <c r="C43">
-        <v>1417</v>
+        <v>2022</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1681,13 +1675,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>2043.585</v>
+        <v>2181.395</v>
       </c>
       <c r="C44">
-        <v>1417</v>
+        <v>2189</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1698,13 +1692,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>2096.896</v>
+        <v>2266.007</v>
       </c>
       <c r="C45">
-        <v>1473</v>
+        <v>2348</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1715,13 +1709,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>2148.948</v>
+        <v>2376.796</v>
       </c>
       <c r="C46">
-        <v>1493</v>
+        <v>2504</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1732,13 +1726,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>2157.009</v>
+        <v>2432.77</v>
       </c>
       <c r="C47">
-        <v>1562</v>
+        <v>2588</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1749,13 +1743,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>2161.978</v>
+        <v>2460.644</v>
       </c>
       <c r="C48">
-        <v>1577</v>
+        <v>2607</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1766,13 +1760,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>2156.424</v>
+        <v>2498.975</v>
       </c>
       <c r="C49">
-        <v>1634</v>
+        <v>2618</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1783,13 +1777,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>2132.348</v>
+        <v>2525.085</v>
       </c>
       <c r="C50">
-        <v>1648</v>
+        <v>2615</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1800,13 +1794,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>2111.721</v>
+        <v>2538.905</v>
       </c>
       <c r="C51">
-        <v>1789</v>
+        <v>2607</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1817,13 +1811,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>2081.298</v>
+        <v>2536.78</v>
       </c>
       <c r="C52">
-        <v>1935</v>
+        <v>2572</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1834,13 +1828,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>2045.447</v>
+        <v>2532.981</v>
       </c>
       <c r="C53">
-        <v>1885</v>
+        <v>2541</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1851,13 +1845,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>1949.736</v>
+        <v>2513.854</v>
       </c>
       <c r="C54">
-        <v>1915</v>
+        <v>2588</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1868,13 +1862,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>1887.299</v>
+        <v>2482.183</v>
       </c>
       <c r="C55">
-        <v>1826</v>
+        <v>2530</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1885,13 +1879,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>1827.529</v>
+        <v>2438.889</v>
       </c>
       <c r="C56">
-        <v>1676</v>
+        <v>2496</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1902,13 +1896,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>1765.357</v>
+        <v>2369.725</v>
       </c>
       <c r="C57">
-        <v>1709</v>
+        <v>2441</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1919,13 +1913,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>1626.34</v>
+        <v>2224.484</v>
       </c>
       <c r="C58">
-        <v>1685</v>
+        <v>2357</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1936,13 +1930,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>1543.603</v>
+        <v>2124.092</v>
       </c>
       <c r="C59">
-        <v>1624</v>
+        <v>2249</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1953,13 +1947,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>1419.536</v>
+        <v>2001.641</v>
       </c>
       <c r="C60">
-        <v>1397</v>
+        <v>2161</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1970,13 +1964,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>1323.283</v>
+        <v>1875.958</v>
       </c>
       <c r="C61">
-        <v>1193</v>
+        <v>1999</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1987,13 +1981,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>1116.083</v>
+        <v>1631.822</v>
       </c>
       <c r="C62">
-        <v>1213</v>
+        <v>1790</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2004,13 +1998,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>1006.18</v>
+        <v>1454.017</v>
       </c>
       <c r="C63">
-        <v>1061</v>
+        <v>1625</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2021,13 +2015,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>903.7430000000001</v>
+        <v>1258.826</v>
       </c>
       <c r="C64">
-        <v>915</v>
+        <v>1331</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2038,13 +2032,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>793.02</v>
+        <v>1052.64</v>
       </c>
       <c r="C65">
-        <v>731</v>
+        <v>1128</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2055,13 +2049,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>561.5700000000001</v>
+        <v>702.301</v>
       </c>
       <c r="C66">
-        <v>606</v>
+        <v>900</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2072,13 +2066,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>452.069</v>
+        <v>543.326</v>
       </c>
       <c r="C67">
-        <v>470</v>
+        <v>645</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2089,13 +2083,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>346.328</v>
+        <v>382.306</v>
       </c>
       <c r="C68">
-        <v>325</v>
+        <v>405</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2106,13 +2100,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>256.71</v>
+        <v>269.442</v>
       </c>
       <c r="C69">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2123,13 +2117,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>105.901</v>
+        <v>168.851</v>
       </c>
       <c r="C70">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2140,13 +2134,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>56.221</v>
+        <v>117.273</v>
       </c>
       <c r="C71">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2157,10 +2151,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>38.553</v>
+        <v>102.393</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2174,10 +2168,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>32.684</v>
+        <v>101.953</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2191,10 +2185,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>49.929</v>
+        <v>50.625</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2208,10 +2202,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>55.359</v>
+        <v>53.417</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2225,10 +2219,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>60.931</v>
+        <v>53.905</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2242,10 +2236,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>61.015</v>
+        <v>54.301</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2259,10 +2253,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>57.26</v>
+        <v>103.968</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2276,10 +2270,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>56.26</v>
+        <v>100.168</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2293,10 +2287,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>57.56</v>
+        <v>96.968</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2310,10 +2304,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>56.36</v>
+        <v>99.268</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2327,10 +2321,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>47.08</v>
+        <v>12.088</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2344,10 +2338,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>44.88</v>
+        <v>8.488</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2361,10 +2355,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>43.58</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2378,10 +2372,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>48.08</v>
+        <v>9.087999999999999</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2395,10 +2389,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>23.98</v>
+        <v>12.188</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2412,10 +2406,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>23.48</v>
+        <v>12.188</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2429,10 +2423,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>21.48</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2446,10 +2440,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>20.88</v>
+        <v>12.988</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2463,10 +2457,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>19.48</v>
+        <v>1.288</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2480,10 +2474,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>18.88</v>
+        <v>1.288</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2497,10 +2491,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>19.18</v>
+        <v>1.288</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2514,10 +2508,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>19.48</v>
+        <v>1.288</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2531,10 +2525,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.08</v>
+        <v>1.288</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2548,10 +2542,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>1.08</v>
+        <v>1.288</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2565,10 +2559,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.08</v>
+        <v>1.288</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2582,10 +2576,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.08</v>
+        <v>1.288</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2599,10 +2593,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2616,10 +2610,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2633,10 +2627,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2650,10 +2644,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2667,10 +2661,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.46</v>
+        <v>1.268</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2684,10 +2678,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.66</v>
+        <v>1.268</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2701,10 +2695,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2718,10 +2712,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2735,10 +2729,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2752,10 +2746,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2769,10 +2763,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2786,10 +2780,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2803,10 +2797,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2820,10 +2814,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2837,10 +2831,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2854,10 +2848,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2871,10 +2865,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.08</v>
+        <v>25.188</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2888,10 +2882,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.08</v>
+        <v>25.288</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2905,10 +2899,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>1.08</v>
+        <v>25.488</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2922,10 +2916,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.08</v>
+        <v>25.688</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2939,10 +2933,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.022</v>
+        <v>20.752</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2956,10 +2950,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>7.554</v>
+        <v>21.192</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2973,10 +2967,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>8.124000000000001</v>
+        <v>21.348</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2990,10 +2984,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.453</v>
+        <v>21.86</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3007,10 +3001,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>8.285</v>
+        <v>15.374</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3024,10 +3018,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>10.025</v>
+        <v>15.819</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3041,10 +3035,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>12.802</v>
+        <v>16.612</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3058,13 +3052,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>31.093</v>
+        <v>32.8</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3075,13 +3069,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>137.296</v>
+        <v>134.456</v>
       </c>
       <c r="C126">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3092,13 +3086,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>203.891</v>
+        <v>199.37</v>
       </c>
       <c r="C127">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3109,13 +3103,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>295.87</v>
+        <v>321.724</v>
       </c>
       <c r="C128">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3126,13 +3120,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>397.35</v>
+        <v>449.13</v>
       </c>
       <c r="C129">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3143,13 +3137,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>644.127</v>
+        <v>788.684</v>
       </c>
       <c r="C130">
-        <v>436</v>
+        <v>508</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3160,13 +3154,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>760.763</v>
+        <v>970.168</v>
       </c>
       <c r="C131">
-        <v>598</v>
+        <v>681</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3177,13 +3171,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>920.083</v>
+        <v>1162.631</v>
       </c>
       <c r="C132">
-        <v>715</v>
+        <v>814</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3194,13 +3188,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B133">
-        <v>1042.677</v>
-      </c>
-      <c r="C133">
-        <v>829</v>
+        <v>1329.529</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3211,13 +3202,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B134">
-        <v>1257.786</v>
-      </c>
-      <c r="C134">
-        <v>977</v>
+        <v>1668.261</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3228,13 +3216,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B135">
-        <v>1378.822</v>
-      </c>
-      <c r="C135">
-        <v>1109</v>
+        <v>1817.922</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3245,13 +3230,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B136">
-        <v>1520.97</v>
-      </c>
-      <c r="C136">
-        <v>1270</v>
+        <v>1992.754</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3262,13 +3244,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B137">
-        <v>1636.746</v>
-      </c>
-      <c r="C137">
-        <v>1325</v>
+        <v>2130.33</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3279,13 +3258,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B138">
-        <v>1799.183</v>
-      </c>
-      <c r="C138">
-        <v>1391</v>
+        <v>2370.992</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3296,13 +3272,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B139">
-        <v>1899.548</v>
-      </c>
-      <c r="C139">
-        <v>1538</v>
+        <v>2488.317</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3313,13 +3286,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B140">
-        <v>2003.66</v>
-      </c>
-      <c r="C140">
-        <v>1657</v>
+        <v>2577.48</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3330,13 +3300,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B141">
-        <v>2086.015</v>
-      </c>
-      <c r="C141">
-        <v>1750</v>
+        <v>2658.241</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3347,13 +3314,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B142">
-        <v>2192.551</v>
-      </c>
-      <c r="C142">
-        <v>1848</v>
+        <v>2786.73</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3364,13 +3328,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B143">
-        <v>2235.983</v>
-      </c>
-      <c r="C143">
-        <v>1910</v>
+        <v>2837.678</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3381,13 +3342,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B144">
-        <v>2265.774</v>
-      </c>
-      <c r="C144">
-        <v>1978</v>
+        <v>2893.517</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3398,13 +3356,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B145">
-        <v>2283.944</v>
-      </c>
-      <c r="C145">
-        <v>2153</v>
+        <v>2921.718</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3415,13 +3370,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B146">
-        <v>2255.933</v>
-      </c>
-      <c r="C146">
-        <v>2124</v>
+        <v>2945.099</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3432,13 +3384,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B147">
-        <v>2235.344</v>
-      </c>
-      <c r="C147">
-        <v>1999</v>
+        <v>2955.308</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3449,13 +3398,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B148">
-        <v>2205.196</v>
-      </c>
-      <c r="C148">
-        <v>1922</v>
+        <v>2954.072</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3466,10 +3412,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B149">
-        <v>2162.365</v>
+        <v>2948.462</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3480,10 +3426,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B150">
-        <v>2072.878</v>
+        <v>2899.119</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3494,10 +3440,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B151">
-        <v>2007.238</v>
+        <v>2865.234</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3508,10 +3454,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B152">
-        <v>1944.759</v>
+        <v>2795.538</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3522,10 +3468,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B153">
-        <v>1869.705</v>
+        <v>2730.767</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3536,10 +3482,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B154">
-        <v>1722.182</v>
+        <v>2553.966</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3550,10 +3496,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B155">
-        <v>1629.759</v>
+        <v>2439.794</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3564,10 +3510,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B156">
-        <v>1529.686</v>
+        <v>2302.919</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3578,10 +3524,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B157">
-        <v>1429.378</v>
+        <v>2164.674</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3592,10 +3538,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B158">
-        <v>1214.323</v>
+        <v>1810.539</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3606,10 +3552,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B159">
-        <v>1112.456</v>
+        <v>1627.316</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3620,10 +3566,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B160">
-        <v>990.564</v>
+        <v>1410.572</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3634,10 +3580,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B161">
-        <v>867.644</v>
+        <v>1210.464</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3648,10 +3594,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B162">
-        <v>622.653</v>
+        <v>827.659</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3662,10 +3608,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B163">
-        <v>502.217</v>
+        <v>637.504</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3676,10 +3622,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B164">
-        <v>365.38</v>
+        <v>443.47</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3690,10 +3636,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B165">
-        <v>256.264</v>
+        <v>295.783</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3704,10 +3650,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B166">
-        <v>118.902</v>
+        <v>145.038</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3718,10 +3664,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B167">
-        <v>58.81</v>
+        <v>88.496</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3732,10 +3678,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B168">
-        <v>40.696</v>
+        <v>73.637</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3746,10 +3692,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B169">
-        <v>33.985</v>
+        <v>71.193</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3760,10 +3706,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B170">
-        <v>55.406</v>
+        <v>65.02500000000001</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3774,10 +3720,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B171">
-        <v>61.149</v>
+        <v>62.165</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3788,10 +3734,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B172">
-        <v>59.221</v>
+        <v>63.345</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3802,10 +3748,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B173">
-        <v>60.005</v>
+        <v>60.121</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3816,10 +3762,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B174">
-        <v>57.56</v>
+        <v>53.962</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3830,10 +3776,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B175">
-        <v>57.26</v>
+        <v>53.168</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3844,10 +3790,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B176">
-        <v>53.96</v>
+        <v>53.068</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3858,10 +3804,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B177">
-        <v>54.46</v>
+        <v>53.168</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3872,10 +3818,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B178">
-        <v>44.38</v>
+        <v>9.188000000000001</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3886,10 +3832,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B179">
-        <v>41.18</v>
+        <v>13.588</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3900,10 +3846,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B180">
-        <v>41.08</v>
+        <v>12.088</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3914,10 +3860,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B181">
-        <v>1.88</v>
+        <v>12.488</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3928,10 +3874,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B182">
-        <v>23.48</v>
+        <v>14.888</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3942,10 +3888,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B183">
-        <v>21.48</v>
+        <v>14.088</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3956,44 +3902,16 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B184">
-        <v>19.18</v>
+        <v>7.688</v>
       </c>
       <c r="D184">
         <v>87</v>
       </c>
       <c r="E184" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="2">
-        <v>46311.90625</v>
-      </c>
-      <c r="B185">
-        <v>2.68</v>
-      </c>
-      <c r="D185">
-        <v>88</v>
-      </c>
-      <c r="E185" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2">
-        <v>46311.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>1.08</v>
-      </c>
-      <c r="D186">
-        <v>89</v>
-      </c>
-      <c r="E186" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,553 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
-  </si>
-  <si>
-    <t>21.10.202636</t>
-  </si>
-  <si>
-    <t>21.10.202637</t>
-  </si>
-  <si>
-    <t>21.10.202638</t>
-  </si>
-  <si>
-    <t>21.10.202639</t>
-  </si>
-  <si>
-    <t>21.10.202640</t>
-  </si>
-  <si>
-    <t>21.10.202641</t>
-  </si>
-  <si>
-    <t>21.10.202642</t>
-  </si>
-  <si>
-    <t>21.10.202643</t>
-  </si>
-  <si>
-    <t>21.10.202644</t>
-  </si>
-  <si>
-    <t>21.10.202645</t>
-  </si>
-  <si>
-    <t>21.10.202646</t>
-  </si>
-  <si>
-    <t>21.10.202647</t>
-  </si>
-  <si>
-    <t>21.10.202648</t>
-  </si>
-  <si>
-    <t>21.10.202649</t>
-  </si>
-  <si>
-    <t>21.10.202650</t>
-  </si>
-  <si>
-    <t>21.10.202651</t>
-  </si>
-  <si>
-    <t>21.10.202652</t>
-  </si>
-  <si>
-    <t>21.10.202653</t>
-  </si>
-  <si>
-    <t>21.10.202654</t>
-  </si>
-  <si>
-    <t>21.10.202655</t>
-  </si>
-  <si>
-    <t>21.10.202656</t>
-  </si>
-  <si>
-    <t>21.10.202657</t>
-  </si>
-  <si>
-    <t>21.10.202658</t>
-  </si>
-  <si>
-    <t>21.10.202659</t>
-  </si>
-  <si>
-    <t>21.10.202660</t>
-  </si>
-  <si>
-    <t>21.10.202661</t>
-  </si>
-  <si>
-    <t>21.10.202662</t>
-  </si>
-  <si>
-    <t>21.10.202663</t>
-  </si>
-  <si>
-    <t>21.10.202664</t>
-  </si>
-  <si>
-    <t>21.10.202665</t>
-  </si>
-  <si>
-    <t>21.10.202666</t>
-  </si>
-  <si>
-    <t>21.10.202667</t>
-  </si>
-  <si>
-    <t>21.10.202668</t>
-  </si>
-  <si>
-    <t>21.10.202669</t>
-  </si>
-  <si>
-    <t>21.10.202670</t>
-  </si>
-  <si>
-    <t>21.10.202671</t>
-  </si>
-  <si>
-    <t>21.10.202672</t>
-  </si>
-  <si>
-    <t>21.10.202673</t>
-  </si>
-  <si>
-    <t>21.10.202674</t>
-  </si>
-  <si>
-    <t>21.10.202675</t>
-  </si>
-  <si>
-    <t>21.10.202676</t>
-  </si>
-  <si>
-    <t>21.10.202677</t>
-  </si>
-  <si>
-    <t>21.10.202678</t>
-  </si>
-  <si>
-    <t>21.10.202679</t>
-  </si>
-  <si>
-    <t>21.10.202680</t>
-  </si>
-  <si>
-    <t>21.10.202681</t>
-  </si>
-  <si>
-    <t>21.10.202682</t>
-  </si>
-  <si>
-    <t>21.10.202683</t>
-  </si>
-  <si>
-    <t>21.10.202684</t>
-  </si>
-  <si>
-    <t>21.10.202685</t>
-  </si>
-  <si>
-    <t>21.10.202686</t>
-  </si>
-  <si>
-    <t>21.10.202687</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
+  </si>
+  <si>
+    <t>25.10.202638</t>
+  </si>
+  <si>
+    <t>25.10.202639</t>
+  </si>
+  <si>
+    <t>25.10.202640</t>
+  </si>
+  <si>
+    <t>25.10.202641</t>
+  </si>
+  <si>
+    <t>25.10.202642</t>
+  </si>
+  <si>
+    <t>25.10.202643</t>
+  </si>
+  <si>
+    <t>25.10.202644</t>
+  </si>
+  <si>
+    <t>25.10.202645</t>
+  </si>
+  <si>
+    <t>25.10.202646</t>
+  </si>
+  <si>
+    <t>25.10.202647</t>
+  </si>
+  <si>
+    <t>25.10.202648</t>
+  </si>
+  <si>
+    <t>25.10.202649</t>
+  </si>
+  <si>
+    <t>25.10.202650</t>
+  </si>
+  <si>
+    <t>25.10.202651</t>
+  </si>
+  <si>
+    <t>25.10.202652</t>
+  </si>
+  <si>
+    <t>25.10.202653</t>
+  </si>
+  <si>
+    <t>25.10.202654</t>
+  </si>
+  <si>
+    <t>25.10.202655</t>
+  </si>
+  <si>
+    <t>25.10.202656</t>
+  </si>
+  <si>
+    <t>25.10.202657</t>
+  </si>
+  <si>
+    <t>25.10.202658</t>
+  </si>
+  <si>
+    <t>25.10.202659</t>
+  </si>
+  <si>
+    <t>25.10.202660</t>
+  </si>
+  <si>
+    <t>25.10.202661</t>
+  </si>
+  <si>
+    <t>25.10.202662</t>
+  </si>
+  <si>
+    <t>25.10.202663</t>
+  </si>
+  <si>
+    <t>25.10.202664</t>
+  </si>
+  <si>
+    <t>25.10.202665</t>
+  </si>
+  <si>
+    <t>25.10.202666</t>
+  </si>
+  <si>
+    <t>25.10.202667</t>
+  </si>
+  <si>
+    <t>25.10.202668</t>
+  </si>
+  <si>
+    <t>25.10.202669</t>
+  </si>
+  <si>
+    <t>25.10.202670</t>
+  </si>
+  <si>
+    <t>25.10.202671</t>
+  </si>
+  <si>
+    <t>25.10.202672</t>
+  </si>
+  <si>
+    <t>25.10.202673</t>
+  </si>
+  <si>
+    <t>25.10.202674</t>
+  </si>
+  <si>
+    <t>25.10.202675</t>
+  </si>
+  <si>
+    <t>25.10.202676</t>
+  </si>
+  <si>
+    <t>25.10.202677</t>
+  </si>
+  <si>
+    <t>25.10.202678</t>
+  </si>
+  <si>
+    <t>25.10.202679</t>
+  </si>
+  <si>
+    <t>25.10.202680</t>
+  </si>
+  <si>
+    <t>25.10.202681</t>
+  </si>
+  <si>
+    <t>25.10.202682</t>
+  </si>
+  <si>
+    <t>25.10.202683</t>
+  </si>
+  <si>
+    <t>25.10.202684</t>
+  </si>
+  <si>
+    <t>25.10.202685</t>
+  </si>
+  <si>
+    <t>25.10.202686</t>
+  </si>
+  <si>
+    <t>25.10.202687</t>
+  </si>
+  <si>
+    <t>25.10.202688</t>
+  </si>
+  <si>
+    <t>25.10.202689</t>
+  </si>
+  <si>
+    <t>25.10.202690</t>
+  </si>
+  <si>
+    <t>25.10.202691</t>
+  </si>
+  <si>
+    <t>25.10.202692</t>
+  </si>
+  <si>
+    <t>25.10.202693</t>
+  </si>
+  <si>
+    <t>25.10.202694</t>
+  </si>
+  <si>
+    <t>25.10.202695</t>
+  </si>
+  <si>
+    <t>25.10.202696</t>
   </si>
 </sst>
 </file>
@@ -939,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -961,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>8.090999999999999</v>
+        <v>2.398</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -978,10 +1005,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>8.090999999999999</v>
+        <v>2.398</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -995,10 +1022,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>8.090999999999999</v>
+        <v>2.398</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1012,10 +1039,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>8.090999999999999</v>
+        <v>1.591</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1029,10 +1056,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>7.768</v>
+        <v>1.671</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1046,10 +1073,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>7.768</v>
+        <v>1.671</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1063,10 +1090,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>7.768</v>
+        <v>1.671</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1080,10 +1107,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>7.768</v>
+        <v>1.268</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1097,10 +1124,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>7.768</v>
+        <v>1.268</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1114,10 +1141,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>7.768</v>
+        <v>1.268</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1131,10 +1158,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>7.768</v>
+        <v>1.268</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1148,10 +1175,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>7.768</v>
+        <v>1.268</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1165,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1182,10 +1209,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1199,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1216,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1233,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1250,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1267,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1284,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.188</v>
+        <v>7.688</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1301,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.217</v>
+        <v>11.361</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1318,10 +1345,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>1.273</v>
+        <v>11.243</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1335,10 +1362,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.293</v>
+        <v>11.264</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1352,10 +1379,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.748</v>
+        <v>11.369</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1369,10 +1396,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>2.958</v>
+        <v>14.9</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1386,10 +1413,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>3.967</v>
+        <v>14.984</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1403,10 +1430,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>7.866</v>
+        <v>16.094</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1420,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>32.013</v>
+        <v>20.36</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1437,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>112.049</v>
+        <v>95.188</v>
       </c>
       <c r="C30">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1454,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>162.328</v>
+        <v>149.175</v>
       </c>
       <c r="C31">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1471,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>245.703</v>
+        <v>246.678</v>
       </c>
       <c r="C32">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1488,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>337.841</v>
+        <v>364.013</v>
       </c>
       <c r="C33">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1505,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>587.265</v>
+        <v>627.155</v>
       </c>
       <c r="C34">
-        <v>505</v>
+        <v>413</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1522,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>730.514</v>
+        <v>765.883</v>
       </c>
       <c r="C35">
-        <v>640</v>
+        <v>547</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1539,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>875.218</v>
+        <v>939.116</v>
       </c>
       <c r="C36">
-        <v>802</v>
+        <v>670</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1556,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>1034.841</v>
+        <v>1094.166</v>
       </c>
       <c r="C37">
-        <v>977</v>
+        <v>783</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1573,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>1309.884</v>
+        <v>1358.427</v>
       </c>
       <c r="C38">
-        <v>1195</v>
+        <v>920</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1590,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>1458.52</v>
+        <v>1539.051</v>
       </c>
       <c r="C39">
-        <v>1386</v>
+        <v>1043</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1607,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>1624.573</v>
+        <v>1690.398</v>
       </c>
       <c r="C40">
-        <v>1618</v>
+        <v>1151</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1624,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>1755.563</v>
+        <v>1819.51</v>
       </c>
       <c r="C41">
-        <v>1832</v>
+        <v>1322</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1641,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>1970.32</v>
+        <v>2058.338</v>
       </c>
       <c r="C42">
-        <v>1943</v>
+        <v>1508</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1658,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>2085.892</v>
+        <v>2172.025</v>
       </c>
       <c r="C43">
-        <v>2022</v>
+        <v>1621</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1675,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>2181.395</v>
+        <v>2266.019</v>
       </c>
       <c r="C44">
-        <v>2189</v>
+        <v>1704</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1692,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>2266.007</v>
+        <v>2345.809</v>
       </c>
       <c r="C45">
-        <v>2348</v>
+        <v>1798</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1709,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>2376.796</v>
+        <v>2480.543</v>
       </c>
       <c r="C46">
-        <v>2504</v>
+        <v>1854</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1726,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>2432.77</v>
+        <v>2538.968</v>
       </c>
       <c r="C47">
-        <v>2588</v>
+        <v>1937</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1743,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>2460.644</v>
+        <v>2585.777</v>
       </c>
       <c r="C48">
-        <v>2607</v>
+        <v>2005</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1760,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>2498.975</v>
+        <v>2621.313</v>
       </c>
       <c r="C49">
-        <v>2618</v>
+        <v>2043</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1777,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>2525.085</v>
+        <v>2648.158</v>
       </c>
       <c r="C50">
-        <v>2615</v>
+        <v>2096</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1794,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>2538.905</v>
+        <v>2656.405</v>
       </c>
       <c r="C51">
-        <v>2607</v>
+        <v>2136</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1811,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>2536.78</v>
+        <v>2655.499</v>
       </c>
       <c r="C52">
-        <v>2572</v>
+        <v>2123</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1828,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>2532.981</v>
+        <v>2643.122</v>
       </c>
       <c r="C53">
-        <v>2541</v>
+        <v>2119</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1845,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>2513.854</v>
+        <v>2604.943</v>
       </c>
       <c r="C54">
-        <v>2588</v>
+        <v>2074</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1862,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>2482.183</v>
+        <v>2565.664</v>
       </c>
       <c r="C55">
-        <v>2530</v>
+        <v>2063</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1879,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>2438.889</v>
+        <v>2515.911</v>
       </c>
       <c r="C56">
-        <v>2496</v>
+        <v>2044</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1896,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>2369.725</v>
+        <v>2454.365</v>
       </c>
       <c r="C57">
-        <v>2441</v>
+        <v>2052</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1913,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>2224.484</v>
+        <v>2299.436</v>
       </c>
       <c r="C58">
-        <v>2357</v>
+        <v>2016</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1930,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>2124.092</v>
+        <v>2197.216</v>
       </c>
       <c r="C59">
-        <v>2249</v>
+        <v>1935</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1947,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>2001.641</v>
+        <v>2050.455</v>
       </c>
       <c r="C60">
-        <v>2161</v>
+        <v>1877</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1964,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>1875.958</v>
+        <v>1907.588</v>
       </c>
       <c r="C61">
-        <v>1999</v>
+        <v>1773</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1981,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>1631.822</v>
+        <v>1598.379</v>
       </c>
       <c r="C62">
-        <v>1790</v>
+        <v>1591</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1998,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>1454.017</v>
+        <v>1407.824</v>
       </c>
       <c r="C63">
-        <v>1625</v>
+        <v>1428</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2015,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>1258.826</v>
+        <v>1190.62</v>
       </c>
       <c r="C64">
-        <v>1331</v>
+        <v>1190</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2032,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>1052.64</v>
+        <v>998.852</v>
       </c>
       <c r="C65">
-        <v>1128</v>
+        <v>970</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2049,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>702.301</v>
+        <v>677.3339999999999</v>
       </c>
       <c r="C66">
-        <v>900</v>
+        <v>728</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2066,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>543.326</v>
+        <v>502.668</v>
       </c>
       <c r="C67">
-        <v>645</v>
+        <v>491</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2083,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>382.306</v>
+        <v>340.735</v>
       </c>
       <c r="C68">
-        <v>405</v>
+        <v>307</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2100,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>269.442</v>
+        <v>213.169</v>
       </c>
       <c r="C69">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2117,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>168.851</v>
+        <v>71.48699999999999</v>
       </c>
       <c r="C70">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2134,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>117.273</v>
+        <v>36.449</v>
       </c>
       <c r="C71">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2151,10 +2178,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>102.393</v>
+        <v>27.466</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2168,10 +2195,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>101.953</v>
+        <v>26.047</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2185,10 +2212,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>50.625</v>
+        <v>22.248</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2202,10 +2229,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>53.417</v>
+        <v>23.561</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2219,10 +2246,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>53.905</v>
+        <v>23.708</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2236,10 +2263,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>54.301</v>
+        <v>22.008</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2253,10 +2280,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>103.968</v>
+        <v>37.969</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2270,10 +2297,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>100.168</v>
+        <v>35.569</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2287,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>96.968</v>
+        <v>30.469</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2304,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>99.268</v>
+        <v>29.869</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2321,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.088</v>
+        <v>31.388</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2338,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>8.488</v>
+        <v>29.088</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2355,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>8.688000000000001</v>
+        <v>29.188</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2372,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>9.087999999999999</v>
+        <v>29.288</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2389,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>12.188</v>
+        <v>10.488</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2406,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>12.188</v>
+        <v>9.488</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2423,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.688000000000001</v>
+        <v>9.188000000000001</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2440,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>12.988</v>
+        <v>9.188000000000001</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2457,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.288</v>
+        <v>10.688</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2474,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.288</v>
+        <v>9.188000000000001</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2491,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>1.288</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2508,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.288</v>
+        <v>8.788</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2525,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
         <v>1.288</v>
@@ -2542,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
         <v>1.288</v>
@@ -2559,10 +2586,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.288</v>
+        <v>1.188</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2576,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
         <v>1.288</v>
@@ -2593,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2610,10 +2637,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2627,10 +2654,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2644,10 +2671,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>7.688</v>
+        <v>1.288</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2661,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
         <v>1.268</v>
@@ -2678,10 +2705,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.268</v>
+        <v>1.368</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2695,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
         <v>1.268</v>
@@ -2712,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
         <v>1.268</v>
@@ -2729,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
         <v>1.268</v>
@@ -2746,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
         <v>1.268</v>
@@ -2763,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
         <v>1.268</v>
@@ -2780,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
         <v>1.268</v>
@@ -2797,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2814,10 +2841,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2831,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2848,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2865,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>25.188</v>
+        <v>1.287</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2882,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>25.288</v>
+        <v>1.323</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2899,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>25.488</v>
+        <v>1.377</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2916,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>25.688</v>
+        <v>1.445</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2933,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>20.752</v>
+        <v>1.797</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2950,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>21.192</v>
+        <v>1.885</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2967,10 +2994,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>21.348</v>
+        <v>1.97</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2984,10 +3011,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>21.86</v>
+        <v>3.157</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3001,10 +3028,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>15.374</v>
+        <v>11.806</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3018,10 +3045,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>15.819</v>
+        <v>14.574</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3035,10 +3062,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>16.612</v>
+        <v>21.692</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3052,10 +3079,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>32.8</v>
+        <v>29.414</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -3069,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>134.456</v>
+        <v>74.223</v>
       </c>
       <c r="C126">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3086,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>199.37</v>
+        <v>114.032</v>
       </c>
       <c r="C127">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3103,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>321.724</v>
+        <v>199.836</v>
       </c>
       <c r="C128">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3120,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>449.13</v>
+        <v>297.479</v>
       </c>
       <c r="C129">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3137,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>788.684</v>
+        <v>499.411</v>
       </c>
       <c r="C130">
-        <v>508</v>
+        <v>367</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3154,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>970.168</v>
+        <v>635.172</v>
       </c>
       <c r="C131">
-        <v>681</v>
+        <v>494</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3171,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>1162.631</v>
+        <v>793.854</v>
       </c>
       <c r="C132">
-        <v>814</v>
+        <v>598</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3188,10 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B133">
-        <v>1329.529</v>
+        <v>946.849</v>
+      </c>
+      <c r="C133">
+        <v>713</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3202,10 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B134">
-        <v>1668.261</v>
+        <v>1239.558</v>
+      </c>
+      <c r="C134">
+        <v>819</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3216,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B135">
-        <v>1817.922</v>
+        <v>1385.831</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3230,10 +3263,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B136">
-        <v>1992.754</v>
+        <v>1509.984</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3244,10 +3277,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B137">
-        <v>2130.33</v>
+        <v>1648.906</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3258,10 +3291,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B138">
-        <v>2370.992</v>
+        <v>1885.642</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3272,10 +3305,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B139">
-        <v>2488.317</v>
+        <v>1998.614</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3286,10 +3319,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B140">
-        <v>2577.48</v>
+        <v>2087.851</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3300,10 +3333,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B141">
-        <v>2658.241</v>
+        <v>2156.544</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3314,10 +3347,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B142">
-        <v>2786.73</v>
+        <v>2307.926</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3328,10 +3361,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B143">
-        <v>2837.678</v>
+        <v>2356.506</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3342,10 +3375,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B144">
-        <v>2893.517</v>
+        <v>2391.671</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3356,10 +3389,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B145">
-        <v>2921.718</v>
+        <v>2412.879</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3370,10 +3403,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B146">
-        <v>2945.099</v>
+        <v>2456.568</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3384,10 +3417,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B147">
-        <v>2955.308</v>
+        <v>2454.316</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3398,10 +3431,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B148">
-        <v>2954.072</v>
+        <v>2442.91</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3412,10 +3445,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B149">
-        <v>2948.462</v>
+        <v>2420.129</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3426,10 +3459,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B150">
-        <v>2899.119</v>
+        <v>2394.444</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3440,10 +3473,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B151">
-        <v>2865.234</v>
+        <v>2353.831</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3454,10 +3487,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B152">
-        <v>2795.538</v>
+        <v>2306.063</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3468,10 +3501,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B153">
-        <v>2730.767</v>
+        <v>2237.795</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3482,10 +3515,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B154">
-        <v>2553.966</v>
+        <v>2116.049</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3496,10 +3529,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B155">
-        <v>2439.794</v>
+        <v>2011.47</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3510,10 +3543,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B156">
-        <v>2302.919</v>
+        <v>1886.886</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3524,10 +3557,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B157">
-        <v>2164.674</v>
+        <v>1754.4</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3538,10 +3571,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B158">
-        <v>1810.539</v>
+        <v>1508.313</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3552,10 +3585,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B159">
-        <v>1627.316</v>
+        <v>1327.8</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3566,10 +3599,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B160">
-        <v>1410.572</v>
+        <v>1132.241</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3580,10 +3613,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B161">
-        <v>1210.464</v>
+        <v>961.468</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3594,10 +3627,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B162">
-        <v>827.659</v>
+        <v>678.6660000000001</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3608,10 +3641,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B163">
-        <v>637.504</v>
+        <v>501.608</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3622,10 +3655,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B164">
-        <v>443.47</v>
+        <v>341.035</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3636,10 +3669,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B165">
-        <v>295.783</v>
+        <v>222.483</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3650,10 +3683,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B166">
-        <v>145.038</v>
+        <v>102.375</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3664,10 +3697,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B167">
-        <v>88.496</v>
+        <v>52.653</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3678,10 +3711,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B168">
-        <v>73.637</v>
+        <v>38.909</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3692,10 +3725,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B169">
-        <v>71.193</v>
+        <v>32.947</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3706,10 +3739,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B170">
-        <v>65.02500000000001</v>
+        <v>38.208</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3720,10 +3753,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B171">
-        <v>62.165</v>
+        <v>40.79</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3734,10 +3767,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B172">
-        <v>63.345</v>
+        <v>37.957</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3748,10 +3781,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B173">
-        <v>60.121</v>
+        <v>38.537</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3762,10 +3795,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B174">
-        <v>53.962</v>
+        <v>37.968</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3776,10 +3809,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B175">
-        <v>53.168</v>
+        <v>38.368</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3790,10 +3823,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B176">
-        <v>53.068</v>
+        <v>33.368</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3804,10 +3837,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B177">
-        <v>53.168</v>
+        <v>30.768</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3818,10 +3851,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B178">
-        <v>9.188000000000001</v>
+        <v>26.368</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3832,10 +3865,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B179">
-        <v>13.588</v>
+        <v>26.468</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3846,10 +3879,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B180">
-        <v>12.088</v>
+        <v>27.768</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3860,10 +3893,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B181">
-        <v>12.488</v>
+        <v>26.668</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3874,10 +3907,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B182">
-        <v>14.888</v>
+        <v>10.588</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3888,10 +3921,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B183">
-        <v>14.088</v>
+        <v>9.788</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3902,16 +3935,142 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B184">
-        <v>7.688</v>
+        <v>11.988</v>
       </c>
       <c r="D184">
         <v>87</v>
       </c>
       <c r="E184" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46320.86458333334</v>
+      </c>
+      <c r="B185">
+        <v>8.988</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46320.875</v>
+      </c>
+      <c r="B186">
+        <v>9.188000000000001</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46320.88541666666</v>
+      </c>
+      <c r="B187">
+        <v>9.788</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46320.89583333334</v>
+      </c>
+      <c r="B188">
+        <v>9.188000000000001</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46320.90625</v>
+      </c>
+      <c r="B189">
+        <v>9.688000000000001</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46320.91666666666</v>
+      </c>
+      <c r="B190">
+        <v>11.188</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46320.92708333334</v>
+      </c>
+      <c r="B191">
+        <v>9.587999999999999</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46320.9375</v>
+      </c>
+      <c r="B192">
+        <v>8.388</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46320.94791666666</v>
+      </c>
+      <c r="B193">
+        <v>7.688</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
